--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -4418,7 +4418,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="40.5" customHeight="1">
+    <row r="16" ht="54" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>PAY-12</t>
@@ -4447,7 +4447,7 @@
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t>• Chiến dịch với đối tượng, thời gian và ưu đãi
-• Chỉ gửi khi có đồng ý nhận tin tiếp thị
+• Chỉ gửi khi có đồng ý nhận tin tiếp thị (cơ chế đồng ý/từ chối được thiết kế cùng tính năng này)
 • Áp dụng giảm giá cho sạc hoặc dịch vụ</t>
         </is>
       </c>
@@ -10376,7 +10376,7 @@
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>• Hồ sơ: họ tên, số điện thoại (tên đăng nhập), e-mail không bắt buộc
-• Trạng thái Đã mời / Hoạt động / Bị khóa; chỉ quản trị nội bộ được khóa cả tài khoản
+• Trạng thái Đã mời / Hoạt động / Bị khóa, kèm lý do; chỉ quản trị nội bộ được khóa cả tài khoản
 • Ghi nhận ai tạo tài khoản và lưu lịch sử thay đổi</t>
         </is>
       </c>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="108" customHeight="1">
+    <row r="8" ht="216" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>ACC-04</t>
@@ -10453,10 +10453,12 @@
       <c r="F8" s="3" t="inlineStr">
         <is>
           <t>• Đăng nhập bằng SĐT + mật khẩu, đăng xuất, hết hạn phiên
+• Xem các thiết bị đang đăng nhập và đăng xuất từng thiết bị hoặc tất cả; mọi phiên kết thúc khi đổi mật khẩu hoặc tài khoản bị khóa
 • Chọn tổ chức sau khi đăng nhập, nhớ tổ chức dùng gần nhất
-• Tạm khóa sau nhiều lần đăng nhập sai
+• Tạm khóa sau nhiều lần đăng nhập sai, kèm giới hạn số lần thử theo thiết bị/IP; vẫn đặt lại mật khẩu bằng OTP được trong lúc bị khóa
 • Mật khẩu chỉ lưu dạng băm một chiều; không dùng lại mật khẩu cũ
-• Ghi nhận lần đăng nhập và hoạt động gần nhất</t>
+• Ghi nhận lần đăng nhập và hoạt động gần nhất
+• Lịch sử đăng nhập (thời gian, IP, thiết bị) cho người dùng và quản trị nội bộ xem; báo người dùng khi đăng nhập từ thiết bị mới</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -10503,7 +10505,7 @@
       </c>
       <c r="Q8" s="3" t="n"/>
     </row>
-    <row r="9" ht="67.5" customHeight="1">
+    <row r="9" ht="94.5" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>ACC-05</t>
@@ -10531,7 +10533,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>• Mã được băm, có hạn dùng và chỉ dùng một lần
+          <t>• Mã được băm, có hạn dùng và chỉ dùng một lần; nhập sai 5 lần thì mã hết hiệu lực; chỉ mã mới nhất được tính
 • Giới hạn số lần gửi theo SĐT để chống lạm dụng và tiết kiệm chi phí SMS
 • Một cơ chế dùng chung cho đăng ký, lời mời, đặt lại mật khẩu và đổi SĐT</t>
         </is>
@@ -10580,7 +10582,7 @@
       </c>
       <c r="Q9" s="3" t="n"/>
     </row>
-    <row r="10" ht="67.5" customHeight="1">
+    <row r="10" ht="108" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ACC-06</t>
@@ -10610,7 +10612,8 @@
         <is>
           <t>• Quên mật khẩu: OTP gửi tới SĐT đã đăng ký, rồi đặt mật khẩu mới
 • Đổi SĐT: OTP gửi tới số mới; thay đổi được lưu lịch sử
-• Đổi mật khẩu khi đang đăng nhập</t>
+• Đổi mật khẩu khi đang đăng nhập
+• CSKH hoặc quản trị tổ chức xác minh thêm trước khi đặt lại mật khẩu cho tài khoản lâu không hoạt động (số điện thoại có thể bị nhà mạng cấp lại)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -10735,7 +10738,7 @@
       </c>
       <c r="Q11" s="3" t="n"/>
     </row>
-    <row r="12" ht="40.5" customHeight="1">
+    <row r="12" ht="67.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>ACC-08</t>
@@ -10765,7 +10768,8 @@
         <is>
           <t>• Tạo tổ chức và gói thuê bao trong một luồng
 • Mời quản trị viên đầu tiên của tổ chức qua SĐT
-• Gán nhân viên phụ trách</t>
+• Gán nhân viên phụ trách
+• Quản trị viên đầu tiên chấp thuận thỏa thuận xử lý dữ liệu thay mặt doanh nghiệp ở lần đăng nhập đầu</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -11041,7 +11045,7 @@
       </c>
       <c r="Q15" s="3" t="n"/>
     </row>
-    <row r="16" ht="54" customHeight="1">
+    <row r="16" ht="67.5" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>ACC-12</t>
@@ -11070,7 +11074,7 @@
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t>• Danh sách thành viên của tổ chức kèm vai trò
-• Khóa, mở khóa hoặc cho thành viên rời tổ chức (vẫn giữ lịch sử)
+• Khóa, mở khóa hoặc cho thành viên rời tổ chức kèm lý do (vẫn giữ lịch sử); xem thời điểm mời và thời điểm tham gia của từng thành viên
 • Người dùng xem và chuyển giữa các tổ chức của mình</t>
         </is>
       </c>
@@ -11118,7 +11122,7 @@
       </c>
       <c r="Q16" s="3" t="n"/>
     </row>
-    <row r="17" ht="81" customHeight="1">
+    <row r="17" ht="108" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>ACC-13</t>
@@ -11146,8 +11150,8 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>• Gán và thu hồi vai trò theo từng thành viên, có lịch sử
-• Luôn còn ít nhất một quản trị tổ chức đang hoạt động
+          <t>• Gán và thu hồi vai trò theo từng thành viên, có lịch sử: ai đã cấp hoặc thu hồi từng vai trò, và khi nào
+• Đúng một quản trị tổ chức: chuyển giao vai trò trong một bước; đồng quản trị của chúng ta chỉ định người mới khi quản trị viên không còn
 • Vai trò quản trị trưởng và đồng quản trị chỉ có ở tổ chức nội bộ; đồng quản trị không quản lý được quản trị viên</t>
         </is>
       </c>
@@ -11358,7 +11362,7 @@
       </c>
       <c r="Q19" s="3" t="n"/>
     </row>
-    <row r="20" ht="54" customHeight="1">
+    <row r="20" ht="94.5" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>ACC-16</t>
@@ -11386,8 +11390,9 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>• Lưu token Firebase theo thiết bị, làm mới khi đăng nhập
-• Xóa token khi đăng xuất, khi bị báo hủy đăng ký và khi quá cũ</t>
+          <t>• Lưu token Firebase trên phiên đăng nhập của thiết bị, làm mới khi đăng nhập; không bắt buộc khi người dùng từ chối thông báo
+• Token mất cùng với phiên: đăng xuất, hết hạn, đổi mật khẩu, khóa tài khoản, hoặc app bị báo đã gỡ
+• Thông báo của mọi tổ chức của người dùng tới mọi thiết bị; mở thông báo sẽ chuyển sang tổ chức của nó</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -11434,7 +11439,7 @@
       </c>
       <c r="Q20" s="3" t="n"/>
     </row>
-    <row r="21" ht="67.5" customHeight="1">
+    <row r="21" ht="189" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>ACC-17</t>
@@ -11442,30 +11447,31 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đồng ý xử lý dữ liệu</t>
+          <t>Chấp thuận văn bản pháp lý &amp; đồng ý xử lý dữ liệu</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Ghi nhận việc mỗi người đồng ý điều khoản, chính sách quyền riêng tư và theo dõi vị trí, theo từng phiên bản văn bản, và cho phép rút lại.</t>
+          <t>Ghi nhận ai đã chấp thuận phiên bản nào của văn bản pháp lý nào: doanh nghiệp chấp thuận thỏa thuận xử lý dữ liệu thay mặt chính mình, tài xế là nhân viên xác nhận đã đọc thông báo quyền riêng tư, khách hàng cá nhân chấp thuận điều khoản, chính sách quyền riêng tư và theo dõi vị trí.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Chứng minh việc xử lý dữ liệu cá nhân đúng luật (Nghị định 13/2023, Luật 91/2025/QH15).</t>
+          <t>Chứng minh việc xử lý dữ liệu cá nhân đúng luật (Nghị định 13/2023, Luật 91/2025/QH15) bằng đúng văn bản đã được chấp thuận.</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Tài xế, Quản trị tổ chức, Hệ thống (tự động)</t>
+          <t>Tài xế, Quản trị tổ chức, Đồng quản trị (nội bộ), Hệ thống (tự động)</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>• Xin đồng ý khi kích hoạt, theo từng mục đích, kèm phiên bản văn bản
-• Rút lại đồng ý; ghi nhận thời điểm và kênh
-• Xin đồng ý lại khi văn bản thay đổi
-• Chỉ gửi tin tiếp thị khi có đồng ý nhận tin tiếp thị</t>
+          <t>• Công bố các phiên bản của từng văn bản pháp lý; phiên bản mới yêu cầu mọi người liên quan chấp thuận lại trước khi tiếp tục
+• Quản trị tổ chức chấp thuận thỏa thuận xử lý dữ liệu thay mặt doanh nghiệp ở lần đăng nhập đầu; thành viên chưa dùng được hệ thống trước đó
+• Tài xế là nhân viên xác nhận đã đọc thông báo quyền riêng tư mỗi phiên bản một lần; khách hàng cá nhân đồng ý theo từng mục đích
+• Bằng chứng lưu kèm mỗi lần chấp thuận: đúng phiên bản văn bản, thời điểm, IP và thiết bị; không bao giờ sửa
+• Rút lại chấp thuận bắt buộc nghĩa là ngừng sử dụng dịch vụ (đóng tài khoản)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -11502,17 +11508,17 @@
       <c r="N21" s="3" t="n"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>• Khi tài xế rút đồng ý theo dõi vị trí, xe của doanh nghiệp có còn được theo dõi vị trí không?</t>
+          <t>• Luật sư cần xác nhận mô hình thỏa thuận với doanh nghiệp tại Việt Nam (câu hỏi mở 6).</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-37, NF-08, Quyết định ID-20</t>
+          <t>Bảng dữ liệu IN-37, NF-08, Quyết định ID-20, Quyết định ID-38</t>
         </is>
       </c>
       <c r="Q21" s="3" t="n"/>
     </row>
-    <row r="22" ht="81" customHeight="1">
+    <row r="22" ht="148.5" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>ACC-18</t>
@@ -11542,7 +11548,9 @@
         <is>
           <t>• Nhật ký chỉ ghi thêm cho mọi lần truy cập dữ liệu cá nhân, vị trí và camera
 • Yêu cầu lý do hoặc mã ticket trước khi trích xuất dữ liệu nhạy cảm
-• Tra cứu nhật ký theo người truy cập, người được truy cập, thời gian và loại dữ liệu</t>
+• Tra cứu nhật ký theo người truy cập, tổ chức, thời gian và loại dữ liệu
+• Ghi một dòng mỗi lần mở màn hình (không ghi mỗi lần làm mới); lưu vĩnh viễn, các tháng cũ được nén
+• Sự kiện bảo mật tài khoản trong cùng nhật ký: đăng nhập, đăng nhập sai, bị khóa tạm, đăng xuất, đổi mật khẩu và số điện thoại, kèm IP và thiết bị</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -11203,7 +11203,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="81" customHeight="1">
+    <row r="18" ht="135" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>ACC-14</t>
@@ -11233,6 +11233,7 @@
         <is>
           <t>• Tính năng = vai trò ∩ gói với khách hàng; toàn bộ vai trò với người dùng nội bộ
 • Tính năng chỉ dành cho nội bộ không bao giờ nằm trong gói
+• Một vai trò cho người dùng nội bộ và khách hàng cùng các tính năng; khác nhau chỉ ở phạm vi dữ liệu được xem. Danh sách tính năng của từng vai trò được cấp trong một bước khi gần hoàn tất các tính năng
 • App và portal ẩn những gì người dùng không được dùng
 • Khóa tính năng khi thuê bao quá hạn</t>
         </is>
@@ -11276,7 +11277,7 @@
       <c r="O18" s="3" t="n"/>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>PRD F-F1, Quyết định ID-11</t>
+          <t>PRD F-F1, Quyết định ID-11, Quyết định ID-44</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -11506,14 +11507,10 @@
       </c>
       <c r="M21" s="3" t="n"/>
       <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>• Luật sư cần xác nhận mô hình thỏa thuận với doanh nghiệp tại Việt Nam (câu hỏi mở 6).</t>
-        </is>
-      </c>
+      <c r="O21" s="3" t="n"/>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-37, NF-08, Quyết định ID-20, Quyết định ID-38</t>
+          <t>Bảng dữ liệu IN-37, NF-08, Quyết định ID-20, Quyết định ID-38, Quyết định ID-43</t>
         </is>
       </c>
       <c r="Q21" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -12700,7 +12700,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="40.5" customHeight="1">
+    <row r="5" ht="135" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>VEH-01</t>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Lưu hồ sơ từng xe: số VIN, biển số, dòng xe, ngày bàn giao, trạng thái bảo hành và trạng thái hoạt động.</t>
+          <t>Lưu hồ sơ từng xe: số VIN, biển số, dòng xe, ngày bàn giao, trạng thái bảo hành và trạng thái phục vụ.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -12729,7 +12729,9 @@
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>• Tạo, sửa, tìm kiếm và ngừng sử dụng xe
-• VIN và biển số không trùng; lưu lịch sử thay đổi
+• VIN và biển số không trùng trong các xe đang dùng và đều sửa được (nhập nhầm, biển số theo chủ xe); lưu lịch sử thay đổi kèm lý do
+• Trạng thái phục vụ do con người đặt: đang phục vụ, đang bảo dưỡng, đã rời hệ thống, kèm lý do; xe nhàn rỗi hay mất tín hiệu được hiển thị từ dữ liệu, không lưu
+• Bảo hành theo từng xe, pin và thiết bị với giới hạn riêng; bảo hành bị hủy lưu kèm lý do
 • Lọc theo trạng thái, dòng xe, chủ sở hữu và đội xe</t>
         </is>
       </c>
@@ -12765,14 +12767,10 @@
       </c>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>• Biển số có được thay đổi sau khi đăng ký không (đăng ký lại, sang tên)?</t>
-        </is>
-      </c>
+      <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-32, PRD F-F2</t>
+          <t>Bảng dữ liệu IN-32, PRD F-F2, Quyết định VH-05, Quyết định VH-07, Quyết định VH-09</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -12932,12 +12930,12 @@
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-32, Bảng dữ liệu IN-34, deferred.md 61</t>
+          <t>Bảng dữ liệu IN-32, Bảng dữ liệu IN-34, deferred.md 61, Quyết định VH-08</t>
         </is>
       </c>
       <c r="Q7" s="3" t="n"/>
     </row>
-    <row r="8" ht="54" customHeight="1">
+    <row r="8" ht="67.5" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>VEH-04</t>
@@ -12950,12 +12948,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Lưu hồ sơ từng pack pin: hóa học pin, dung lượng thiết kế và sơ đồ cell/module (mã cell và vị trí).</t>
+          <t>Quản lý từng pin xe như một tài sản: dòng pin, chủ sở hữu và các xe pin đã được lắp.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Cho phép chẩn đoán cấp cell và thay cell đơn lẻ.</t>
+          <t>Pin chiếm tới hai phần ba giá xe; sức khỏe, bảo hành và giá trị của pin đi theo pin từ xe này sang xe khác.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -12965,9 +12963,9 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>• Mã pack, hóa học (LFP/CATL), dung lượng thiết kế, gắn với xe
-• Sơ đồ cell/module: số lượng, mã và vị trí
-• Lịch sử thay pack</t>
+          <t>• Danh mục dòng pin: hóa học (LFP/CATL), dung lượng thiết kế, điện áp, cấu trúc
+• Từng pin: số serial, dòng pin, chủ sở hữu (có thể khác chủ xe), trạng thái kèm lý do
+• Mỗi xe một pin; lịch sử pin đã được lắp trên xe nào</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -13009,7 +13007,7 @@
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-33</t>
+          <t>Bảng dữ liệu IN-33, Quyết định VH-08, deferred.md 87, deferred.md 88</t>
         </is>
       </c>
       <c r="Q8" s="3" t="n"/>
@@ -13042,7 +13040,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>• Các bước kích hoạt: chờ, đã gắn thiết bị, đã kích hoạt khi có dữ liệu đầu tiên
+          <t>• Kích hoạt được tính từ thiết bị đang lắp và dữ liệu đã nhận, nên xe bị tháo T-Box sẽ hiện đúng như vậy
 • Tỷ lệ kích hoạt thành công và danh sách xe còn đang chờ</t>
         </is>
       </c>
@@ -13085,7 +13083,7 @@
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>PRD F-F2, Quyết định VH-01</t>
+          <t>PRD F-F2, Quyết định VH-06</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -16569,7 +16567,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>• Mỗi tài xế một xe và mỗi xe một tài xế đang hoạt động
+          <t>• Mỗi tài xế một xe đang hoạt động; một xe có thể có nhiều tài xế cùng lúc (chia ca, lái phụ)
 • Đổi xe trong một bước; lịch sử theo tài xế và theo xe</t>
         </is>
       </c>
@@ -16616,7 +16614,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-01</t>
+          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-01, Quyết định DR-05</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -917,7 +917,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>0/63</t>
+          <t>0/64</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -16539,7 +16539,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="189" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>DRV-02</t>
@@ -16547,28 +16547,32 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Phân công xe</t>
+          <t>Nhận xe</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Giao và đổi xe cho tài xế, lưu toàn bộ lịch sử phân công.</t>
+          <t>Tài xế nhận chiếc xe sắp lái bằng cách quét mã QR trên xe hoặc chọn xe trên ứng dụng; hệ thống luôn biết ai đang cầm lái và lưu toàn bộ lịch sử.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Mọi sự kiện của xe đều truy được tài xế tại thời điểm đó.</t>
+          <t>Trong vận tải chặng ngắn, tài xế và xe đổi nhau hằng ngày; mọi sự kiện của xe vẫn truy được tài xế tại thời điểm đó.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe, Điều vận</t>
+          <t>Tài xế, Quản lý đội xe, Điều vận, Hệ thống (tự động)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>• Mỗi tài xế một xe đang hoạt động; một xe có thể có nhiều tài xế cùng lúc (chia ca, lái phụ)
-• Đổi xe trong một bước; lịch sử theo tài xế và theo xe</t>
+          <t>• Nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, bị từ chối khi điện thoại ở xa xe; quản lý có thể nhận xe giúp tài xế trên portal
+• Tài xế đang hoạt động nào cũng có thể lái xe của bất kỳ tổ chức nào; cảnh báo khi tài xế thuộc tổ chức khác
+• Mỗi xe một người cầm lái; phiên kết thúc khi trả xe, khi tài xế khác nhận xe, khi tài xế nhận xe khác, hoặc khi xe không di chuyển quá thời gian tự kết thúc của tổ chức (mặc định 2 giờ)
+• Cảnh báo lên portal khi xe chạy mà không ai nhận xe
+• Cảnh báo dành cho tài xế gửi tới tài xế đang nhận xe và portal
+• Lịch sử theo tài xế và theo xe</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -16593,7 +16597,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Không cần</t>
+          <t>Chưa làm</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -16607,14 +16611,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>• Hai tài xế dùng chung một xe theo ca: một hay hai tài khoản app? (xem DRV-04)</t>
-        </is>
-      </c>
+      <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-01, Quyết định DR-05</t>
+          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-07, Quyết định NT-07, Quyết định ID-45</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -16614,7 +16614,7 @@
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-07, Quyết định NT-07, Quyết định ID-45</t>
+          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-07, Quyết định DR-08, Quyết định NT-07, Quyết định ID-45</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -12779,7 +12779,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="40.5" customHeight="1">
+    <row r="6" ht="108" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>VEH-02</t>
@@ -12808,7 +12808,8 @@
       <c r="F6" s="3" t="inlineStr">
         <is>
           <t>• Ghi nhận chủ sở hữu khi bàn giao
-• Chuyển quyền sở hữu kèm ngày hiệu lực; lưu lịch sử</t>
+• Chuyển quyền sở hữu kèm ngày hiệu lực trong một bước: tư cách thành viên đội xe, phiên lái, quy tắc sạc, thuê bao và thẻ sạc theo VIN của bên bán đối với xe kết thúc cùng lúc
+• Chủ cũ giữ dữ liệu của mình trước ngày bán; tình trạng xe và các tổng tích lũy đi theo xe sang chủ mới; mọi giai đoạn sở hữu kèm người ghi nhận và lý do</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -12847,14 +12848,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>• Sau khi đổi chủ, chủ mới có xem được dữ liệu của xe trước ngày chuyển không? (quyết định mở D3)</t>
-        </is>
-      </c>
+      <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-32, Quyết định VH-03</t>
+          <t>Bảng dữ liệu IN-32, Quyết định VH-03, Quyết định VH-10, Quyết định VH-11, Quyết định VH-12</t>
         </is>
       </c>
       <c r="Q6" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -10,23 +10,24 @@
     <sheet name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ACC Tài khoản &amp; phân quyền" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="VEH Hồ sơ xe" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DEV Thiết bị telematics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="MON Giám sát xe &amp; pin" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="RTE Quãng đường &amp; lộ trình" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DRV Tài xế" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="FLT Quản lý đội xe" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="STN Mạng lưới trạm sạc" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="CHG Phiên sạc" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="POL Chính sách sạc &amp; bảo hành" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="PAY Gói, thanh toán &amp; hóa đơn" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="NTF Thông báo" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="SUP CSKH &amp; cứu hộ" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="MNT Bảo dưỡng &amp; tài sản" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="SAF An toàn lái xe &amp; camera" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="CRB Carbon &amp; chuyển đổi xanh" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="PLT Nền tảng, dữ liệu, tuân thủ" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="TMS Tích hợp TMS (Phase 2)" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Phi chức năng" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="BAT Pin" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="DEV Thiết bị telematics" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MON Giám sát xe &amp; pin" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="RTE Quãng đường &amp; lộ trình" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DRV Tài xế" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FLT Quản lý đội xe" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="STN Mạng lưới trạm sạc" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="CHG Phiên sạc" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="POL Chính sách sạc &amp; bảo hành" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="PAY Gói, thanh toán &amp; hóa đơn" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="NTF Thông báo" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="SUP CSKH &amp; cứu hộ" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="MNT Bảo dưỡng &amp; tài sản" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SAF An toàn lái xe &amp; camera" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="CRB Carbon &amp; chuyển đổi xanh" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="PLT Nền tảng, dữ liệu, tuân thủ" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TMS Tích hợp TMS (Phase 2)" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Phi chức năng" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -669,7 +670,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Hồ sơ xe, chủ sở hữu, dòng xe, thông tin pin và kích hoạt xe khi bàn giao.</t>
+          <t>Hồ sơ xe, chủ sở hữu, dòng xe và kích hoạt xe khi bàn giao.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -678,17 +679,17 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -698,7 +699,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -713,38 +714,36 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>DEV</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Thiết bị telematics</t>
+          <t>Pin</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Thiết bị gắn trên xe gửi dữ liệu về: danh mục, gắn với xe, sức khỏe thiết bị, bảo mật và cấu hình từ xa.</t>
+          <t>Quản lý từng pin xe như một tài sản riêng: dòng pin, chủ sở hữu và các xe pin đã được lắp.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>telematics</t>
+          <t>batteries</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -754,7 +753,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -769,50 +768,48 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>MON</t>
+          <t>DEV</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Giám sát xe &amp; pin</t>
+          <t>Thiết bị telematics</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Dữ liệu xe theo thời gian thực và lịch sử, cảnh báo pin và an toàn, sức khỏe pin, chuyến đi và báo cáo vận hành.</t>
+          <t>Thiết bị gắn trên xe gửi dữ liệu về: danh mục, gắn với xe, sức khỏe thiết bị, bảo mật và cấu hình từ xa.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>telemetry</t>
+          <t>telematics</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>0/18</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>0/16</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -827,17 +824,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>RTE</t>
+          <t>MON</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Quãng đường &amp; lộ trình</t>
+          <t>Giám sát xe &amp; pin</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Xe còn đi được bao xa, bao lâu, có tới được đích không, nên sạc ở đâu và lúc nào, và những đoạn đường cấm tải.</t>
+          <t>Dữ liệu xe theo thời gian thực và lịch sử, cảnh báo pin và an toàn, sức khỏe pin, chuyến đi và báo cáo vận hành.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -846,29 +843,31 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/10</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/16</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -883,36 +882,38 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DRV</t>
+          <t>RTE</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Tài xế</t>
+          <t>Quãng đường &amp; lộ trình</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Hồ sơ tài xế, phân công xe, ca làm việc, thời gian lái và báo cáo theo tài xế.</t>
+          <t>Xe còn đi được bao xa, bao lâu, có tới được đích không, nên sạc ở đâu và lúc nào, và những đoạn đường cấm tải.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>drivers</t>
+          <t>telemetry</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -922,7 +923,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -937,46 +938,46 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>FLT</t>
+          <t>DRV</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Quản lý đội xe</t>
+          <t>Tài xế</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Nhóm xe trong một tổ chức, người quản lý, bản đồ đội xe, vùng địa lý và báo cáo đội xe.</t>
+          <t>Hồ sơ tài xế, phân công xe, ca làm việc, thời gian lái và báo cáo theo tài xế.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>fleet</t>
+          <t>drivers</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -991,50 +992,46 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>STN</t>
+          <t>FLT</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Mạng lưới trạm sạc</t>
+          <t>Quản lý đội xe</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Trạm và trụ sạc, trạng thái realtime qua OCPP, sự cố, bản đồ trạm, hàng đợi, đặt chỗ và phân tải.</t>
+          <t>Nhóm xe trong một tổ chức, người quản lý, bản đồ đội xe, vùng địa lý và báo cáo đội xe.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>charging_stations</t>
+          <t>fleet</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>0/15</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>0/12</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1049,48 +1046,50 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>CHG</t>
+          <t>STN</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Phiên sạc</t>
+          <t>Mạng lưới trạm sạc</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Bắt đầu sạc, bản ghi phiên sạc, biên nhận, lịch sử, điện năng theo khách hàng và đối soát.</t>
+          <t>Trạm và trụ sạc, trạng thái realtime qua OCPP, sự cố, bản đồ trạm, hàng đợi, đặt chỗ và phân tải.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>charging_stations</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="3" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="I11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/15</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/12</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1099,47 +1098,49 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="40.5" customHeight="1">
+    <row r="12" ht="27" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>CHG</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Chính sách sạc &amp; bảo hành</t>
+          <t>Phiên sạc</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Quy tắc sạc gắn với bảo hành, phát hiện vi phạm kèm bằng chứng, và nguy cơ mất bảo hành cho tài xế, đội xe và bộ phận bảo hành.</t>
+          <t>Bắt đầu sạc, bản ghi phiên sạc, biên nhận, lịch sử, điện năng theo khách hàng và đối soát.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>policy</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
+      <c r="I12" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1159,48 +1160,46 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>PAY</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Gói dịch vụ, thanh toán &amp; hóa đơn</t>
+          <t>Chính sách sạc &amp; bảo hành</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Khách hàng mua gì (tính năng, gói, tiện ích thêm), cách thanh toán tiền sạc và thuê bao, biểu giá và hóa đơn điện tử.</t>
+          <t>Quy tắc sạc gắn với bảo hành, phát hiện vi phạm kèm bằng chứng, và nguy cơ mất bảo hành cho tài xế, đội xe và bộ phận bảo hành.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>billing</t>
+          <t>policy</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>0/13</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>0/10</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1209,54 +1208,54 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14" ht="40.5" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>NTF</t>
+          <t>PAY</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>Gói dịch vụ, thanh toán &amp; hóa đơn</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Gửi cảnh báo và tin nhắn tới đúng người, đúng kênh (app, portal, push, SMS, e-mail).</t>
+          <t>Khách hàng mua gì (tính năng, gói, tiện ích thêm), cách thanh toán tiền sạc và thuê bao, biểu giá và hóa đơn điện tử.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>billing</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/13</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/10</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1271,43 +1270,43 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>SUP</t>
+          <t>NTF</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>CSKH &amp; cứu hộ</t>
+          <t>Thông báo</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Yêu cầu hỗ trợ, SOS, hàng đợi CSKH và SLA, điều phối đối tác sửa chữa – cứu hộ.</t>
+          <t>Gửi cảnh báo và tin nhắn tới đúng người, đúng kênh (app, portal, push, SMS, e-mail).</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="H15" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1327,50 +1326,48 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>MNT</t>
+          <t>SUP</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Bảo dưỡng &amp; vòng đời tài sản</t>
+          <t>CSKH &amp; cứu hộ</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Nhắc và đặt lịch bảo dưỡng, hồ sơ sửa chữa, chi phí bảo dưỡng, khấu hao và vòng đời vật tư.</t>
+          <t>Yêu cầu hỗ trợ, SOS, hàng đợi CSKH và SLA, điều phối đối tác sửa chữa – cứu hộ.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>support</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>0/10</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>0/10</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1379,52 +1376,56 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="40.5" customHeight="1">
+    <row r="17" ht="27" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>SAF</t>
+          <t>MNT</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>An toàn lái xe &amp; camera</t>
+          <t>Bảo dưỡng &amp; vòng đời tài sản</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Chấm điểm an toàn lái xe, camera giám sát người lái, cảnh báo ADAS trong cabin, clip bằng chứng và nghĩa vụ pháp lý của camera.</t>
+          <t>Nhắc và đặt lịch bảo dưỡng, hồ sơ sửa chữa, chi phí bảo dưỡng, khấu hao và vòng đời vật tư.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>scoring</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
+      <c r="I17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>0/9</t>
+          <t>0/10</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/10</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1433,52 +1434,52 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="27" customHeight="1">
+    <row r="18" ht="40.5" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>SAF</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Kiểm kê carbon &amp; chuyển đổi xanh</t>
+          <t>An toàn lái xe &amp; camera</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Lượng phát thải giảm được nhờ xe điện, sạc xanh, kiểm kê khí nhà kính của đội xe và hồ sơ tín chỉ carbon.</t>
+          <t>Chấm điểm an toàn lái xe, camera giám sát người lái, cảnh báo ADAS trong cabin, clip bằng chứng và nghĩa vụ pháp lý của camera.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>carbon</t>
+          <t>scoring</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H18" s="3" t="n"/>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>0/11</t>
+          <t>0/9</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1493,264 +1494,304 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>PLT</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Nền tảng, dữ liệu &amp; tuân thủ</t>
+          <t>Kiểm kê carbon &amp; chuyển đổi xanh</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Đường ống và kho dữ liệu, sức khỏe hệ thống, lưu trữ dữ liệu, chủ quyền dữ liệu và dashboard toàn công ty.</t>
+          <t>Lượng phát thải giảm được nhờ xe điện, sạc xanh, kiểm kê khí nhà kính của đội xe và hồ sơ tín chỉ carbon.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Chưa có</t>
+          <t>carbon</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
           <t>0/7</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="40.5" customHeight="1">
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" s="3" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>PLT</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Nền tảng, dữ liệu &amp; tuân thủ</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Đường ống và kho dữ liệu, sức khỏe hệ thống, lưu trữ dữ liệu, chủ quyền dữ liệu và dashboard toàn công ty.</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>0/7</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40.5" customHeight="1">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>TMS</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Tích hợp quản lý vận tải (Phase 2)</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Đơn hàng, chủ hàng và depot, làm ở Phase 2 bằng cách tích hợp với hệ thống quản lý vận tải (TMS) của khách hàng, không thay thế TMS.</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n">
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>0/6</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n">
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n">
         <v>177</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G22" s="5" t="n">
         <v>143</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I22" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="J22" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>0/175</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>0/64</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>0/137</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Yêu cầu phi chức năng</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n">
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25" ht="27" customHeight="1">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>CÁCH ĐỌC</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Trạng thái</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Theo từng phần cần làm (Backend, App, Portal web): Chưa làm, Đang làm, Xong. 'Không cần' = tính năng không cần phần đó. Cột 'xong' ở trên = số tính năng đã xong / số tính năng cần phần đó.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+    <row r="26" ht="54" customHeight="1">
       <c r="A26" s="3" t="n"/>
       <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Ưu tiên</t>
+          <t>Trạng thái</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Bắt buộc (Must), Nên có (Should), Có thì tốt (Could)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="27" customHeight="1">
+          <t>Theo từng phần cần làm (Backend, App, Portal web): Chưa làm, Đang làm, Xong. 'Không cần' = tính năng không cần phần đó. Cột 'xong' ở trên = số tính năng đã xong / số tính năng cần phần đó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" s="3" t="n"/>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Đợt</t>
+          <t>Ưu tiên</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>P1.0 ra mắt, P1.1 khoảng 90 ngày sau, P1.5 năm 2026–27, P2 Phase 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="40.5" customHeight="1">
+          <t>Bắt buộc (Must), Nên có (Should), Có thì tốt (Could)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="27" customHeight="1">
       <c r="A28" s="3" t="n"/>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hình thức bán</t>
+          <t>Đợt</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Chỉ nội bộ (không bán); Có trong mọi gói; Chưa định giá. Giá được bổ sung khi làm phần định giá; tính năng nội bộ không bao giờ nằm trong gói.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+          <t>P1.0 ra mắt, P1.1 khoảng 90 ngày sau, P1.5 năm 2026–27, P2 Phase 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40.5" customHeight="1">
       <c r="A29" s="3" t="n"/>
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="3" t="inlineStr">
         <is>
+          <t>Hình thức bán</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán); Có trong mọi gói; Chưa định giá. Giá được bổ sung khi làm phần định giá; tính năng nội bộ không bao giờ nằm trong gói.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n"/>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
           <t>Bảng dữ liệu</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Để trống cho tới khi rà soát xong thiết kế cơ sở dữ liệu.</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31" ht="27" customHeight="1">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="6" t="inlineStr">
+    <row r="31"/>
+    <row r="32" ht="27" customHeight="1">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>VAI TRÒ</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Quản trị trưởng (nội bộ)</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>HEAD_ADMIN</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1800,12 @@
       <c r="B33" s="3" t="n"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Đồng quản trị (nội bộ)</t>
+          <t>Quản trị trưởng (nội bộ)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>CO_ADMIN</t>
+          <t>HEAD_ADMIN</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1814,12 @@
       <c r="B34" s="3" t="n"/>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Quản trị tổ chức</t>
+          <t>Đồng quản trị (nội bộ)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>ORG_ADMIN</t>
+          <t>CO_ADMIN</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1828,12 @@
       <c r="B35" s="3" t="n"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Kinh doanh</t>
+          <t>Quản trị tổ chức</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>ORG_ADMIN</t>
         </is>
       </c>
     </row>
@@ -1801,12 +1842,12 @@
       <c r="B36" s="3" t="n"/>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Kế toán</t>
+          <t>Kinh doanh</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>ACCOUNTANT</t>
+          <t>SALES</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1856,12 @@
       <c r="B37" s="3" t="n"/>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>CSKH</t>
+          <t>Kế toán</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>CUSTOMER_CARE</t>
+          <t>ACCOUNTANT</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1870,12 @@
       <c r="B38" s="3" t="n"/>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>CSKH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>CUSTOMER_CARE</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1884,12 @@
       <c r="B39" s="3" t="n"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Bảo trì</t>
+          <t>Vận hành</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>MAINTENANCE</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1898,12 @@
       <c r="B40" s="3" t="n"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Bảo trì</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>WARRANTY</t>
+          <t>MAINTENANCE</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1912,12 @@
       <c r="B41" s="3" t="n"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>FLEET_MANAGER</t>
+          <t>WARRANTY</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1926,12 @@
       <c r="B42" s="3" t="n"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Điều vận</t>
+          <t>Quản lý đội xe</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>DISPATCHER</t>
+          <t>FLEET_MANAGER</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1940,12 @@
       <c r="B43" s="3" t="n"/>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Tài xế</t>
+          <t>Điều vận</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>DISPATCHER</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1954,12 @@
       <c r="B44" s="3" t="n"/>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Kỹ thuật viên đối tác</t>
+          <t>Tài xế</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>TECHNICIAN</t>
+          <t>DRIVER</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1968,12 @@
       <c r="B45" s="3" t="n"/>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Hệ thống (tự động)</t>
+          <t>Kỹ thuật viên đối tác</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>SYSTEM</t>
+          <t>TECHNICIAN</t>
         </is>
       </c>
     </row>
@@ -1941,10 +1982,24 @@
       <c r="B46" s="3" t="n"/>
       <c r="C46" s="3" t="inlineStr">
         <is>
+          <t>Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n"/>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
           <t>Hệ thống bên ngoài</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>EXTERNAL</t>
         </is>
@@ -1956,45 +2011,1384 @@
     <hyperlink ref="N3" location="'ACC Tài khoản &amp; phân quyền'!A1"/>
     <hyperlink ref="C4" location="'VEH Hồ sơ xe'!A1"/>
     <hyperlink ref="N4" location="'VEH Hồ sơ xe'!A1"/>
-    <hyperlink ref="C5" location="'DEV Thiết bị telematics'!A1"/>
-    <hyperlink ref="N5" location="'DEV Thiết bị telematics'!A1"/>
-    <hyperlink ref="C6" location="'MON Giám sát xe &amp; pin'!A1"/>
-    <hyperlink ref="N6" location="'MON Giám sát xe &amp; pin'!A1"/>
-    <hyperlink ref="C7" location="'RTE Quãng đường &amp; lộ trình'!A1"/>
-    <hyperlink ref="N7" location="'RTE Quãng đường &amp; lộ trình'!A1"/>
-    <hyperlink ref="C8" location="'DRV Tài xế'!A1"/>
-    <hyperlink ref="N8" location="'DRV Tài xế'!A1"/>
-    <hyperlink ref="C9" location="'FLT Quản lý đội xe'!A1"/>
-    <hyperlink ref="N9" location="'FLT Quản lý đội xe'!A1"/>
-    <hyperlink ref="C10" location="'STN Mạng lưới trạm sạc'!A1"/>
-    <hyperlink ref="N10" location="'STN Mạng lưới trạm sạc'!A1"/>
-    <hyperlink ref="C11" location="'CHG Phiên sạc'!A1"/>
-    <hyperlink ref="N11" location="'CHG Phiên sạc'!A1"/>
-    <hyperlink ref="C12" location="'POL Chính sách sạc &amp; bảo hành'!A1"/>
-    <hyperlink ref="N12" location="'POL Chính sách sạc &amp; bảo hành'!A1"/>
-    <hyperlink ref="C13" location="'PAY Gói, thanh toán &amp; hóa đơn'!A1"/>
-    <hyperlink ref="N13" location="'PAY Gói, thanh toán &amp; hóa đơn'!A1"/>
-    <hyperlink ref="C14" location="'NTF Thông báo'!A1"/>
-    <hyperlink ref="N14" location="'NTF Thông báo'!A1"/>
-    <hyperlink ref="C15" location="'SUP CSKH &amp; cứu hộ'!A1"/>
-    <hyperlink ref="N15" location="'SUP CSKH &amp; cứu hộ'!A1"/>
-    <hyperlink ref="C16" location="'MNT Bảo dưỡng &amp; tài sản'!A1"/>
-    <hyperlink ref="N16" location="'MNT Bảo dưỡng &amp; tài sản'!A1"/>
-    <hyperlink ref="C17" location="'SAF An toàn lái xe &amp; camera'!A1"/>
-    <hyperlink ref="N17" location="'SAF An toàn lái xe &amp; camera'!A1"/>
-    <hyperlink ref="C18" location="'CRB Carbon &amp; chuyển đổi xanh'!A1"/>
-    <hyperlink ref="N18" location="'CRB Carbon &amp; chuyển đổi xanh'!A1"/>
-    <hyperlink ref="C19" location="'PLT Nền tảng, dữ liệu, tuân thủ'!A1"/>
-    <hyperlink ref="N19" location="'PLT Nền tảng, dữ liệu, tuân thủ'!A1"/>
-    <hyperlink ref="C20" location="'TMS Tích hợp TMS (Phase 2)'!A1"/>
-    <hyperlink ref="N20" location="'TMS Tích hợp TMS (Phase 2)'!A1"/>
-    <hyperlink ref="C22" location="'Phi chức năng'!A1"/>
+    <hyperlink ref="C5" location="'BAT Pin'!A1"/>
+    <hyperlink ref="N5" location="'BAT Pin'!A1"/>
+    <hyperlink ref="C6" location="'DEV Thiết bị telematics'!A1"/>
+    <hyperlink ref="N6" location="'DEV Thiết bị telematics'!A1"/>
+    <hyperlink ref="C7" location="'MON Giám sát xe &amp; pin'!A1"/>
+    <hyperlink ref="N7" location="'MON Giám sát xe &amp; pin'!A1"/>
+    <hyperlink ref="C8" location="'RTE Quãng đường &amp; lộ trình'!A1"/>
+    <hyperlink ref="N8" location="'RTE Quãng đường &amp; lộ trình'!A1"/>
+    <hyperlink ref="C9" location="'DRV Tài xế'!A1"/>
+    <hyperlink ref="N9" location="'DRV Tài xế'!A1"/>
+    <hyperlink ref="C10" location="'FLT Quản lý đội xe'!A1"/>
+    <hyperlink ref="N10" location="'FLT Quản lý đội xe'!A1"/>
+    <hyperlink ref="C11" location="'STN Mạng lưới trạm sạc'!A1"/>
+    <hyperlink ref="N11" location="'STN Mạng lưới trạm sạc'!A1"/>
+    <hyperlink ref="C12" location="'CHG Phiên sạc'!A1"/>
+    <hyperlink ref="N12" location="'CHG Phiên sạc'!A1"/>
+    <hyperlink ref="C13" location="'POL Chính sách sạc &amp; bảo hành'!A1"/>
+    <hyperlink ref="N13" location="'POL Chính sách sạc &amp; bảo hành'!A1"/>
+    <hyperlink ref="C14" location="'PAY Gói, thanh toán &amp; hóa đơn'!A1"/>
+    <hyperlink ref="N14" location="'PAY Gói, thanh toán &amp; hóa đơn'!A1"/>
+    <hyperlink ref="C15" location="'NTF Thông báo'!A1"/>
+    <hyperlink ref="N15" location="'NTF Thông báo'!A1"/>
+    <hyperlink ref="C16" location="'SUP CSKH &amp; cứu hộ'!A1"/>
+    <hyperlink ref="N16" location="'SUP CSKH &amp; cứu hộ'!A1"/>
+    <hyperlink ref="C17" location="'MNT Bảo dưỡng &amp; tài sản'!A1"/>
+    <hyperlink ref="N17" location="'MNT Bảo dưỡng &amp; tài sản'!A1"/>
+    <hyperlink ref="C18" location="'SAF An toàn lái xe &amp; camera'!A1"/>
+    <hyperlink ref="N18" location="'SAF An toàn lái xe &amp; camera'!A1"/>
+    <hyperlink ref="C19" location="'CRB Carbon &amp; chuyển đổi xanh'!A1"/>
+    <hyperlink ref="N19" location="'CRB Carbon &amp; chuyển đổi xanh'!A1"/>
+    <hyperlink ref="C20" location="'PLT Nền tảng, dữ liệu, tuân thủ'!A1"/>
+    <hyperlink ref="N20" location="'PLT Nền tảng, dữ liệu, tuân thủ'!A1"/>
+    <hyperlink ref="C21" location="'TMS Tích hợp TMS (Phase 2)'!A1"/>
+    <hyperlink ref="N21" location="'TMS Tích hợp TMS (Phase 2)'!A1"/>
+    <hyperlink ref="C23" location="'Phi chức năng'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="54" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>STN — Mạng lưới trạm sạc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="229.5" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Trạm và trụ sạc, trạng thái realtime qua OCPP, sự cố, bản đồ trạm, hàng đợi, đặt chỗ và phân tải.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tên tính năng</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Giá trị mang lại</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Người dùng</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Chức năng chi tiết</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Đợt</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Hình thức bán / Giá</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Portal web</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Phụ thuộc</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu liên quan</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Câu hỏi mở</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Mã cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>STN-01</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Danh mục trạm sạc</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Lưu từng trạm sạc: vị trí, khu vực, công suất, số trụ, chuẩn đầu sạc, giờ hoạt động, tình trạng bảo trì và hoạt động thực tế, đơn vị quản lý và đầu mối xử lý sự cố.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Nền tảng cho bản đồ trạm, cảnh báo và báo cáo sản lượng.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>• Tạo, sửa, tìm kiếm và ngừng hoạt động trạm
+• Đơn vị quản lý và đầu mối sự cố của từng trạm
+• Xem mọi trạm trên bản đồ</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-C1, Bảng dữ liệu IN-25</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>F-C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>STN-02</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Cấu trúc trụ &amp; súng sạc</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Mô tả các trụ và súng sạc của từng trạm: mã định danh mà trụ dùng, công suất và chuẩn đầu sạc của từng súng.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Mọi trạng thái và phiên sạc từ trụ đều ghi đúng súng sạc.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>• Khai báo trụ và súng trước khi kết nối
+• Công suất và chuẩn đầu sạc theo từng súng</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>STN-01</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Quyết định CS-02, Quyết định CS-03, deferred.md 80</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="67.5" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>STN-03</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Kết nối trụ sạc (OCPP)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Kết nối trụ sạc qua OCPP 1.6J và 2.0.1: khởi động, heartbeat, trạng thái, giao dịch và chỉ số công tơ, lưu lại mọi bản tin.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Làm việc được với mọi hãng trụ sạc theo chuẩn, bắt đầu với Willdigits.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>• Cả hai phiên bản giao thức trên một cổng kết nối
+• Thông tin trụ, firmware và cấu hình được ghi lại sau mỗi lần khởi động
+• Nhật ký bản tin nguyên văn, chỉ ghi thêm
+• Cờ online từ bản tin gần nhất</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>STN-02</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>• Còn thiếu tài liệu từ nhà cung cấp: hướng dẫn tích hợp, bảng mã lỗi, thông tin công tơ, TLS/xác thực (câu hỏi mở 4).
+• Các lần mua trụ sau yêu cầu OCPP 2.0.1 hay chỉ cần 1.6J?</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-G2, Quyết định CO-01, Quyết định CO-02, Quyết định CO-05</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>F-G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40.5" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>STN-04</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Trạng thái súng sạc realtime</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Trạng thái trống, đang sạc hay lỗi và công suất khả dụng của mọi súng sạc trên toàn mạng, cập nhật trong vòng 30 giây.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế chỉ tới những trạm có thể phục vụ mình.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành, Tài xế, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>• Trạng thái theo đúng trụ báo, kèm chi tiết lỗi
+• Trạng thái cả trụ và từng súng trong một màn hình
+• Đánh dấu không rõ trạng thái khi trụ mất kết nối</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Có trong mọi gói</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>STN-03</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-C2, Bảng dữ liệu IN-26, Bảng dữ liệu OUT-48, NF-02, deferred.md 76</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>F-C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>STN-05</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Cảnh báo trụ sạc lỗi</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Cảnh báo trụ lỗi, mất kết nối hoặc công suất bất thường, kèm đơn vị quản lý và đầu mối xử lý sự cố của trạm.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sự cố được xử lý nhanh và gọi đúng người.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>• Cảnh báo khi lỗi, mất kết nối và công suất bất thường
+• Dịch mã lỗi của hãng thành nguyên nhân dễ hiểu
+• Chuyển cảnh báo tới đầu mối của trạm</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>STN-04, NTF-01</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu OUT-49, Quyết định CS-08, deferred.md 75</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>STN-06</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Bản đồ &amp; tìm trạm sạc</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Tìm trạm gần nhất trên bản đồ, lọc theo tình trạng trống, công suất và chuẩn đầu sạc.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế nhanh chóng tìm được trụ trống.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế, Điều vận</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>• Các trạm gần nhất trong bán kính
+• Bộ lọc: đang trống, công suất tối thiểu, chuẩn đầu sạc
+• Số súng trống và giá hiện tại của từng trạm</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Có trong mọi gói</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>STN-04</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-D1, Bảng dữ liệu OUT-5</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>F-D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>STN-07</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Hàng đợi &amp; thời gian chờ tại trạm</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Hiển thị số xe đang chờ, số xe dự kiến đến trong 60 phút và thời gian chờ dự kiến tới khi có súng trống; cảnh báo khi chờ quá lâu.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế tránh xếp hàng và kịp điều chỉnh kế hoạch.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>• Số xe đang chờ và đang tới của từng trạm
+• Thời gian chờ ước tính từ thời lượng phiên (trung vị/p90 theo súng, công suất và khung giờ)
+• Cảnh báo khi vượt ngưỡng, kèm trạm thay thế</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>STN-04, MON-02, CHG-02</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-C3, Bảng dữ liệu IN-28, Bảng dữ liệu IN-29, Bảng dữ liệu OUT-6</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>F-C3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>STN-08</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Dự báo tải trạm &amp; phân tải</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Dự báo số xe sẽ đến mỗi trạm so với số súng trống, cảnh báo tài xế đang hướng tới trạm sắp quá tải trong 60 phút và đề xuất ít nhất một trạm thay thế trong tầm pin.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Phân bổ nhu cầu trên toàn mạng; giảm thời gian chờ, tăng hiệu suất trụ.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế, Vận hành, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>• Dự báo xe đến từ vị trí, mức pin, hướng đi và lịch sử
+• Tỷ lệ lấp đầy theo trụ; khuyến nghị cho vận hành
+• Cảnh báo tài xế kèm trạm thay thế</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>STN-07, RTE-01</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-C7, Bảng dữ liệu IN-28, Bảng dữ liệu OUT-53, NF-20</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>F-C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40.5" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>STN-09</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Đặt chỗ sạc</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Đặt trước một súng sạc theo khung giờ và hủy đặt; áp dụng phạt khi không đến.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Đảm bảo được sạc cho những chuyến cần đúng giờ.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế, Điều vận</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>• Đặt và hủy chỗ dựa trên thời gian chờ dự kiến
+• Giữ súng trên trụ trong khung giờ đã đặt
+• Mức phạt không đến cấu hình được</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Có thì tốt</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>P1.5</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>STN-07, STN-10, PAY-06</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>• Mức phạt khi không đến là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-C4, Bảng dữ liệu IN-54</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>F-C4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40.5" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>STN-10</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Điều khiển trụ sạc từ xa</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Gửi lệnh tới trụ sạc: bắt đầu và dừng sạc, mở khóa đầu sạc, khởi động lại, đổi cấu hình, lấy dữ liệu chẩn đoán.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Cần để bắt đầu sạc từ app và xử lý trụ mà không phải ra trạm.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>• Bắt đầu và dừng sạc từ xa
+• Mở khóa, khởi động lại, đổi cấu hình, chẩn đoán
+• Mọi lệnh và phản hồi đều được ghi lại</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>STN-03</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Quyết định CO-12, deferred.md 74</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>STN-11</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Kết nối trụ sạc an toàn</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Mã hóa kết nối trụ sạc và xác thực từng trụ trước khi triển khai thật.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Không trụ giả mạo nào báo phiên sạc hoặc nhận lệnh được.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>• Kết nối mã hóa (wss://)
+• Mật khẩu hoặc chứng chỉ riêng cho từng trụ</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>STN-03</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>NF-05, Quyết định IS-05, deferred.md 73</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="n"/>
+    </row>
+    <row r="16" ht="40.5" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>STN-12</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Trạm sạc riêng</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Trạm không công cộng (ví dụ tại mỏ hoặc bãi của khách hàng) chỉ hiển thị và dùng được cho các tổ chức được phép, với cách tính giá riêng.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Phục vụ khách hàng sở hữu hoặc đặt trụ sạc riêng mà không mở cho mọi người.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành, Kinh doanh</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>• Trạm công cộng hay riêng; danh sách tổ chức được phép
+• Biểu giá riêng cho trạm riêng</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>STN-01, PAY-09</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>• Trụ riêng (của mỏ, không công cộng) tính tiền thế nào? Bảng dữ liệu ghi 'phương án riêng'.</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu OUT-10</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="40.5" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>STN-13</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Dữ liệu nguồn phát xanh &amp; BESS</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Ghi nhận các nguồn điện của từng trạm (lưới, mặt trời, gió, sinh khối, pin lưu trữ BESS), sản lượng theo giờ, mức pin BESS và dự báo.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Làm căn cứ cho giá điện xanh, nhãn sạc xanh và báo cáo carbon.</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>• Nguồn phát theo trạm
+• Sản lượng theo giờ, mức pin BESS, dự báo sản lượng</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>STN-01</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu IN-31</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="40.5" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>STN-14</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Sản lượng điện theo trạm</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>kWh bán ra theo trạm và theo khung giờ, phục vụ tối ưu giá theo giờ.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Cho biết trạm nào, giờ nào mang lại doanh thu, để định giá.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành, Quản trị trưởng (nội bộ)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>• Tổng kWh và số phiên theo trạm trong kỳ
+• Chuỗi số liệu theo giờ và theo ngày
+• Xếp hạng toàn bộ trạm</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>CHG-02</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-C5, Bảng dữ liệu OUT-50, deferred.md 77</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>F-C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40.5" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>STN-15</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Xem nhật ký bản tin trụ sạc</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Cho vận hành đọc bản tin gốc của trụ để xử lý sự cố, che mã thẻ, và xóa bản tin cũ sau thời hạn lưu.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Chẩn đoán sự cố trụ mà không cần truy cập cơ sở dữ liệu.</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>• Đọc bản tin theo trụ và thời gian
+• Che mã thẻ và dữ liệu cá nhân khác
+• Thời hạn lưu bản tin gốc</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Có thì tốt</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>P1.1</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>STN-03</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Quyết định IS-07, deferred.md 79</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2773,7 +4167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3402,7 +4796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4587,7 +5981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5348,7 +6742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6053,7 +7447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6643,7 +8037,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>VEH-01, VEH-04</t>
+          <t>VEH-01, BAT-01</t>
         </is>
       </c>
       <c r="N10" s="3" t="n"/>
@@ -6965,7 +8359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7820,7 +9214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8788,7 +10182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9452,601 +10846,6 @@
         </is>
       </c>
       <c r="Q11" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="94.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TMS — Tích hợp quản lý vận tải (Phase 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="297" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Đơn hàng, chủ hàng và depot, làm ở Phase 2 bằng cách tích hợp với hệ thống quản lý vận tải (TMS) của khách hàng, không thay thế TMS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Tên tính năng</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Giá trị mang lại</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Người dùng</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Chức năng chi tiết</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Đợt</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Hình thức bán / Giá</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Portal web</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Phụ thuộc</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu liên quan</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Câu hỏi mở</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Nguồn</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Mã cũ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>TMS-01</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Đơn hàng &amp; chủ hàng</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Chủ hàng, đơn hàng và chuyến hàng, liên kết chuyến ↔ xe ↔ tài xế ↔ đơn hàng ↔ chủ hàng.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Biết xe đang chạy đơn hàng nào cho khách hàng nào.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Điều vận, Quản lý đội xe</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>• Dữ liệu đơn hàng nhận từ TMS của khách hàng
-• Gắn đơn hàng với chuyến qua các khóa dành sẵn</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Có thì tốt</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>MON-11, PLT-01</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>Phase 2 T1, Điều kiện tiên quyết 6</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>TMS-02</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Tích hợp TMS &amp; mốc tác nghiệp chuyến</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>API và webhook hai chiều với TMS; sự kiện vùng địa lý cho các mốc tác nghiệp (lấy container rỗng, đến/rời nhà máy, đến cảng).</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Chủ hàng nhận các mốc tự động; app G3 tích hợp TMS chứ không thay thế TMS.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Hệ thống bên ngoài, Điều vận</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>• Webhook cho vị trí và các mốc
-• Chủ hàng truy vấn GPS qua API</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Có thì tốt</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>TMS-01, FLT-05, ACC-21</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>Phase 2 T2, Điều kiện tiên quyết 6</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>TMS-03</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Danh mục depot</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Danh mục điểm dịch vụ dùng chung cho điều phối: depot cắt kéo container, depot hãng tàu và depot ảo kèm tọa độ, dịch vụ và giờ hoạt động.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Điều vận lập kế hoạch kéo container quanh các depot đã biết.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Điều vận, Vận hành</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>• Điểm depot kèm dịch vụ và giờ hoạt động</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Có thì tốt</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>Phase 2 T3</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="40.5" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>TMS-04</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Truy vết carbon tới chủ hàng (Scope 3)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Phân bổ phát thải theo chuỗi chủ hàng → đơn hàng → chuyến → xe → kWh, và báo cáo cường độ theo chủ hàng (gCO₂e/tấn-km) cho Scope 3 của họ.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Chuyển Scope 1 &amp; 2 của doanh nghiệp vận tải thành Scope 3 của khách hàng.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Quản lý đội xe, Hệ thống bên ngoài</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>• Phân bổ phát thải theo đơn hàng
-• Báo cáo Scope 3 sẵn sàng kiểm toán theo chủ hàng</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Có thì tốt</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>TMS-01, CRB-08</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>Phase 2 T4, Phase 2 T6</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="40.5" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>TMS-05</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Chứng thư giảm phát thải cho chủ hàng</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Chứng thư PDF có mã tra cứu xác nhận lượng CO₂ của các chuyến hàng đã thực hiện, gửi chủ hàng qua API.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Lợi thế bán hàng của doanh nghiệp vận tải với chủ hàng.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Quản lý đội xe, Hệ thống bên ngoài</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>• Chứng thư theo kỳ và theo chủ hàng
-• Tra cứu công khai bằng mã</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Có thì tốt</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>TMS-04</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>Phase 2 T5, Phase 2 T7</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>TMS-06</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Báo cáo tác nghiệp của tài xế về điều hành</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế gửi báo cáo tác nghiệp về đơn vị điều hành để TMS tối ưu điều phối.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Điều phối tốt hơn nhờ thông tin trực tiếp từ hiện trường.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Điều vận</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>• Biểu mẫu báo cáo trên app tài xế
-• Chuyển tiếp sang TMS</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Có thì tốt</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>TMS-02</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>Phase 2 T8</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11911,6 +12710,601 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="94.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TMS — Tích hợp quản lý vận tải (Phase 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="297" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Đơn hàng, chủ hàng và depot, làm ở Phase 2 bằng cách tích hợp với hệ thống quản lý vận tải (TMS) của khách hàng, không thay thế TMS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tên tính năng</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Giá trị mang lại</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Người dùng</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Chức năng chi tiết</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Đợt</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Hình thức bán / Giá</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Portal web</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Phụ thuộc</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu liên quan</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Câu hỏi mở</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Mã cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>TMS-01</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Đơn hàng &amp; chủ hàng</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Chủ hàng, đơn hàng và chuyến hàng, liên kết chuyến ↔ xe ↔ tài xế ↔ đơn hàng ↔ chủ hàng.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Biết xe đang chạy đơn hàng nào cho khách hàng nào.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Điều vận, Quản lý đội xe</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>• Dữ liệu đơn hàng nhận từ TMS của khách hàng
+• Gắn đơn hàng với chuyến qua các khóa dành sẵn</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Có thì tốt</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>MON-11, PLT-01</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 T1, Điều kiện tiên quyết 6</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>TMS-02</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Tích hợp TMS &amp; mốc tác nghiệp chuyến</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>API và webhook hai chiều với TMS; sự kiện vùng địa lý cho các mốc tác nghiệp (lấy container rỗng, đến/rời nhà máy, đến cảng).</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Chủ hàng nhận các mốc tự động; app G3 tích hợp TMS chứ không thay thế TMS.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Hệ thống bên ngoài, Điều vận</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>• Webhook cho vị trí và các mốc
+• Chủ hàng truy vấn GPS qua API</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Có thì tốt</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>TMS-01, FLT-05, ACC-21</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 T2, Điều kiện tiên quyết 6</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>TMS-03</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Danh mục depot</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Danh mục điểm dịch vụ dùng chung cho điều phối: depot cắt kéo container, depot hãng tàu và depot ảo kèm tọa độ, dịch vụ và giờ hoạt động.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Điều vận lập kế hoạch kéo container quanh các depot đã biết.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Điều vận, Vận hành</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>• Điểm depot kèm dịch vụ và giờ hoạt động</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Có thì tốt</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 T3</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="40.5" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TMS-04</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Truy vết carbon tới chủ hàng (Scope 3)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Phân bổ phát thải theo chuỗi chủ hàng → đơn hàng → chuyến → xe → kWh, và báo cáo cường độ theo chủ hàng (gCO₂e/tấn-km) cho Scope 3 của họ.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Chuyển Scope 1 &amp; 2 của doanh nghiệp vận tải thành Scope 3 của khách hàng.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe, Hệ thống bên ngoài</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>• Phân bổ phát thải theo đơn hàng
+• Báo cáo Scope 3 sẵn sàng kiểm toán theo chủ hàng</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Có thì tốt</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>TMS-01, CRB-08</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 T4, Phase 2 T6</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="40.5" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>TMS-05</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Chứng thư giảm phát thải cho chủ hàng</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Chứng thư PDF có mã tra cứu xác nhận lượng CO₂ của các chuyến hàng đã thực hiện, gửi chủ hàng qua API.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Lợi thế bán hàng của doanh nghiệp vận tải với chủ hàng.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe, Hệ thống bên ngoài</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>• Chứng thư theo kỳ và theo chủ hàng
+• Tra cứu công khai bằng mã</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Có thì tốt</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>TMS-04</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 T5, Phase 2 T7</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>TMS-06</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Báo cáo tác nghiệp của tài xế về điều hành</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế gửi báo cáo tác nghiệp về đơn vị điều hành để TMS tối ưu điều phối.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Điều phối tốt hơn nhờ thông tin trực tiếp từ hiện trường.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế, Điều vận</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>• Biểu mẫu báo cáo trên app tài xế
+• Chuyển tiếp sang TMS</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Có thì tốt</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>TMS-02</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 T8</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12570,7 +13964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12599,10 +13993,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="175.5" customHeight="1">
+    <row r="2" ht="135" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Hồ sơ xe, chủ sở hữu, dòng xe, thông tin pin và kích hoạt xe khi bàn giao.</t>
+          <t>Hồ sơ xe, chủ sở hữu, dòng xe và kích hoạt xe khi bàn giao.</t>
         </is>
       </c>
     </row>
@@ -12932,37 +14326,36 @@
       </c>
       <c r="Q7" s="3" t="n"/>
     </row>
-    <row r="8" ht="67.5" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>VEH-04</t>
+          <t>VEH-05</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Hồ sơ pin</t>
+          <t>Kích hoạt xe</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Quản lý từng pin xe như một tài sản: dòng pin, chủ sở hữu và các xe pin đã được lắp.</t>
+          <t>Theo dõi từng xe từ khi đăng ký, gắn thiết bị tới khi nhận dữ liệu đầu tiên, và báo cáo tỷ lệ kích hoạt thành công.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Pin chiếm tới hai phần ba giá xe; sức khỏe, bảo hành và giá trị của pin đi theo pin từ xe này sang xe khác.</t>
+          <t>Không xe nào rời bàn giao khi chưa có dữ liệu; mục tiêu kích hoạt thành công ≥98%.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Vận hành, Bảo trì, Bảo hành</t>
+          <t>Vận hành, Hệ thống (tự động)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>• Danh mục dòng pin: hóa học (LFP/CATL), dung lượng thiết kế, điện áp, cấu trúc
-• Từng pin: số serial, dòng pin, chủ sở hữu (có thể khác chủ xe), trạng thái kèm lý do
-• Mỗi xe một pin; lịch sử pin đã được lắp trên xe nào</t>
+          <t>• Kích hoạt được tính từ thiết bị đang lắp và dữ liệu đã nhận, nên xe bị tháo T-Box sẽ hiện đúng như vậy
+• Tỷ lệ kích hoạt thành công và danh sách xe còn đang chờ</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -12997,174 +14390,98 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>VEH-01</t>
+          <t>VEH-01, DEV-02</t>
         </is>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-33, Quyết định VH-08, deferred.md 87, deferred.md 88</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="n"/>
+          <t>PRD F-F2, Quyết định VH-06</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>F-F2</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>VEH-05</t>
+          <t>VEH-06</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Kích hoạt xe</t>
+          <t>Bảng mã lỗi</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Theo dõi từng xe từ khi đăng ký, gắn thiết bị tới khi nhận dữ liệu đầu tiên, và báo cáo tỷ lệ kích hoạt thành công.</t>
+          <t>Bảng mã lỗi (DTC) của nhà sản xuất: mô tả, mức nghiêm trọng, xe có tiếp tục chạy được không và hướng xử lý.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Không xe nào rời bàn giao khi chưa có dữ liệu; mục tiêu kích hoạt thành công ≥98%.</t>
+          <t>Biến mã lỗi thô thành cảnh báo và hướng dẫn rõ ràng cho tài xế và CSKH.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Vận hành, Hệ thống (tự động)</t>
+          <t>Vận hành, CSKH, Bảo hành</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>• Kích hoạt được tính từ thiết bị đang lắp và dữ liệu đã nhận, nên xe bị tháo T-Box sẽ hiện đúng như vậy
-• Tỷ lệ kích hoạt thành công và danh sách xe còn đang chờ</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>VEH-01, DEV-02</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-F2, Quyết định VH-06</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>F-F2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>VEH-06</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Bảng mã lỗi</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Bảng mã lỗi (DTC) của nhà sản xuất: mô tả, mức nghiêm trọng, xe có tiếp tục chạy được không và hướng xử lý.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Biến mã lỗi thô thành cảnh báo và hướng dẫn rõ ràng cho tài xế và CSKH.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành, CSKH, Bảo hành</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>• Nhập và quản lý phiên bản bảng DTC của nhà sản xuất
 • Mức nghiêm trọng, kết luận xe chạy tiếp được không và hướng xử lý theo từng mã
 • Danh sách chuẩn trạng thái motor</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Bắt buộc</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>P1.0</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Chỉ nội bộ (không bán)</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>Không cần</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>• Nhà sản xuất phải cung cấp bằng văn bản bảng DTC kèm mức nghiêm trọng (điều kiện tiên quyết 1).</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>Bảng dữ liệu IN-16, Bảng dữ liệu IN-34, Điều kiện tiên quyết 1, deferred.md 42</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13175,6 +14492,227 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BAT — Pin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="202.5" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Quản lý từng pin xe như một tài sản riêng: dòng pin, chủ sở hữu và các xe pin đã được lắp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tên tính năng</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Giá trị mang lại</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Người dùng</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Chức năng chi tiết</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Đợt</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Hình thức bán / Giá</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Portal web</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Phụ thuộc</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu liên quan</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Câu hỏi mở</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Mã cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="67.5" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>BAT-01</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Hồ sơ pin</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý từng pin xe như một tài sản: dòng pin, chủ sở hữu và các xe pin đã được lắp.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Pin chiếm tới hai phần ba giá xe; sức khỏe, bảo hành và giá trị của pin đi theo pin từ xe này sang xe khác.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành, Bảo trì, Bảo hành</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>• Danh mục dòng pin: hóa học (LFP/CATL), dung lượng thiết kế, điện áp, cấu trúc
+• Từng pin: số serial, dòng pin, chủ sở hữu (có thể khác chủ xe), trạng thái kèm lý do
+• Mỗi xe một pin; lịch sử pin đã được lắp trên xe nào</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>VEH-01</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu IN-33, Quyết định VH-08, Quyết định VH-13, deferred.md 87, deferred.md 88</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13959,7 +15497,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14737,7 +16275,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>MON-07, VEH-04</t>
+          <t>MON-07, BAT-01</t>
         </is>
       </c>
       <c r="N12" s="3" t="n"/>
@@ -15615,701 +17153,6 @@
         </is>
       </c>
       <c r="Q23" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="67.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RTE — Quãng đường &amp; lộ trình</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="256.5" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Xe còn đi được bao xa, bao lâu, có tới được đích không, nên sạc ở đâu và lúc nào, và những đoạn đường cấm tải.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Tên tính năng</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Giá trị mang lại</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Người dùng</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Chức năng chi tiết</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Đợt</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Hình thức bán / Giá</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Portal web</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Phụ thuộc</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu liên quan</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Câu hỏi mở</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Nguồn</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Mã cũ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="67.5" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>RTE-01</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Dự báo quãng đường &amp; thời gian còn lại</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Ước tính số km và số phút xe còn chạy được từ mức pin, tốc độ tiêu thụ tức thời, tải trọng, địa hình, nhiệt độ và cách lái, kèm khoảng tin cậy.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Thay thế cách ước tính tuyến tính theo % pin vốn sai lệch khi lên dốc và chở nặng.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>• Mô hình dự báo dùng tải trọng, cao độ (DEM), thời tiết và cách lái
-• Số km và số phút còn lại kèm khoảng tin cậy
-• Huấn luyện lại định kỳ trên dữ liệu tuyến thực (sai số ≤10% p50, ≤15% p90)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>MON-01, MON-13, RTE-07, VEH-03</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-A7, Bảng dữ liệu IN-2, Bảng dữ liệu IN-3, NF-20</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>F-A7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>RTE-02</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Kiểm tra đủ pin cho hành trình</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Cho tài xế biết với mức pin hiện tại xe có đi hết hành trình hoặc tới được trạm đã chọn không, và gợi ý các trạm trong tầm khi không đủ.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế lên kế hoạch dừng sạc trước khi quá muộn.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>• So sánh đích đến hoặc trạm với quãng đường dự báo
-• Gợi ý các trạm tới được</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>RTE-01, STN-06</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-D3, Bảng dữ liệu OUT-3</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>F-D3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>RTE-03</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ đường tới trạm</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ đường từng bước tới trạm đã chọn, ngay trong app hoặc chuyển sang Google Maps hay VietMap.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Một chạm từ cảnh báo tới chỉ đường.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>• Mở chỉ đường từ màn hình trạm và từ cảnh báo pin
-• Chuyển sang ứng dụng bản đồ bên ngoài</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Có trong mọi gói</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>STN-06</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-D2, Bảng dữ liệu OUT-5</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>F-D2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>RTE-04</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Cảnh báo đường cấm tải &amp; khung giờ cấm</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Cảnh báo tài xế trước khi vào đoạn đường cấm tải hoặc trong khung giờ cấm, đề xuất tuyến khác và ảnh hưởng tới các điểm dừng sạc.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Tránh bị phạt và chạy uổng công.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Điều vận</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>• Đường cấm tải và khung giờ cấm từ nhà cung cấp bản đồ
-• Cảnh báo trước đoạn cấm
-• Tuyến thay thế và ảnh hưởng tới việc sạc</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>P1.1</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>RTE-07, RTE-02</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>• Dữ liệu đường cấm tải – cấm giờ tại Việt Nam phải là tiêu chí bắt buộc khi chọn nhà cung cấp bản đồ (điều kiện tiên quyết 4).</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu OUT-7, Bảng dữ liệu IN-42, Điều kiện tiên quyết 4</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>RTE-05</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Gợi ý sạc tối ưu chi phí</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Gợi ý nên sạc ở đâu, lúc nào để chi phí thấp nhất mà vẫn đúng giờ, kèm số tiền tiết kiệm ước tính và rủi ro trễ; tài xế luôn có thể bỏ qua.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Dịch chuyển việc sạc sang giờ rẻ và giờ điện xanh, giúp khách hàng tiết kiệm.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Điều vận</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>• Kết hợp biểu giá, dự báo tải trạm, mức pin và dự báo tiêu thụ trên tuyến
-• Hiển thị tiền tiết kiệm và rủi ro trễ cho mỗi gợi ý</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>RTE-01, STN-08, PAY-09</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-D6, Bảng dữ liệu OUT-9, NF-20</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>F-D6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>RTE-06</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Báo cáo chất lượng mô hình dự báo</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Đo sai số dự báo: quãng đường (p50/p90), tải trạm và thời gian chờ, theo tuần.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Cho biết dự báo có đáng tin không và khi nào cần huấn luyện lại.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>• So sánh dự báo với thực tế
-• Độ chính xác theo tuần của từng mô hình</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>RTE-01, STN-07, STN-08</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu OUT-63, NF-20</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="n"/>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>RTE-07</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Dữ liệu bản đồ, địa hình &amp; thời tiết</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Kết nối dữ liệu bên thứ ba về bản đồ, chỉ đường, khoảng cách, giới hạn tốc độ, giao thông, cao độ và thời tiết.</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Dự báo, cảnh báo và chấm điểm an toàn cần bối cảnh con đường.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>• Tuyến đường, ETA, ma trận khoảng cách, giới hạn tốc độ, giao thông
-• Cao độ dọc tuyến
-• Nhiệt độ và thời tiết theo khu vực và theo tuyến</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu IN-42, Bảng dữ liệu IN-43, Bảng dữ liệu IN-44, Điều kiện tiên quyết 4</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16347,17 +17190,17 @@
     <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" customHeight="1">
+    <row r="1" ht="67.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DRV — Tài xế</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="175.5" customHeight="1">
+          <t>RTE — Quãng đường &amp; lộ trình</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="256.5" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Hồ sơ tài xế, phân công xe, ca làm việc, thời gian lái và báo cáo theo tài xế.</t>
+          <t>Xe còn đi được bao xa, bao lâu, có tới được đích không, nên sạc ở đâu và lúc nào, và những đoạn đường cấm tải.</t>
         </is>
       </c>
     </row>
@@ -16455,42 +17298,42 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1">
+    <row r="5" ht="67.5" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DRV-01</t>
+          <t>RTE-01</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Hồ sơ tài xế</t>
+          <t>Dự báo quãng đường &amp; thời gian còn lại</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Lưu thông tin của tài xế trong một tổ chức: số bằng lái, hạng, ngày hết hạn và trạng thái.</t>
+          <t>Ước tính số km và số phút xe còn chạy được từ mức pin, tốc độ tiêu thụ tức thời, tải trọng, địa hình, nhiệt độ và cách lái, kèm khoảng tin cậy.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Chỉ tài xế có bằng lái hợp lệ mới được giao xe.</t>
+          <t>Thay thế cách ước tính tuyến tính theo % pin vốn sai lệch khi lên dốc và chở nặng.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe, Quản trị tổ chức</t>
+          <t>Tài xế, Hệ thống (tự động)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>• Thêm, sửa, tìm kiếm và ngừng hoạt động tài xế
-• Nhắc bằng lái sắp hết hạn
-• Hồ sơ tài xế thuộc một thành viên tổ chức; tài xế đã nghỉ vẫn giữ lịch sử</t>
+          <t>• Mô hình dự báo dùng tải trọng, cao độ (DEM), thời tiết và cách lái
+• Số km và số phút còn lại kèm khoảng tin cậy
+• Huấn luyện lại định kỳ trên dữ liệu tuyến thực (sai số ≤10% p50, ≤15% p90)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Bắt buộc</t>
+          <t>Nên có</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -16510,71 +17353,67 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>Không cần</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>ACC-12</t>
+          <t>MON-01, MON-13, RTE-07, VEH-03</t>
         </is>
       </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E4, Bảng dữ liệu IN-37, Bảng dữ liệu OUT-34, Quyết định ID-13, Quyết định DR-03</t>
+          <t>PRD F-A7, Bảng dữ liệu IN-2, Bảng dữ liệu IN-3, NF-20</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>F-E4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="189" customHeight="1">
+          <t>F-A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DRV-02</t>
+          <t>RTE-02</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nhận xe</t>
+          <t>Kiểm tra đủ pin cho hành trình</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Tài xế nhận chiếc xe sắp lái bằng cách quét mã QR trên xe hoặc chọn xe trên ứng dụng; hệ thống luôn biết ai đang cầm lái và lưu toàn bộ lịch sử.</t>
+          <t>Cho tài xế biết với mức pin hiện tại xe có đi hết hành trình hoặc tới được trạm đã chọn không, và gợi ý các trạm trong tầm khi không đủ.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Trong vận tải chặng ngắn, tài xế và xe đổi nhau hằng ngày; mọi sự kiện của xe vẫn truy được tài xế tại thời điểm đó.</t>
+          <t>Tài xế lên kế hoạch dừng sạc trước khi quá muộn.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Tài xế, Quản lý đội xe, Điều vận, Hệ thống (tự động)</t>
+          <t>Tài xế</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>• Nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, bị từ chối khi điện thoại ở xa xe; quản lý có thể nhận xe giúp tài xế trên portal
-• Tài xế đang hoạt động nào cũng có thể lái xe của bất kỳ tổ chức nào; cảnh báo khi tài xế thuộc tổ chức khác
-• Mỗi xe một người cầm lái; phiên kết thúc khi trả xe, khi tài xế khác nhận xe, khi tài xế nhận xe khác, hoặc khi xe không di chuyển quá thời gian tự kết thúc của tổ chức (mặc định 2 giờ)
-• Cảnh báo lên portal khi xe chạy mà không ai nhận xe
-• Cảnh báo dành cho tài xế gửi tới tài xế đang nhận xe và portal
-• Lịch sử theo tài xế và theo xe</t>
+          <t>• So sánh đích đến hoặc trạm với quãng đường dự báo
+• Gợi ý các trạm tới được</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Bắt buộc</t>
+          <t>Nên có</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -16599,154 +17438,155 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Không cần</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>DRV-01, VEH-01</t>
+          <t>RTE-01, STN-06</t>
         </is>
       </c>
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-07, Quyết định DR-08, Quyết định NT-07, Quyết định ID-45</t>
+          <t>PRD F-D3, Bảng dữ liệu OUT-3</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>F-E4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="27" customHeight="1">
+          <t>F-D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40.5" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DRV-03</t>
+          <t>RTE-03</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Lịch làm việc của tài xế</t>
+          <t>Chỉ đường tới trạm</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Lập lịch ngày làm việc và ca của tài xế.</t>
+          <t>Chỉ đường từng bước tới trạm đã chọn, ngay trong app hoặc chuyển sang Google Maps hay VietMap.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Điều vận biết ai đang sẵn sàng và bố trí nghỉ ngơi hợp lý.</t>
+          <t>Một chạm từ cảnh báo tới chỉ đường.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Điều vận, Quản lý đội xe, Tài xế</t>
+          <t>Tài xế</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>• Lập ca theo tài xế và theo xe
-• Tài xế xem lịch của mình trên app</t>
+          <t>• Mở chỉ đường từ màn hình trạm và từ cảnh báo pin
+• Chuyển sang ứng dụng bản đồ bên ngoài</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Có trong mọi gói</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>STN-06</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-D2, Bảng dữ liệu OUT-5</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>F-D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>RTE-04</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Cảnh báo đường cấm tải &amp; khung giờ cấm</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Cảnh báo tài xế trước khi vào đoạn đường cấm tải hoặc trong khung giờ cấm, đề xuất tuyến khác và ảnh hưởng tới các điểm dừng sạc.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Tránh bị phạt và chạy uổng công.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế, Điều vận</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>• Đường cấm tải và khung giờ cấm từ nhà cung cấp bản đồ
+• Cảnh báo trước đoạn cấm
+• Tuyến thay thế và ảnh hưởng tới việc sạc</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
           <t>Nên có</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>P1.1</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Chưa định giá</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>DRV-02</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>• Phạm vi lịch làm việc cần làm rõ (Hùng Võ).</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu IN-55</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="40.5" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>DRV-04</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Định danh tài xế theo ca</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Ghi nhận ai thực sự lái xe trong từng ca, bằng khuôn mặt, thẻ hoặc đăng nhập app, kèm thời điểm bắt đầu và kết thúc ca.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Hồ sơ thời gian lái đúng luật và báo cáo theo tài xế công bằng.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>• Bắt đầu và kết thúc ca bằng khuôn mặt, thẻ hoặc app
-• Cảnh báo khi người lái không phải tài xế được phân công</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Chưa làm</t>
@@ -16764,58 +17604,57 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>DRV-02, SAF-03</t>
+          <t>RTE-07, RTE-02</t>
         </is>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>• Hai tài xế một xe: dùng một app hay hai app?</t>
+          <t>• Dữ liệu đường cấm tải – cấm giờ tại Việt Nam phải là tiêu chí bắt buộc khi chọn nhà cung cấp bản đồ (điều kiện tiên quyết 4).</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-58</t>
+          <t>Bảng dữ liệu OUT-7, Bảng dữ liệu IN-42, Điều kiện tiên quyết 4</t>
         </is>
       </c>
       <c r="Q8" s="3" t="n"/>
     </row>
-    <row r="9" ht="40.5" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DRV-05</t>
+          <t>RTE-05</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Cảnh báo thời gian lái liên tục</t>
+          <t>Gợi ý sạc tối ưu chi phí</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Nhắc tài xế trước khi chạm ngưỡng 4 giờ lái liên tục hoặc 10 giờ/ngày, và gợi ý điểm dừng nghỉ, ưu tiên trạm sạc trên tuyến.</t>
+          <t>Gợi ý nên sạc ở đâu, lúc nào để chi phí thấp nhất mà vẫn đúng giờ, kèm số tiền tiết kiệm ước tính và rủi ro trễ; tài xế luôn có thể bỏ qua.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Tài xế an toàn hơn và tuân thủ luật về thời gian lái; thời gian nghỉ kết hợp sạc.</t>
+          <t>Dịch chuyển việc sạc sang giờ rẻ và giờ điện xanh, giúp khách hàng tiết kiệm.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Tài xế, Hệ thống (tự động)</t>
+          <t>Tài xế, Điều vận</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>• Thời gian lái liên tục và trong ngày của từng tài xế
-• Cảnh báo trước mỗi ngưỡng
-• Gợi ý điểm dừng nghỉ ưu tiên trạm sạc</t>
+          <t>• Kết hợp biểu giá, dự báo tải trạm, mức pin và dự báo tiêu thụ trên tuyến
+• Hiển thị tiền tiết kiệm và rủi ro trễ cho mỗi gợi ý</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Bắt buộc</t>
+          <t>Nên có</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -16845,53 +17684,57 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>DRV-04, MON-12, STN-06</t>
+          <t>RTE-01, STN-08, PAY-09</t>
         </is>
       </c>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-59, Bảng dữ liệu OUT-19</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="40.5" customHeight="1">
+          <t>PRD F-D6, Bảng dữ liệu OUT-9, NF-20</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>F-D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>DRV-06</t>
+          <t>RTE-06</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Báo cáo tuân thủ thời gian lái &amp; nghỉ</t>
+          <t>Báo cáo chất lượng mô hình dự báo</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Theo từng tài xế: số ca vượt 4 giờ liên tục, 10 giờ/ngày và 48 giờ/tuần.</t>
+          <t>Đo sai số dự báo: quãng đường (p50/p90), tải trạm và thời gian chờ, theo tuần.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe chứng minh tuân thủ và phát hiện tài xế làm việc quá sức.</t>
+          <t>Cho biết dự báo có đáng tin không và khi nào cần huấn luyện lại.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe</t>
+          <t>Vận hành</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>• Số lần vượt theo tài xế và kỳ báo cáo
-• Xuất báo cáo phục vụ thanh tra</t>
+          <t>• So sánh dự báo với thực tế
+• Độ chính xác theo tuần của từng mô hình</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Bắt buộc</t>
+          <t>Nên có</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -16901,7 +17744,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Chưa định giá</t>
+          <t>Chỉ nội bộ (không bán)</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -16921,49 +17764,49 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>DRV-05</t>
+          <t>RTE-01, STN-07, STN-08</t>
         </is>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu OUT-39</t>
+          <t>Bảng dữ liệu OUT-63, NF-20</t>
         </is>
       </c>
       <c r="Q10" s="3" t="n"/>
     </row>
-    <row r="11" ht="67.5" customHeight="1">
+    <row r="11" ht="54" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DRV-07</t>
+          <t>RTE-07</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Báo cáo hiệu quả sạc theo tài xế</t>
+          <t>Dữ liệu bản đồ, địa hình &amp; thời tiết</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Theo tài xế: tỷ lệ kWh sạc giờ thấp điểm hoặc giờ điện tái tạo, chi phí điện/km, tiền tiết kiệm so với sạc giờ cao điểm và xếp hạng trong đội; có khung nhìn của quản lý và của chính tài xế.</t>
+          <t>Kết nối dữ liệu bên thứ ba về bản đồ, chỉ đường, khoảng cách, giới hạn tốc độ, giao thông, cao độ và thời tiết.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Khuyến khích thói quen sạc rẻ và xanh.</t>
+          <t>Dự báo, cảnh báo và chấm điểm an toàn cần bối cảnh con đường.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe, Tài xế</t>
+          <t>Hệ thống (tự động)</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>• Báo cáo theo tuần và tháng cho từng tài xế
-• Xếp hạng trong đội xe
-• Xuất CSV/PDF</t>
+          <t>• Tuyến đường, ETA, ma trận khoảng cách, giới hạn tốc độ, giao thông
+• Cao độ dọc tuyến
+• Nhiệt độ và thời tiết theo khu vực và theo tuyến</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -16978,7 +17821,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Chưa định giá</t>
+          <t>Chỉ nội bộ (không bán)</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -16988,35 +17831,23 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Không cần</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>CHG-07, PAY-09, DRV-02</t>
-        </is>
-      </c>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n"/>
       <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>• Báo cáo có gắn với chương trình thưởng hay thi đua không, hay chỉ để tham khảo?</t>
-        </is>
-      </c>
+      <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>PRD F-A8, Bảng dữ liệu OUT-32</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>F-A8</t>
-        </is>
-      </c>
+          <t>Bảng dữ liệu IN-42, Bảng dữ liệu IN-43, Bảng dữ liệu IN-44, Điều kiện tiên quyết 4</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -17027,6 +17858,713 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DRV — Tài xế</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="175.5" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Hồ sơ tài xế, phân công xe, ca làm việc, thời gian lái và báo cáo theo tài xế.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tên tính năng</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Giá trị mang lại</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Người dùng</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Chức năng chi tiết</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Đợt</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Hình thức bán / Giá</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Portal web</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Phụ thuộc</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu liên quan</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Câu hỏi mở</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Mã cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>DRV-01</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Hồ sơ tài xế</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Lưu thông tin của tài xế trong một tổ chức: số bằng lái, hạng, ngày hết hạn và trạng thái.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ tài xế có bằng lái hợp lệ mới được giao xe.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe, Quản trị tổ chức</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>• Thêm, sửa, tìm kiếm và ngừng hoạt động tài xế
+• Nhắc bằng lái sắp hết hạn
+• Hồ sơ tài xế thuộc một thành viên tổ chức; tài xế đã nghỉ vẫn giữ lịch sử</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>ACC-12</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-E4, Bảng dữ liệu IN-37, Bảng dữ liệu OUT-34, Quyết định ID-13, Quyết định DR-03</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>F-E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="189" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>DRV-02</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Nhận xe</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế nhận chiếc xe sắp lái bằng cách quét mã QR trên xe hoặc chọn xe trên ứng dụng; hệ thống luôn biết ai đang cầm lái và lưu toàn bộ lịch sử.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Trong vận tải chặng ngắn, tài xế và xe đổi nhau hằng ngày; mọi sự kiện của xe vẫn truy được tài xế tại thời điểm đó.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế, Quản lý đội xe, Điều vận, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>• Nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, bị từ chối khi điện thoại ở xa xe; quản lý có thể nhận xe giúp tài xế trên portal
+• Tài xế đang hoạt động nào cũng có thể lái xe của bất kỳ tổ chức nào; cảnh báo khi tài xế thuộc tổ chức khác
+• Mỗi xe một người cầm lái; phiên kết thúc khi trả xe, khi tài xế khác nhận xe, khi tài xế nhận xe khác, hoặc khi xe không di chuyển quá thời gian tự kết thúc của tổ chức (mặc định 2 giờ)
+• Cảnh báo lên portal khi xe chạy mà không ai nhận xe
+• Cảnh báo dành cho tài xế gửi tới tài xế đang nhận xe và portal
+• Lịch sử theo tài xế và theo xe</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>DRV-01, VEH-01</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-07, Quyết định DR-08, Quyết định NT-07, Quyết định ID-45</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>F-E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>DRV-03</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Lịch làm việc của tài xế</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Lập lịch ngày làm việc và ca của tài xế.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Điều vận biết ai đang sẵn sàng và bố trí nghỉ ngơi hợp lý.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Điều vận, Quản lý đội xe, Tài xế</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>• Lập ca theo tài xế và theo xe
+• Tài xế xem lịch của mình trên app</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>DRV-02</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>• Phạm vi lịch làm việc cần làm rõ (Hùng Võ).</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu IN-55</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="40.5" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>DRV-04</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Định danh tài xế theo ca</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Ghi nhận ai thực sự lái xe trong từng ca, bằng khuôn mặt, thẻ hoặc đăng nhập app, kèm thời điểm bắt đầu và kết thúc ca.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Hồ sơ thời gian lái đúng luật và báo cáo theo tài xế công bằng.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>• Bắt đầu và kết thúc ca bằng khuôn mặt, thẻ hoặc app
+• Cảnh báo khi người lái không phải tài xế được phân công</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>DRV-02, SAF-03</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>• Hai tài xế một xe: dùng một app hay hai app?</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu IN-58</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="40.5" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>DRV-05</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Cảnh báo thời gian lái liên tục</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Nhắc tài xế trước khi chạm ngưỡng 4 giờ lái liên tục hoặc 10 giờ/ngày, và gợi ý điểm dừng nghỉ, ưu tiên trạm sạc trên tuyến.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế an toàn hơn và tuân thủ luật về thời gian lái; thời gian nghỉ kết hợp sạc.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>• Thời gian lái liên tục và trong ngày của từng tài xế
+• Cảnh báo trước mỗi ngưỡng
+• Gợi ý điểm dừng nghỉ ưu tiên trạm sạc</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>DRV-04, MON-12, STN-06</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu IN-59, Bảng dữ liệu OUT-19</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>DRV-06</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Báo cáo tuân thủ thời gian lái &amp; nghỉ</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Theo từng tài xế: số ca vượt 4 giờ liên tục, 10 giờ/ngày và 48 giờ/tuần.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe chứng minh tuân thủ và phát hiện tài xế làm việc quá sức.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>• Số lần vượt theo tài xế và kỳ báo cáo
+• Xuất báo cáo phục vụ thanh tra</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>DRV-05</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu OUT-39</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="67.5" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>DRV-07</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Báo cáo hiệu quả sạc theo tài xế</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Theo tài xế: tỷ lệ kWh sạc giờ thấp điểm hoặc giờ điện tái tạo, chi phí điện/km, tiền tiết kiệm so với sạc giờ cao điểm và xếp hạng trong đội; có khung nhìn của quản lý và của chính tài xế.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Khuyến khích thói quen sạc rẻ và xanh.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe, Tài xế</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>• Báo cáo theo tuần và tháng cho từng tài xế
+• Xếp hạng trong đội xe
+• Xuất CSV/PDF</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>CHG-07, PAY-09, DRV-02</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>• Báo cáo có gắn với chương trình thưởng hay thi đua không, hay chỉ để tham khảo?</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-A8, Bảng dữ liệu OUT-32</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>F-A8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17806,1341 +19344,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="54" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>STN — Mạng lưới trạm sạc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="229.5" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Trạm và trụ sạc, trạng thái realtime qua OCPP, sự cố, bản đồ trạm, hàng đợi, đặt chỗ và phân tải.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Tên tính năng</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Giá trị mang lại</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Người dùng</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Chức năng chi tiết</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Đợt</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Hình thức bán / Giá</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Portal web</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Phụ thuộc</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu liên quan</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Câu hỏi mở</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Nguồn</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Mã cũ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>STN-01</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Danh mục trạm sạc</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Lưu từng trạm sạc: vị trí, khu vực, công suất, số trụ, chuẩn đầu sạc, giờ hoạt động, tình trạng bảo trì và hoạt động thực tế, đơn vị quản lý và đầu mối xử lý sự cố.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Nền tảng cho bản đồ trạm, cảnh báo và báo cáo sản lượng.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>• Tạo, sửa, tìm kiếm và ngừng hoạt động trạm
-• Đơn vị quản lý và đầu mối sự cố của từng trạm
-• Xem mọi trạm trên bản đồ</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-C1, Bảng dữ liệu IN-25</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>F-C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>STN-02</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Cấu trúc trụ &amp; súng sạc</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Mô tả các trụ và súng sạc của từng trạm: mã định danh mà trụ dùng, công suất và chuẩn đầu sạc của từng súng.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Mọi trạng thái và phiên sạc từ trụ đều ghi đúng súng sạc.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>• Khai báo trụ và súng trước khi kết nối
-• Công suất và chuẩn đầu sạc theo từng súng</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>STN-01</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>Quyết định CS-02, Quyết định CS-03, deferred.md 80</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="67.5" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>STN-03</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Kết nối trụ sạc (OCPP)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Kết nối trụ sạc qua OCPP 1.6J và 2.0.1: khởi động, heartbeat, trạng thái, giao dịch và chỉ số công tơ, lưu lại mọi bản tin.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Làm việc được với mọi hãng trụ sạc theo chuẩn, bắt đầu với Willdigits.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>• Cả hai phiên bản giao thức trên một cổng kết nối
-• Thông tin trụ, firmware và cấu hình được ghi lại sau mỗi lần khởi động
-• Nhật ký bản tin nguyên văn, chỉ ghi thêm
-• Cờ online từ bản tin gần nhất</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>STN-02</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>• Còn thiếu tài liệu từ nhà cung cấp: hướng dẫn tích hợp, bảng mã lỗi, thông tin công tơ, TLS/xác thực (câu hỏi mở 4).
-• Các lần mua trụ sau yêu cầu OCPP 2.0.1 hay chỉ cần 1.6J?</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-G2, Quyết định CO-01, Quyết định CO-02, Quyết định CO-05</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>F-G2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40.5" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>STN-04</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Trạng thái súng sạc realtime</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Trạng thái trống, đang sạc hay lỗi và công suất khả dụng của mọi súng sạc trên toàn mạng, cập nhật trong vòng 30 giây.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế chỉ tới những trạm có thể phục vụ mình.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành, Tài xế, Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>• Trạng thái theo đúng trụ báo, kèm chi tiết lỗi
-• Trạng thái cả trụ và từng súng trong một màn hình
-• Đánh dấu không rõ trạng thái khi trụ mất kết nối</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Có trong mọi gói</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>STN-03</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-C2, Bảng dữ liệu IN-26, Bảng dữ liệu OUT-48, NF-02, deferred.md 76</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>F-C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>STN-05</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Cảnh báo trụ sạc lỗi</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Cảnh báo trụ lỗi, mất kết nối hoặc công suất bất thường, kèm đơn vị quản lý và đầu mối xử lý sự cố của trạm.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Sự cố được xử lý nhanh và gọi đúng người.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành, Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>• Cảnh báo khi lỗi, mất kết nối và công suất bất thường
-• Dịch mã lỗi của hãng thành nguyên nhân dễ hiểu
-• Chuyển cảnh báo tới đầu mối của trạm</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>STN-04, NTF-01</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu OUT-49, Quyết định CS-08, deferred.md 75</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>STN-06</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Bản đồ &amp; tìm trạm sạc</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Tìm trạm gần nhất trên bản đồ, lọc theo tình trạng trống, công suất và chuẩn đầu sạc.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế nhanh chóng tìm được trụ trống.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Điều vận</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>• Các trạm gần nhất trong bán kính
-• Bộ lọc: đang trống, công suất tối thiểu, chuẩn đầu sạc
-• Số súng trống và giá hiện tại của từng trạm</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Có trong mọi gói</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>STN-04</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-D1, Bảng dữ liệu OUT-5</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>F-D1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>STN-07</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Hàng đợi &amp; thời gian chờ tại trạm</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Hiển thị số xe đang chờ, số xe dự kiến đến trong 60 phút và thời gian chờ dự kiến tới khi có súng trống; cảnh báo khi chờ quá lâu.</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế tránh xếp hàng và kịp điều chỉnh kế hoạch.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>• Số xe đang chờ và đang tới của từng trạm
-• Thời gian chờ ước tính từ thời lượng phiên (trung vị/p90 theo súng, công suất và khung giờ)
-• Cảnh báo khi vượt ngưỡng, kèm trạm thay thế</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>STN-04, MON-02, CHG-02</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-C3, Bảng dữ liệu IN-28, Bảng dữ liệu IN-29, Bảng dữ liệu OUT-6</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>F-C3</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>STN-08</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Dự báo tải trạm &amp; phân tải</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Dự báo số xe sẽ đến mỗi trạm so với số súng trống, cảnh báo tài xế đang hướng tới trạm sắp quá tải trong 60 phút và đề xuất ít nhất một trạm thay thế trong tầm pin.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Phân bổ nhu cầu trên toàn mạng; giảm thời gian chờ, tăng hiệu suất trụ.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Vận hành, Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>• Dự báo xe đến từ vị trí, mức pin, hướng đi và lịch sử
-• Tỷ lệ lấp đầy theo trụ; khuyến nghị cho vận hành
-• Cảnh báo tài xế kèm trạm thay thế</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>STN-07, RTE-01</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-C7, Bảng dữ liệu IN-28, Bảng dữ liệu OUT-53, NF-20</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>F-C7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40.5" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>STN-09</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Đặt chỗ sạc</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Đặt trước một súng sạc theo khung giờ và hủy đặt; áp dụng phạt khi không đến.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Đảm bảo được sạc cho những chuyến cần đúng giờ.</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Điều vận</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>• Đặt và hủy chỗ dựa trên thời gian chờ dự kiến
-• Giữ súng trên trụ trong khung giờ đã đặt
-• Mức phạt không đến cấu hình được</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Có thì tốt</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>P1.5</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>STN-07, STN-10, PAY-06</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>• Mức phạt khi không đến là bao nhiêu?</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-C4, Bảng dữ liệu IN-54</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>F-C4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40.5" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>STN-10</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Điều khiển trụ sạc từ xa</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Gửi lệnh tới trụ sạc: bắt đầu và dừng sạc, mở khóa đầu sạc, khởi động lại, đổi cấu hình, lấy dữ liệu chẩn đoán.</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Cần để bắt đầu sạc từ app và xử lý trụ mà không phải ra trạm.</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành, Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>• Bắt đầu và dừng sạc từ xa
-• Mở khóa, khởi động lại, đổi cấu hình, chẩn đoán
-• Mọi lệnh và phản hồi đều được ghi lại</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>STN-03</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>Quyết định CO-12, deferred.md 74</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="n"/>
-    </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>STN-11</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Kết nối trụ sạc an toàn</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Mã hóa kết nối trụ sạc và xác thực từng trụ trước khi triển khai thật.</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Không trụ giả mạo nào báo phiên sạc hoặc nhận lệnh được.</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>• Kết nối mã hóa (wss://)
-• Mật khẩu hoặc chứng chỉ riêng cho từng trụ</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>STN-03</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>NF-05, Quyết định IS-05, deferred.md 73</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="n"/>
-    </row>
-    <row r="16" ht="40.5" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>STN-12</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Trạm sạc riêng</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Trạm không công cộng (ví dụ tại mỏ hoặc bãi của khách hàng) chỉ hiển thị và dùng được cho các tổ chức được phép, với cách tính giá riêng.</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Phục vụ khách hàng sở hữu hoặc đặt trụ sạc riêng mà không mở cho mọi người.</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành, Kinh doanh</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>• Trạm công cộng hay riêng; danh sách tổ chức được phép
-• Biểu giá riêng cho trạm riêng</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>STN-01, PAY-09</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>• Trụ riêng (của mỏ, không công cộng) tính tiền thế nào? Bảng dữ liệu ghi 'phương án riêng'.</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu OUT-10</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="40.5" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>STN-13</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Dữ liệu nguồn phát xanh &amp; BESS</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Ghi nhận các nguồn điện của từng trạm (lưới, mặt trời, gió, sinh khối, pin lưu trữ BESS), sản lượng theo giờ, mức pin BESS và dự báo.</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Làm căn cứ cho giá điện xanh, nhãn sạc xanh và báo cáo carbon.</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành, Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>• Nguồn phát theo trạm
-• Sản lượng theo giờ, mức pin BESS, dự báo sản lượng</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>STN-01</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu IN-31</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="40.5" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>STN-14</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Sản lượng điện theo trạm</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>kWh bán ra theo trạm và theo khung giờ, phục vụ tối ưu giá theo giờ.</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Cho biết trạm nào, giờ nào mang lại doanh thu, để định giá.</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành, Quản trị trưởng (nội bộ)</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>• Tổng kWh và số phiên theo trạm trong kỳ
-• Chuỗi số liệu theo giờ và theo ngày
-• Xếp hạng toàn bộ trạm</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>CHG-02</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-C5, Bảng dữ liệu OUT-50, deferred.md 77</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>F-C5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40.5" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>STN-15</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Xem nhật ký bản tin trụ sạc</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Cho vận hành đọc bản tin gốc của trụ để xử lý sự cố, che mã thẻ, và xóa bản tin cũ sau thời hạn lưu.</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Chẩn đoán sự cố trụ mà không cần truy cập cơ sở dữ liệu.</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>• Đọc bản tin theo trụ và thời gian
-• Che mã thẻ và dữ liệu cá nhân khác
-• Thời hạn lưu bản tin gốc</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Có thì tốt</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>P1.1</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>STN-03</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>Quyết định IS-07, deferred.md 79</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -11,23 +11,24 @@
     <sheet name="ACC Tài khoản &amp; phân quyền" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="VEH Hồ sơ xe" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="BAT Pin" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="DEV Thiết bị telematics" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MON Giám sát xe &amp; pin" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="RTE Quãng đường &amp; lộ trình" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DRV Tài xế" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="FLT Quản lý đội xe" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="STN Mạng lưới trạm sạc" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="CHG Phiên sạc" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="POL Chính sách sạc &amp; bảo hành" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="PAY Gói, thanh toán &amp; hóa đơn" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="NTF Thông báo" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="SUP CSKH &amp; cứu hộ" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="MNT Bảo dưỡng &amp; tài sản" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="SAF An toàn lái xe &amp; camera" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="CRB Carbon &amp; chuyển đổi xanh" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="PLT Nền tảng, dữ liệu, tuân thủ" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="TMS Tích hợp TMS (Phase 2)" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Phi chức năng" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="WAR Bảo hành" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DEV Thiết bị telematics" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MON Giám sát xe &amp; pin" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="RTE Quãng đường &amp; lộ trình" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="DRV Tài xế" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="FLT Quản lý đội xe" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="STN Mạng lưới trạm sạc" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="CHG Phiên sạc" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="POL Chính sách sạc &amp; bảo hành" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="PAY Gói, thanh toán &amp; hóa đơn" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="NTF Thông báo" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="SUP CSKH &amp; cứu hộ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="MNT Bảo dưỡng &amp; tài sản" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="SAF An toàn lái xe &amp; camera" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="CRB Carbon &amp; chuyển đổi xanh" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="PLT Nền tảng, dữ liệu, tuân thủ" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TMS Tích hợp TMS (Phase 2)" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Phi chức năng" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -768,38 +769,36 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>DEV</t>
+          <t>WAR</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Thiết bị telematics</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Thiết bị gắn trên xe gửi dữ liệu về: danh mục, gắn với xe, sức khỏe thiết bị, bảo mật và cấu hình từ xa.</t>
+          <t>Bảo hành của từng xe, pin và thiết bị: thời hạn, giới hạn và lý do một bảo hành bị hủy.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>telematics</t>
+          <t>warranties</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -809,7 +808,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -824,50 +823,48 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MON</t>
+          <t>DEV</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Giám sát xe &amp; pin</t>
+          <t>Thiết bị telematics</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Dữ liệu xe theo thời gian thực và lịch sử, cảnh báo pin và an toàn, sức khỏe pin, chuyến đi và báo cáo vận hành.</t>
+          <t>Thiết bị gắn trên xe gửi dữ liệu về: danh mục, gắn với xe, sức khỏe thiết bị, bảo mật và cấu hình từ xa.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>telemetry</t>
+          <t>telematics</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>0/18</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>0/16</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -882,17 +879,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>RTE</t>
+          <t>MON</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Quãng đường &amp; lộ trình</t>
+          <t>Giám sát xe &amp; pin</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Xe còn đi được bao xa, bao lâu, có tới được đích không, nên sạc ở đâu và lúc nào, và những đoạn đường cấm tải.</t>
+          <t>Dữ liệu xe theo thời gian thực và lịch sử, cảnh báo pin và an toàn, sức khỏe pin, chuyến đi và báo cáo vận hành.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -901,29 +898,31 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/18</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/10</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/16</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -938,36 +937,38 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>DRV</t>
+          <t>RTE</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Tài xế</t>
+          <t>Quãng đường &amp; lộ trình</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Hồ sơ tài xế, phân công xe, ca làm việc, thời gian lái và báo cáo theo tài xế.</t>
+          <t>Xe còn đi được bao xa, bao lâu, có tới được đích không, nên sạc ở đâu và lúc nào, và những đoạn đường cấm tải.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>drivers</t>
+          <t>telemetry</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -977,7 +978,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -992,46 +993,46 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>FLT</t>
+          <t>DRV</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Quản lý đội xe</t>
+          <t>Tài xế</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Nhóm xe trong một tổ chức, người quản lý, bản đồ đội xe, vùng địa lý và báo cáo đội xe.</t>
+          <t>Hồ sơ tài xế, phân công xe, ca làm việc, thời gian lái và báo cáo theo tài xế.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>fleet</t>
+          <t>drivers</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1046,50 +1047,46 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>STN</t>
+          <t>FLT</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Mạng lưới trạm sạc</t>
+          <t>Quản lý đội xe</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Trạm và trụ sạc, trạng thái realtime qua OCPP, sự cố, bản đồ trạm, hàng đợi, đặt chỗ và phân tải.</t>
+          <t>Nhóm xe trong một tổ chức, người quản lý, bản đồ đội xe, vùng địa lý và báo cáo đội xe.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>charging_stations</t>
+          <t>fleet</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>0/15</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>0/12</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1104,48 +1101,50 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>CHG</t>
+          <t>STN</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Phiên sạc</t>
+          <t>Mạng lưới trạm sạc</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Bắt đầu sạc, bản ghi phiên sạc, biên nhận, lịch sử, điện năng theo khách hàng và đối soát.</t>
+          <t>Trạm và trụ sạc, trạng thái realtime qua OCPP, sự cố, bản đồ trạm, hàng đợi, đặt chỗ và phân tải.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>charging_sessions</t>
+          <t>charging_stations</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="3" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="I12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/15</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/12</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1154,47 +1153,49 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="40.5" customHeight="1">
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>CHG</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Chính sách sạc &amp; bảo hành</t>
+          <t>Phiên sạc</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Quy tắc sạc gắn với bảo hành, phát hiện vi phạm kèm bằng chứng, và nguy cơ mất bảo hành cho tài xế, đội xe và bộ phận bảo hành.</t>
+          <t>Bắt đầu sạc, bản ghi phiên sạc, biên nhận, lịch sử, điện năng theo khách hàng và đối soát.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>policy</t>
+          <t>charging_sessions</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
+      <c r="I13" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1214,48 +1215,46 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>PAY</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Gói dịch vụ, thanh toán &amp; hóa đơn</t>
+          <t>Chính sách sạc &amp; bảo hành</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Khách hàng mua gì (tính năng, gói, tiện ích thêm), cách thanh toán tiền sạc và thuê bao, biểu giá và hóa đơn điện tử.</t>
+          <t>Quy tắc sạc gắn với bảo hành, phát hiện vi phạm kèm bằng chứng, và nguy cơ mất bảo hành cho tài xế, đội xe và bộ phận bảo hành.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>billing</t>
+          <t>policy</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>0/13</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>0/10</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1264,54 +1263,54 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="27" customHeight="1">
+    <row r="15" ht="40.5" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>NTF</t>
+          <t>PAY</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>Gói dịch vụ, thanh toán &amp; hóa đơn</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Gửi cảnh báo và tin nhắn tới đúng người, đúng kênh (app, portal, push, SMS, e-mail).</t>
+          <t>Khách hàng mua gì (tính năng, gói, tiện ích thêm), cách thanh toán tiền sạc và thuê bao, biểu giá và hóa đơn điện tử.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>billing</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/13</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/10</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1326,43 +1325,43 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>SUP</t>
+          <t>NTF</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>CSKH &amp; cứu hộ</t>
+          <t>Thông báo</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Yêu cầu hỗ trợ, SOS, hàng đợi CSKH và SLA, điều phối đối tác sửa chữa – cứu hộ.</t>
+          <t>Gửi cảnh báo và tin nhắn tới đúng người, đúng kênh (app, portal, push, SMS, e-mail).</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="H16" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1382,50 +1381,48 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>MNT</t>
+          <t>SUP</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Bảo dưỡng &amp; vòng đời tài sản</t>
+          <t>CSKH &amp; cứu hộ</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Nhắc và đặt lịch bảo dưỡng, hồ sơ sửa chữa, chi phí bảo dưỡng, khấu hao và vòng đời vật tư.</t>
+          <t>Yêu cầu hỗ trợ, SOS, hàng đợi CSKH và SLA, điều phối đối tác sửa chữa – cứu hộ.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>support</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>0/10</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>0/10</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1434,52 +1431,56 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="40.5" customHeight="1">
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>SAF</t>
+          <t>MNT</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>An toàn lái xe &amp; camera</t>
+          <t>Bảo dưỡng &amp; vòng đời tài sản</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Chấm điểm an toàn lái xe, camera giám sát người lái, cảnh báo ADAS trong cabin, clip bằng chứng và nghĩa vụ pháp lý của camera.</t>
+          <t>Nhắc và đặt lịch bảo dưỡng, hồ sơ sửa chữa, chi phí bảo dưỡng, khấu hao và vòng đời vật tư.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>scoring</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
+      <c r="I18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>0/9</t>
+          <t>0/10</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>0/10</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1488,52 +1489,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="27" customHeight="1">
+    <row r="19" ht="40.5" customHeight="1">
       <c r="A19" s="3" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>SAF</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Kiểm kê carbon &amp; chuyển đổi xanh</t>
+          <t>An toàn lái xe &amp; camera</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Lượng phát thải giảm được nhờ xe điện, sạc xanh, kiểm kê khí nhà kính của đội xe và hồ sơ tín chỉ carbon.</t>
+          <t>Chấm điểm an toàn lái xe, camera giám sát người lái, cảnh báo ADAS trong cabin, clip bằng chứng và nghĩa vụ pháp lý của camera.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>carbon</t>
+          <t>scoring</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>0/11</t>
+          <t>0/9</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1548,264 +1549,304 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>PLT</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Nền tảng, dữ liệu &amp; tuân thủ</t>
+          <t>Kiểm kê carbon &amp; chuyển đổi xanh</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Đường ống và kho dữ liệu, sức khỏe hệ thống, lưu trữ dữ liệu, chủ quyền dữ liệu và dashboard toàn công ty.</t>
+          <t>Lượng phát thải giảm được nhờ xe điện, sạc xanh, kiểm kê khí nhà kính của đội xe và hồ sơ tín chỉ carbon.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Chưa có</t>
+          <t>carbon</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
           <t>0/7</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="40.5" customHeight="1">
+    <row r="21" ht="27" customHeight="1">
       <c r="A21" s="3" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>PLT</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Nền tảng, dữ liệu &amp; tuân thủ</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Đường ống và kho dữ liệu, sức khỏe hệ thống, lưu trữ dữ liệu, chủ quyền dữ liệu và dashboard toàn công ty.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>0/7</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>→ Mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40.5" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>TMS</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Tích hợp quản lý vận tải (Phase 2)</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Đơn hàng, chủ hàng và depot, làm ở Phase 2 bằng cách tích hợp với hệ thống quản lý vận tải (TMS) của khách hàng, không thay thế TMS.</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n">
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>0/6</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>→ Mở</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n">
-        <v>177</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>143</v>
-      </c>
-      <c r="H22" s="5" t="n">
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I23" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="J23" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>0/175</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>0/176</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>0/64</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>0/137</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>0/138</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Yêu cầu phi chức năng</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n">
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="6" t="inlineStr">
+    <row r="25"/>
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>CÁCH ĐỌC</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Trạng thái</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Theo từng phần cần làm (Backend, App, Portal web): Chưa làm, Đang làm, Xong. 'Không cần' = tính năng không cần phần đó. Cột 'xong' ở trên = số tính năng đã xong / số tính năng cần phần đó.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+    <row r="27" ht="54" customHeight="1">
       <c r="A27" s="3" t="n"/>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Ưu tiên</t>
+          <t>Trạng thái</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Bắt buộc (Must), Nên có (Should), Có thì tốt (Could)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="27" customHeight="1">
+          <t>Theo từng phần cần làm (Backend, App, Portal web): Chưa làm, Đang làm, Xong. 'Không cần' = tính năng không cần phần đó. Cột 'xong' ở trên = số tính năng đã xong / số tính năng cần phần đó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" s="3" t="n"/>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Đợt</t>
+          <t>Ưu tiên</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>P1.0 ra mắt, P1.1 khoảng 90 ngày sau, P1.5 năm 2026–27, P2 Phase 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="40.5" customHeight="1">
+          <t>Bắt buộc (Must), Nên có (Should), Có thì tốt (Could)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="27" customHeight="1">
       <c r="A29" s="3" t="n"/>
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Hình thức bán</t>
+          <t>Đợt</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Chỉ nội bộ (không bán); Có trong mọi gói; Chưa định giá. Giá được bổ sung khi làm phần định giá; tính năng nội bộ không bao giờ nằm trong gói.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
+          <t>P1.0 ra mắt, P1.1 khoảng 90 ngày sau, P1.5 năm 2026–27, P2 Phase 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40.5" customHeight="1">
       <c r="A30" s="3" t="n"/>
       <c r="B30" s="3" t="n"/>
       <c r="C30" s="3" t="inlineStr">
         <is>
+          <t>Hình thức bán</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán); Có trong mọi gói; Chưa định giá. Giá được bổ sung khi làm phần định giá; tính năng nội bộ không bao giờ nằm trong gói.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
           <t>Bảng dữ liệu</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Để trống cho tới khi rà soát xong thiết kế cơ sở dữ liệu.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32" ht="27" customHeight="1">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="32"/>
+    <row r="33" ht="27" customHeight="1">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>VAI TRÒ</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Quản trị trưởng (nội bộ)</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>HEAD_ADMIN</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1855,12 @@
       <c r="B34" s="3" t="n"/>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Đồng quản trị (nội bộ)</t>
+          <t>Quản trị trưởng (nội bộ)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>CO_ADMIN</t>
+          <t>HEAD_ADMIN</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1869,12 @@
       <c r="B35" s="3" t="n"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Quản trị tổ chức</t>
+          <t>Đồng quản trị (nội bộ)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>ORG_ADMIN</t>
+          <t>CO_ADMIN</t>
         </is>
       </c>
     </row>
@@ -1842,12 +1883,12 @@
       <c r="B36" s="3" t="n"/>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Kinh doanh</t>
+          <t>Quản trị tổ chức</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>ORG_ADMIN</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1897,12 @@
       <c r="B37" s="3" t="n"/>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Kế toán</t>
+          <t>Kinh doanh</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>ACCOUNTANT</t>
+          <t>SALES</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1911,12 @@
       <c r="B38" s="3" t="n"/>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>CSKH</t>
+          <t>Kế toán</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>CUSTOMER_CARE</t>
+          <t>ACCOUNTANT</t>
         </is>
       </c>
     </row>
@@ -1884,12 +1925,12 @@
       <c r="B39" s="3" t="n"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>CSKH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>CUSTOMER_CARE</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1939,12 @@
       <c r="B40" s="3" t="n"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Bảo trì</t>
+          <t>Vận hành</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>MAINTENANCE</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1953,12 @@
       <c r="B41" s="3" t="n"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Bảo trì</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>WARRANTY</t>
+          <t>MAINTENANCE</t>
         </is>
       </c>
     </row>
@@ -1926,12 +1967,12 @@
       <c r="B42" s="3" t="n"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>FLEET_MANAGER</t>
+          <t>WARRANTY</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1981,12 @@
       <c r="B43" s="3" t="n"/>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Điều vận</t>
+          <t>Quản lý đội xe</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>DISPATCHER</t>
+          <t>FLEET_MANAGER</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1995,12 @@
       <c r="B44" s="3" t="n"/>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Tài xế</t>
+          <t>Điều vận</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>DRIVER</t>
+          <t>DISPATCHER</t>
         </is>
       </c>
     </row>
@@ -1968,12 +2009,12 @@
       <c r="B45" s="3" t="n"/>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Kỹ thuật viên đối tác</t>
+          <t>Tài xế</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>TECHNICIAN</t>
+          <t>DRIVER</t>
         </is>
       </c>
     </row>
@@ -1982,12 +2023,12 @@
       <c r="B46" s="3" t="n"/>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Hệ thống (tự động)</t>
+          <t>Kỹ thuật viên đối tác</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>SYSTEM</t>
+          <t>TECHNICIAN</t>
         </is>
       </c>
     </row>
@@ -1996,10 +2037,24 @@
       <c r="B47" s="3" t="n"/>
       <c r="C47" s="3" t="inlineStr">
         <is>
+          <t>Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n"/>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
           <t>Hệ thống bên ngoài</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>EXTERNAL</t>
         </is>
@@ -2013,45 +2068,829 @@
     <hyperlink ref="N4" location="'VEH Hồ sơ xe'!A1"/>
     <hyperlink ref="C5" location="'BAT Pin'!A1"/>
     <hyperlink ref="N5" location="'BAT Pin'!A1"/>
-    <hyperlink ref="C6" location="'DEV Thiết bị telematics'!A1"/>
-    <hyperlink ref="N6" location="'DEV Thiết bị telematics'!A1"/>
-    <hyperlink ref="C7" location="'MON Giám sát xe &amp; pin'!A1"/>
-    <hyperlink ref="N7" location="'MON Giám sát xe &amp; pin'!A1"/>
-    <hyperlink ref="C8" location="'RTE Quãng đường &amp; lộ trình'!A1"/>
-    <hyperlink ref="N8" location="'RTE Quãng đường &amp; lộ trình'!A1"/>
-    <hyperlink ref="C9" location="'DRV Tài xế'!A1"/>
-    <hyperlink ref="N9" location="'DRV Tài xế'!A1"/>
-    <hyperlink ref="C10" location="'FLT Quản lý đội xe'!A1"/>
-    <hyperlink ref="N10" location="'FLT Quản lý đội xe'!A1"/>
-    <hyperlink ref="C11" location="'STN Mạng lưới trạm sạc'!A1"/>
-    <hyperlink ref="N11" location="'STN Mạng lưới trạm sạc'!A1"/>
-    <hyperlink ref="C12" location="'CHG Phiên sạc'!A1"/>
-    <hyperlink ref="N12" location="'CHG Phiên sạc'!A1"/>
-    <hyperlink ref="C13" location="'POL Chính sách sạc &amp; bảo hành'!A1"/>
-    <hyperlink ref="N13" location="'POL Chính sách sạc &amp; bảo hành'!A1"/>
-    <hyperlink ref="C14" location="'PAY Gói, thanh toán &amp; hóa đơn'!A1"/>
-    <hyperlink ref="N14" location="'PAY Gói, thanh toán &amp; hóa đơn'!A1"/>
-    <hyperlink ref="C15" location="'NTF Thông báo'!A1"/>
-    <hyperlink ref="N15" location="'NTF Thông báo'!A1"/>
-    <hyperlink ref="C16" location="'SUP CSKH &amp; cứu hộ'!A1"/>
-    <hyperlink ref="N16" location="'SUP CSKH &amp; cứu hộ'!A1"/>
-    <hyperlink ref="C17" location="'MNT Bảo dưỡng &amp; tài sản'!A1"/>
-    <hyperlink ref="N17" location="'MNT Bảo dưỡng &amp; tài sản'!A1"/>
-    <hyperlink ref="C18" location="'SAF An toàn lái xe &amp; camera'!A1"/>
-    <hyperlink ref="N18" location="'SAF An toàn lái xe &amp; camera'!A1"/>
-    <hyperlink ref="C19" location="'CRB Carbon &amp; chuyển đổi xanh'!A1"/>
-    <hyperlink ref="N19" location="'CRB Carbon &amp; chuyển đổi xanh'!A1"/>
-    <hyperlink ref="C20" location="'PLT Nền tảng, dữ liệu, tuân thủ'!A1"/>
-    <hyperlink ref="N20" location="'PLT Nền tảng, dữ liệu, tuân thủ'!A1"/>
-    <hyperlink ref="C21" location="'TMS Tích hợp TMS (Phase 2)'!A1"/>
-    <hyperlink ref="N21" location="'TMS Tích hợp TMS (Phase 2)'!A1"/>
-    <hyperlink ref="C23" location="'Phi chức năng'!A1"/>
+    <hyperlink ref="C6" location="'WAR Bảo hành'!A1"/>
+    <hyperlink ref="N6" location="'WAR Bảo hành'!A1"/>
+    <hyperlink ref="C7" location="'DEV Thiết bị telematics'!A1"/>
+    <hyperlink ref="N7" location="'DEV Thiết bị telematics'!A1"/>
+    <hyperlink ref="C8" location="'MON Giám sát xe &amp; pin'!A1"/>
+    <hyperlink ref="N8" location="'MON Giám sát xe &amp; pin'!A1"/>
+    <hyperlink ref="C9" location="'RTE Quãng đường &amp; lộ trình'!A1"/>
+    <hyperlink ref="N9" location="'RTE Quãng đường &amp; lộ trình'!A1"/>
+    <hyperlink ref="C10" location="'DRV Tài xế'!A1"/>
+    <hyperlink ref="N10" location="'DRV Tài xế'!A1"/>
+    <hyperlink ref="C11" location="'FLT Quản lý đội xe'!A1"/>
+    <hyperlink ref="N11" location="'FLT Quản lý đội xe'!A1"/>
+    <hyperlink ref="C12" location="'STN Mạng lưới trạm sạc'!A1"/>
+    <hyperlink ref="N12" location="'STN Mạng lưới trạm sạc'!A1"/>
+    <hyperlink ref="C13" location="'CHG Phiên sạc'!A1"/>
+    <hyperlink ref="N13" location="'CHG Phiên sạc'!A1"/>
+    <hyperlink ref="C14" location="'POL Chính sách sạc &amp; bảo hành'!A1"/>
+    <hyperlink ref="N14" location="'POL Chính sách sạc &amp; bảo hành'!A1"/>
+    <hyperlink ref="C15" location="'PAY Gói, thanh toán &amp; hóa đơn'!A1"/>
+    <hyperlink ref="N15" location="'PAY Gói, thanh toán &amp; hóa đơn'!A1"/>
+    <hyperlink ref="C16" location="'NTF Thông báo'!A1"/>
+    <hyperlink ref="N16" location="'NTF Thông báo'!A1"/>
+    <hyperlink ref="C17" location="'SUP CSKH &amp; cứu hộ'!A1"/>
+    <hyperlink ref="N17" location="'SUP CSKH &amp; cứu hộ'!A1"/>
+    <hyperlink ref="C18" location="'MNT Bảo dưỡng &amp; tài sản'!A1"/>
+    <hyperlink ref="N18" location="'MNT Bảo dưỡng &amp; tài sản'!A1"/>
+    <hyperlink ref="C19" location="'SAF An toàn lái xe &amp; camera'!A1"/>
+    <hyperlink ref="N19" location="'SAF An toàn lái xe &amp; camera'!A1"/>
+    <hyperlink ref="C20" location="'CRB Carbon &amp; chuyển đổi xanh'!A1"/>
+    <hyperlink ref="N20" location="'CRB Carbon &amp; chuyển đổi xanh'!A1"/>
+    <hyperlink ref="C21" location="'PLT Nền tảng, dữ liệu, tuân thủ'!A1"/>
+    <hyperlink ref="N21" location="'PLT Nền tảng, dữ liệu, tuân thủ'!A1"/>
+    <hyperlink ref="C22" location="'TMS Tích hợp TMS (Phase 2)'!A1"/>
+    <hyperlink ref="N22" location="'TMS Tích hợp TMS (Phase 2)'!A1"/>
+    <hyperlink ref="C24" location="'Phi chức năng'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="54" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FLT — Quản lý đội xe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="202.5" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Nhóm xe trong một tổ chức, người quản lý, bản đồ đội xe, vùng địa lý và báo cáo đội xe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tên tính năng</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Giá trị mang lại</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Người dùng</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Chức năng chi tiết</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Đợt</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Hình thức bán / Giá</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Portal web</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Phụ thuộc</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu liên quan</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Câu hỏi mở</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Mã cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40.5" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>FLT-01</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Đội xe &amp; cấp bậc đội xe</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Nhóm xe của một tổ chức thành các đội xe có tên, đội này có thể nằm dưới đội khác (vùng, chi nhánh, bãi).</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Mỗi khách hàng tự mô tả cơ cấu của mình bằng dữ liệu; tổ chức lại không phải sửa hệ thống.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe, Quản trị tổ chức</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>• Tạo, đổi tên, di chuyển và đóng đội xe
+• Đội xe lồng nhau; báo cáo cộng dồn lên cấp trên
+• Tìm theo tên hoặc mã</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>ACC-01</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-E1, Quyết định FL-02</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>F-E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>FLT-02</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Thành viên xe của đội</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Thêm xe vào đội và rút xe khỏi đội, lưu lịch sử; mỗi xe chỉ thuộc tối đa một đội tại một thời điểm.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Báo cáo cho một kỳ trước dùng đúng thành phần đội xe tại thời điểm đó.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>• Thêm hoặc rút xe theo VIN; lịch sử thành viên
+• Xe này đang thuộc đội nào?</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>FLT-01, VEH-01</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-E1, Quyết định FL-01, Quyết định FL-06</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>F-E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>FLT-03</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Phạm vi quản lý đội xe</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Giới hạn quản lý đội xe hoặc điều vận chỉ trong một số đội (và mọi đội cấp dưới); không giới hạn thì xem toàn bộ tổ chức.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Khách hàng lớn phân quyền cho quản lý vùng an toàn trên cùng một tài khoản.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Quản trị tổ chức</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>• Giao đội xe cho vai trò cấp đội xe của thành viên
+• Phạm vi được giao bao gồm mọi đội cấp dưới</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>FLT-01, ACC-13</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Quyết định FL-03</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>FLT-04</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Danh sách &amp; bản đồ toàn đội xe</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Toàn bộ xe của đội trên danh sách và bản đồ realtime, kèm trạng thái vận hành (đang lái, đỗ, sạc, tắt máy), vị trí, xe offline và cảnh báo qua đêm; lọc và tìm kiếm.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Màn hình chính của quản lý đội xe: nắm toàn bộ hoạt động trong một cái nhìn.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe, Điều vận</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>• Vị trí và trạng thái mới nhất của mọi xe trong đội
+• Làm nổi bật xe offline và cảnh báo qua đêm
+• Lọc theo trạng thái và tìm theo VIN hoặc biển số</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>FLT-02, MON-02, MON-09</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-E1, Bảng dữ liệu OUT-24</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>F-E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40.5" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>FLT-05</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Vùng địa lý &amp; cảnh báo ra/vào vùng</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Vẽ vùng trên bản đồ và nhận cảnh báo khi xe đi vào hoặc ra khỏi vùng.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Biết khi xe tới bãi, tới khách hàng hoặc vào khu vực không được phép.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe, Điều vận, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>• Tạo, sửa và xóa vùng đa giác
+• Cảnh báo vào và ra vùng theo từng bản tin
+• Vùng thuộc tổ chức, áp dụng cho các đội được chọn</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>FLT-02, MON-01, NTF-01</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-A5, Quyết định FL-05, deferred.md 86</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>F-A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>FLT-06</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard KPI đội xe</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Km, kWh, kWh/km, chi phí/km, SOH, tỷ lệ sử dụng và cảnh báo, cho cả đội và từng xe, theo kỳ chọn, có xuất file.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý biết đội xe điện có vận hành như kế hoạch không.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe, Quản trị tổ chức</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>• Tổng của đội và từng xe
+• Tỷ lệ sử dụng tính từ trạng thái vận hành
+• Số cảnh báo theo kỳ
+• Lọc thời gian và xuất file</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>MON-14, MON-07, MON-09, NTF-01</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-E2, Bảng dữ liệu OUT-25, deferred.md 72</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>F-E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>FLT-07</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Báo cáo chi phí vận hành đội xe</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Chi phí điện và chi phí/km theo xe, tài xế và tuyến.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Cho thấy tiền đi đâu và tuyến hay tài xế nào tốn kém hơn.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe, Kế toán</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>• Chi phí/km theo xe, tài xế và tuyến
+• Cộng dồn theo đội xe; xuất CSV</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>MON-14, MON-11, DRV-02</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu OUT-36, PRD F-A6</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="40.5" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>FLT-08</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Báo cáo sạc &amp; bảo hành theo đội/xe</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Phiên sạc, mức tuân thủ chính sách sạc và trạng thái bảo hành theo đội và xe, lọc được, xuất CSV/PDF.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe giữ quyền bảo hành bằng cách sửa thói quen sạc sai.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý đội xe, Bảo hành</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>• Phiên sạc theo xe và đội
+• Điểm tuân thủ và vi phạm
+• Xuất CSV/PDF</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>CHG-07, POL-04</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-E3, Bảng dữ liệu OUT-29</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>F-E3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3388,7 +4227,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4167,7 +5006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4796,7 +5635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5981,7 +6820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6742,7 +7581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7447,7 +8286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8359,7 +9198,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9214,7 +10053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10173,679 +11012,6 @@
         </is>
       </c>
       <c r="Q15" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="81" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PLT — Nền tảng, dữ liệu &amp; tuân thủ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="243" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Đường ống và kho dữ liệu, sức khỏe hệ thống, lưu trữ dữ liệu, chủ quyền dữ liệu và dashboard toàn công ty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Tên tính năng</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Giá trị mang lại</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Người dùng</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Chức năng chi tiết</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Đợt</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Hình thức bán / Giá</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Portal web</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Phụ thuộc</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu liên quan</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Câu hỏi mở</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Nguồn</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Mã cũ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>PLT-01</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Đường ống &amp; kho dữ liệu chuẩn hóa</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Thu thập, chuẩn hóa, gắn nhãn và lưu dữ liệu theo xe, khách hàng và tuyến vào kho phục vụ AI và BI, có phiên bản cấu trúc và dành sẵn khóa chuyến/đơn hàng/khách hàng cho Phase 2.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Phân tích và các tính năng AI sau này chạy trên dữ liệu sạch, so sánh được.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Hệ thống (tự động), Vận hành</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>• Bộ dữ liệu chuẩn hóa, gắn nhãn, có phiên bản cấu trúc
-• Khóa tùy chọn dành sẵn trip_id, shipment_id, customer_id</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>MON-01, CHG-02</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-G3, Bảng dữ liệu IN-40, Bảng dữ liệu OUT-64, Điều kiện tiên quyết 8, NF-16</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>F-G3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>PLT-02</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Giám sát chất lượng dữ liệu</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Phát hiện dữ liệu bẩn, thiếu hoặc bất hợp lý và cảnh báo vận hành.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Báo cáo và hóa đơn không dựa trên dữ liệu sai.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành, Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>• Quy tắc chất lượng theo nguồn dữ liệu
-• Điểm chất lượng và cảnh báo</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>PLT-01</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-G3, Bảng dữ liệu OUT-61</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>F-G3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>PLT-03</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Dashboard sức khỏe hệ thống</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Uptime, độ trễ thu nhận, gián đoạn luồng dữ liệu và chất lượng dữ liệu, có cảnh báo tới đội vận hành.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Thấy sự cố trước khi khách hàng báo.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>• Sức khỏe từng tiến trình (API, thu nhận dữ liệu, cổng trụ sạc, giám sát)
-• Cảnh báo khi luồng dữ liệu bị dừng
-• Log và chỉ số tập trung</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu OUT-61, NF-14, deferred.md 17, deferred.md 19</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="40.5" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>PLT-04</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Lưu trữ &amp; lưu trữ lạnh dữ liệu</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Lưu dữ liệu chuỗi thời gian dạng nóng 12 tháng và lạnh 5 năm (bằng thời hạn bảo hành), có quy tắc lưu theo từng loại dữ liệu.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Đáp ứng yêu cầu pháp lý và bảo hành mà vẫn kiểm soát chi phí lưu trữ.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Hệ thống (tự động), Vận hành</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>• Quy tắc lưu theo loại dữ liệu
-• Tự động chuyển sang lưu trữ lạnh và xóa</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>NF-16, deferred.md 48</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="67.5" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>PLT-05</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Giám sát chủ quyền dữ liệu</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Lập bản đồ dữ liệu nào rời khỏi xe, tới máy chủ nào, đặt ở quốc gia nào, bên thứ ba nào nhận; phát hiện kết nối tới máy chủ nước ngoài không khai báo và đối chiếu với cam kết bằng văn bản của nhà sản xuất.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Bảo vệ dữ liệu quốc gia và khách hàng; được kiểm chứng, không dựa vào cam kết miệng.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành, Quản trị trưởng (nội bộ)</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>• Bản đồ luồng dữ liệu khai báo theo loại thiết bị
-• Giám sát lưu lượng trong giai đoạn pilot
-• Báo cáo kết nối nước ngoài không khai báo</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu IN-24, Bảng dữ liệu OUT-60, Điều kiện tiên quyết 2</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="67.5" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>PLT-06</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Bộ KPI cho Ban lãnh đạo</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ số North Star (WHAV), tuân thủ sạc, kích hoạt app, CSAT/NPS, doanh thu và số xe.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Ban lãnh đạo điều hành bằng vài con số rõ ràng.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Quản trị trưởng (nội bộ)</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>• Bộ KPI kèm mục tiêu và xu hướng</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>PAY-13, POL-04, VEH-05</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>• Bộ KPI này dành cho lãnh đạo G3 hay lãnh đạo từng doanh nghiệp vận tải (bảng dữ liệu xếp vào nhóm doanh nghiệp vận tải)?
-• Định nghĩa chính xác WHAV và cách thu thập CSAT/NPS.</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu OUT-37</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="n"/>
-    </row>
-    <row r="11" ht="40.5" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>PLT-07</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Dữ liệu tổng hợp từ đối tác ngoài</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Nhập dữ liệu luồng di chuyển và nhu cầu theo khu vực dạng tổng hợp, ẩn danh từ đối tác bên ngoài.</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Quy hoạch trạm và dự báo tốt hơn.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>• Nhập và lưu bộ dữ liệu tổng hợp</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Có thì tốt</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>P1.5</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu IN-48</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12710,6 +12876,679 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="81" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PLT — Nền tảng, dữ liệu &amp; tuân thủ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="243" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Đường ống và kho dữ liệu, sức khỏe hệ thống, lưu trữ dữ liệu, chủ quyền dữ liệu và dashboard toàn công ty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tên tính năng</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Giá trị mang lại</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Người dùng</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Chức năng chi tiết</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Đợt</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Hình thức bán / Giá</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Portal web</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Phụ thuộc</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu liên quan</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Câu hỏi mở</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Mã cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>PLT-01</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Đường ống &amp; kho dữ liệu chuẩn hóa</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Thu thập, chuẩn hóa, gắn nhãn và lưu dữ liệu theo xe, khách hàng và tuyến vào kho phục vụ AI và BI, có phiên bản cấu trúc và dành sẵn khóa chuyến/đơn hàng/khách hàng cho Phase 2.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Phân tích và các tính năng AI sau này chạy trên dữ liệu sạch, so sánh được.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Hệ thống (tự động), Vận hành</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>• Bộ dữ liệu chuẩn hóa, gắn nhãn, có phiên bản cấu trúc
+• Khóa tùy chọn dành sẵn trip_id, shipment_id, customer_id</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>MON-01, CHG-02</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-G3, Bảng dữ liệu IN-40, Bảng dữ liệu OUT-64, Điều kiện tiên quyết 8, NF-16</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>F-G3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>PLT-02</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Giám sát chất lượng dữ liệu</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Phát hiện dữ liệu bẩn, thiếu hoặc bất hợp lý và cảnh báo vận hành.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Báo cáo và hóa đơn không dựa trên dữ liệu sai.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>• Quy tắc chất lượng theo nguồn dữ liệu
+• Điểm chất lượng và cảnh báo</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>PLT-01</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-G3, Bảng dữ liệu OUT-61</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>F-G3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PLT-03</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard sức khỏe hệ thống</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Uptime, độ trễ thu nhận, gián đoạn luồng dữ liệu và chất lượng dữ liệu, có cảnh báo tới đội vận hành.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Thấy sự cố trước khi khách hàng báo.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>• Sức khỏe từng tiến trình (API, thu nhận dữ liệu, cổng trụ sạc, giám sát)
+• Cảnh báo khi luồng dữ liệu bị dừng
+• Log và chỉ số tập trung</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu OUT-61, NF-14, deferred.md 17, deferred.md 19</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="40.5" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>PLT-04</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Lưu trữ &amp; lưu trữ lạnh dữ liệu</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Lưu dữ liệu chuỗi thời gian dạng nóng 12 tháng và lạnh 5 năm (bằng thời hạn bảo hành), có quy tắc lưu theo từng loại dữ liệu.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Đáp ứng yêu cầu pháp lý và bảo hành mà vẫn kiểm soát chi phí lưu trữ.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Hệ thống (tự động), Vận hành</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>• Quy tắc lưu theo loại dữ liệu
+• Tự động chuyển sang lưu trữ lạnh và xóa</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>NF-16, deferred.md 48</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="67.5" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PLT-05</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Giám sát chủ quyền dữ liệu</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Lập bản đồ dữ liệu nào rời khỏi xe, tới máy chủ nào, đặt ở quốc gia nào, bên thứ ba nào nhận; phát hiện kết nối tới máy chủ nước ngoài không khai báo và đối chiếu với cam kết bằng văn bản của nhà sản xuất.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Bảo vệ dữ liệu quốc gia và khách hàng; được kiểm chứng, không dựa vào cam kết miệng.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành, Quản trị trưởng (nội bộ)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>• Bản đồ luồng dữ liệu khai báo theo loại thiết bị
+• Giám sát lưu lượng trong giai đoạn pilot
+• Báo cáo kết nối nước ngoài không khai báo</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu IN-24, Bảng dữ liệu OUT-60, Điều kiện tiên quyết 2</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="67.5" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>PLT-06</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Bộ KPI cho Ban lãnh đạo</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ số North Star (WHAV), tuân thủ sạc, kích hoạt app, CSAT/NPS, doanh thu và số xe.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Ban lãnh đạo điều hành bằng vài con số rõ ràng.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Quản trị trưởng (nội bộ)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>• Bộ KPI kèm mục tiêu và xu hướng</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>PAY-13, POL-04, VEH-05</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>• Bộ KPI này dành cho lãnh đạo G3 hay lãnh đạo từng doanh nghiệp vận tải (bảng dữ liệu xếp vào nhóm doanh nghiệp vận tải)?
+• Định nghĩa chính xác WHAV và cách thu thập CSAT/NPS.</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu OUT-37</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="40.5" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>PLT-07</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Dữ liệu tổng hợp từ đối tác ngoài</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Nhập dữ liệu luồng di chuyển và nhu cầu theo khu vực dạng tổng hợp, ẩn danh từ đối tác bên ngoài.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Quy hoạch trạm và dự báo tốt hơn.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Vận hành</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>• Nhập và lưu bộ dữ liệu tổng hợp</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Có thì tốt</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>P1.5</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nội bộ (không bán)</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu IN-48</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13299,7 +14138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14094,7 +14933,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="135" customHeight="1">
+    <row r="5" ht="108" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>VEH-01</t>
@@ -14125,7 +14964,6 @@
           <t>• Tạo, sửa, tìm kiếm và ngừng sử dụng xe
 • VIN và biển số không trùng trong các xe đang dùng và đều sửa được (nhập nhầm, biển số theo chủ xe); lưu lịch sử thay đổi kèm lý do
 • Trạng thái phục vụ do con người đặt: đang phục vụ, đang bảo dưỡng, đã rời hệ thống, kèm lý do; xe nhàn rỗi hay mất tín hiệu được hiển thị từ dữ liệu, không lưu
-• Bảo hành theo từng xe, pin và thiết bị với giới hạn riêng; bảo hành bị hủy lưu kèm lý do
 • Lọc theo trạng thái, dòng xe, chủ sở hữu và đội xe</t>
         </is>
       </c>
@@ -14164,7 +15002,7 @@
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-32, PRD F-F2, Quyết định VH-05, Quyết định VH-07, Quyết định VH-09</t>
+          <t>Bảng dữ liệu IN-32, PRD F-F2, Quyết định VH-05, Quyết định VH-07</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -14718,6 +15556,227 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WAR — Bảo hành</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="202.5" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Bảo hành của từng xe, pin và thiết bị: thời hạn, giới hạn và lý do một bảo hành bị hủy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>← Tổng quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tên tính năng</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Giá trị mang lại</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Người dùng</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Chức năng chi tiết</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Đợt</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Hình thức bán / Giá</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Portal web</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Phụ thuộc</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu liên quan</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Câu hỏi mở</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Mã cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="67.5" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>WAR-01</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Sổ bảo hành</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Lưu mọi bảo hành của xe, pin và thiết bị trên xe: thời hạn, các giới hạn như quãng đường hay số chu kỳ sạc, và trạng thái, kèm lý do khi bảo hành bị hủy.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Mọi bên đều biết những gì còn được bảo hành; bảo hành bị hủy có lý do rõ ràng và chứng minh được.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Bảo hành, Vận hành, Quản lý đội xe</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>• Bảo hành theo từng xe, pin và thiết bị, đặt riêng cho từng xe, mỗi bảo hành có thời hạn và giới hạn riêng
+• Hết hạn được tính từ ngày và bộ đếm của xe hoặc pin; hủy bảo hành kèm lý do và lịch sử
+• Bảo hành của pin đi theo pin sang xe khác</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Có trong mọi gói</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>VEH-01, BAT-01</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu IN-32, Quyết định VH-09, Quyết định VH-14</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15497,7 +16556,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17153,701 +18212,6 @@
         </is>
       </c>
       <c r="Q23" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" location="'Tổng quan'!A1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="67.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RTE — Quãng đường &amp; lộ trình</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="256.5" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Xe còn đi được bao xa, bao lâu, có tới được đích không, nên sạc ở đâu và lúc nào, và những đoạn đường cấm tải.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>← Tổng quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Tên tính năng</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Giá trị mang lại</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Người dùng</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Chức năng chi tiết</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Đợt</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Hình thức bán / Giá</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Portal web</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Phụ thuộc</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu liên quan</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Câu hỏi mở</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Nguồn</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Mã cũ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="67.5" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>RTE-01</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Dự báo quãng đường &amp; thời gian còn lại</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Ước tính số km và số phút xe còn chạy được từ mức pin, tốc độ tiêu thụ tức thời, tải trọng, địa hình, nhiệt độ và cách lái, kèm khoảng tin cậy.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Thay thế cách ước tính tuyến tính theo % pin vốn sai lệch khi lên dốc và chở nặng.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>• Mô hình dự báo dùng tải trọng, cao độ (DEM), thời tiết và cách lái
-• Số km và số phút còn lại kèm khoảng tin cậy
-• Huấn luyện lại định kỳ trên dữ liệu tuyến thực (sai số ≤10% p50, ≤15% p90)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>MON-01, MON-13, RTE-07, VEH-03</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-A7, Bảng dữ liệu IN-2, Bảng dữ liệu IN-3, NF-20</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>F-A7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>RTE-02</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Kiểm tra đủ pin cho hành trình</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Cho tài xế biết với mức pin hiện tại xe có đi hết hành trình hoặc tới được trạm đã chọn không, và gợi ý các trạm trong tầm khi không đủ.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế lên kế hoạch dừng sạc trước khi quá muộn.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>• So sánh đích đến hoặc trạm với quãng đường dự báo
-• Gợi ý các trạm tới được</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>RTE-01, STN-06</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-D3, Bảng dữ liệu OUT-3</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>F-D3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>RTE-03</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ đường tới trạm</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ đường từng bước tới trạm đã chọn, ngay trong app hoặc chuyển sang Google Maps hay VietMap.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Một chạm từ cảnh báo tới chỉ đường.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>• Mở chỉ đường từ màn hình trạm và từ cảnh báo pin
-• Chuyển sang ứng dụng bản đồ bên ngoài</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Có trong mọi gói</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>STN-06</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-D2, Bảng dữ liệu OUT-5</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>F-D2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>RTE-04</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Cảnh báo đường cấm tải &amp; khung giờ cấm</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Cảnh báo tài xế trước khi vào đoạn đường cấm tải hoặc trong khung giờ cấm, đề xuất tuyến khác và ảnh hưởng tới các điểm dừng sạc.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Tránh bị phạt và chạy uổng công.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Điều vận</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>• Đường cấm tải và khung giờ cấm từ nhà cung cấp bản đồ
-• Cảnh báo trước đoạn cấm
-• Tuyến thay thế và ảnh hưởng tới việc sạc</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>P1.1</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>RTE-07, RTE-02</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>• Dữ liệu đường cấm tải – cấm giờ tại Việt Nam phải là tiêu chí bắt buộc khi chọn nhà cung cấp bản đồ (điều kiện tiên quyết 4).</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu OUT-7, Bảng dữ liệu IN-42, Điều kiện tiên quyết 4</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>RTE-05</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Gợi ý sạc tối ưu chi phí</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Gợi ý nên sạc ở đâu, lúc nào để chi phí thấp nhất mà vẫn đúng giờ, kèm số tiền tiết kiệm ước tính và rủi ro trễ; tài xế luôn có thể bỏ qua.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Dịch chuyển việc sạc sang giờ rẻ và giờ điện xanh, giúp khách hàng tiết kiệm.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Điều vận</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>• Kết hợp biểu giá, dự báo tải trạm, mức pin và dự báo tiêu thụ trên tuyến
-• Hiển thị tiền tiết kiệm và rủi ro trễ cho mỗi gợi ý</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>RTE-01, STN-08, PAY-09</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-D6, Bảng dữ liệu OUT-9, NF-20</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>F-D6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>RTE-06</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Báo cáo chất lượng mô hình dự báo</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Đo sai số dự báo: quãng đường (p50/p90), tải trạm và thời gian chờ, theo tuần.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Cho biết dự báo có đáng tin không và khi nào cần huấn luyện lại.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Vận hành</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>• So sánh dự báo với thực tế
-• Độ chính xác theo tuần của từng mô hình</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>RTE-01, STN-07, STN-08</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu OUT-63, NF-20</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="n"/>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>RTE-07</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Dữ liệu bản đồ, địa hình &amp; thời tiết</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Kết nối dữ liệu bên thứ ba về bản đồ, chỉ đường, khoảng cách, giới hạn tốc độ, giao thông, cao độ và thời tiết.</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Dự báo, cảnh báo và chấm điểm an toàn cần bối cảnh con đường.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>• Tuyến đường, ETA, ma trận khoảng cách, giới hạn tốc độ, giao thông
-• Cao độ dọc tuyến
-• Nhiệt độ và thời tiết theo khu vực và theo tuyến</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Nên có</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ nội bộ (không bán)</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu IN-42, Bảng dữ liệu IN-43, Bảng dữ liệu IN-44, Điều kiện tiên quyết 4</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -17885,17 +18249,17 @@
     <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" customHeight="1">
+    <row r="1" ht="67.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DRV — Tài xế</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="175.5" customHeight="1">
+          <t>RTE — Quãng đường &amp; lộ trình</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="256.5" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Hồ sơ tài xế, phân công xe, ca làm việc, thời gian lái và báo cáo theo tài xế.</t>
+          <t>Xe còn đi được bao xa, bao lâu, có tới được đích không, nên sạc ở đâu và lúc nào, và những đoạn đường cấm tải.</t>
         </is>
       </c>
     </row>
@@ -17993,42 +18357,42 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1">
+    <row r="5" ht="67.5" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DRV-01</t>
+          <t>RTE-01</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Hồ sơ tài xế</t>
+          <t>Dự báo quãng đường &amp; thời gian còn lại</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Lưu thông tin của tài xế trong một tổ chức: số bằng lái, hạng, ngày hết hạn và trạng thái.</t>
+          <t>Ước tính số km và số phút xe còn chạy được từ mức pin, tốc độ tiêu thụ tức thời, tải trọng, địa hình, nhiệt độ và cách lái, kèm khoảng tin cậy.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Chỉ tài xế có bằng lái hợp lệ mới được giao xe.</t>
+          <t>Thay thế cách ước tính tuyến tính theo % pin vốn sai lệch khi lên dốc và chở nặng.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe, Quản trị tổ chức</t>
+          <t>Tài xế, Hệ thống (tự động)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>• Thêm, sửa, tìm kiếm và ngừng hoạt động tài xế
-• Nhắc bằng lái sắp hết hạn
-• Hồ sơ tài xế thuộc một thành viên tổ chức; tài xế đã nghỉ vẫn giữ lịch sử</t>
+          <t>• Mô hình dự báo dùng tải trọng, cao độ (DEM), thời tiết và cách lái
+• Số km và số phút còn lại kèm khoảng tin cậy
+• Huấn luyện lại định kỳ trên dữ liệu tuyến thực (sai số ≤10% p50, ≤15% p90)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Bắt buộc</t>
+          <t>Nên có</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -18048,71 +18412,67 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>Không cần</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>ACC-12</t>
+          <t>MON-01, MON-13, RTE-07, VEH-03</t>
         </is>
       </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E4, Bảng dữ liệu IN-37, Bảng dữ liệu OUT-34, Quyết định ID-13, Quyết định DR-03</t>
+          <t>PRD F-A7, Bảng dữ liệu IN-2, Bảng dữ liệu IN-3, NF-20</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>F-E4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="189" customHeight="1">
+          <t>F-A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DRV-02</t>
+          <t>RTE-02</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nhận xe</t>
+          <t>Kiểm tra đủ pin cho hành trình</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Tài xế nhận chiếc xe sắp lái bằng cách quét mã QR trên xe hoặc chọn xe trên ứng dụng; hệ thống luôn biết ai đang cầm lái và lưu toàn bộ lịch sử.</t>
+          <t>Cho tài xế biết với mức pin hiện tại xe có đi hết hành trình hoặc tới được trạm đã chọn không, và gợi ý các trạm trong tầm khi không đủ.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Trong vận tải chặng ngắn, tài xế và xe đổi nhau hằng ngày; mọi sự kiện của xe vẫn truy được tài xế tại thời điểm đó.</t>
+          <t>Tài xế lên kế hoạch dừng sạc trước khi quá muộn.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Tài xế, Quản lý đội xe, Điều vận, Hệ thống (tự động)</t>
+          <t>Tài xế</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>• Nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, bị từ chối khi điện thoại ở xa xe; quản lý có thể nhận xe giúp tài xế trên portal
-• Tài xế đang hoạt động nào cũng có thể lái xe của bất kỳ tổ chức nào; cảnh báo khi tài xế thuộc tổ chức khác
-• Mỗi xe một người cầm lái; phiên kết thúc khi trả xe, khi tài xế khác nhận xe, khi tài xế nhận xe khác, hoặc khi xe không di chuyển quá thời gian tự kết thúc của tổ chức (mặc định 2 giờ)
-• Cảnh báo lên portal khi xe chạy mà không ai nhận xe
-• Cảnh báo dành cho tài xế gửi tới tài xế đang nhận xe và portal
-• Lịch sử theo tài xế và theo xe</t>
+          <t>• So sánh đích đến hoặc trạm với quãng đường dự báo
+• Gợi ý các trạm tới được</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Bắt buộc</t>
+          <t>Nên có</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -18137,154 +18497,155 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Không cần</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>DRV-01, VEH-01</t>
+          <t>RTE-01, STN-06</t>
         </is>
       </c>
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-07, Quyết định DR-08, Quyết định NT-07, Quyết định ID-45</t>
+          <t>PRD F-D3, Bảng dữ liệu OUT-3</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>F-E4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="27" customHeight="1">
+          <t>F-D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40.5" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DRV-03</t>
+          <t>RTE-03</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Lịch làm việc của tài xế</t>
+          <t>Chỉ đường tới trạm</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Lập lịch ngày làm việc và ca của tài xế.</t>
+          <t>Chỉ đường từng bước tới trạm đã chọn, ngay trong app hoặc chuyển sang Google Maps hay VietMap.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Điều vận biết ai đang sẵn sàng và bố trí nghỉ ngơi hợp lý.</t>
+          <t>Một chạm từ cảnh báo tới chỉ đường.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Điều vận, Quản lý đội xe, Tài xế</t>
+          <t>Tài xế</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>• Lập ca theo tài xế và theo xe
-• Tài xế xem lịch của mình trên app</t>
+          <t>• Mở chỉ đường từ màn hình trạm và từ cảnh báo pin
+• Chuyển sang ứng dụng bản đồ bên ngoài</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Có trong mọi gói</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>STN-06</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>PRD F-D2, Bảng dữ liệu OUT-5</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>F-D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>RTE-04</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Cảnh báo đường cấm tải &amp; khung giờ cấm</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Cảnh báo tài xế trước khi vào đoạn đường cấm tải hoặc trong khung giờ cấm, đề xuất tuyến khác và ảnh hưởng tới các điểm dừng sạc.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Tránh bị phạt và chạy uổng công.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế, Điều vận</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>• Đường cấm tải và khung giờ cấm từ nhà cung cấp bản đồ
+• Cảnh báo trước đoạn cấm
+• Tuyến thay thế và ảnh hưởng tới việc sạc</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
           <t>Nên có</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>P1.1</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Chưa định giá</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>DRV-02</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>• Phạm vi lịch làm việc cần làm rõ (Hùng Võ).</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>Bảng dữ liệu IN-55</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="40.5" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>DRV-04</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Định danh tài xế theo ca</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Ghi nhận ai thực sự lái xe trong từng ca, bằng khuôn mặt, thẻ hoặc đăng nhập app, kèm thời điểm bắt đầu và kết thúc ca.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Hồ sơ thời gian lái đúng luật và báo cáo theo tài xế công bằng.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Tài xế, Hệ thống (tự động)</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>• Bắt đầu và kết thúc ca bằng khuôn mặt, thẻ hoặc app
-• Cảnh báo khi người lái không phải tài xế được phân công</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Chưa làm</t>
@@ -18302,58 +18663,57 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>DRV-02, SAF-03</t>
+          <t>RTE-07, RTE-02</t>
         </is>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>• Hai tài xế một xe: dùng một app hay hai app?</t>
+          <t>• Dữ liệu đường cấm tải – cấm giờ tại Việt Nam phải là tiêu chí bắt buộc khi chọn nhà cung cấp bản đồ (điều kiện tiên quyết 4).</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-58</t>
+          <t>Bảng dữ liệu OUT-7, Bảng dữ liệu IN-42, Điều kiện tiên quyết 4</t>
         </is>
       </c>
       <c r="Q8" s="3" t="n"/>
     </row>
-    <row r="9" ht="40.5" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DRV-05</t>
+          <t>RTE-05</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Cảnh báo thời gian lái liên tục</t>
+          <t>Gợi ý sạc tối ưu chi phí</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Nhắc tài xế trước khi chạm ngưỡng 4 giờ lái liên tục hoặc 10 giờ/ngày, và gợi ý điểm dừng nghỉ, ưu tiên trạm sạc trên tuyến.</t>
+          <t>Gợi ý nên sạc ở đâu, lúc nào để chi phí thấp nhất mà vẫn đúng giờ, kèm số tiền tiết kiệm ước tính và rủi ro trễ; tài xế luôn có thể bỏ qua.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Tài xế an toàn hơn và tuân thủ luật về thời gian lái; thời gian nghỉ kết hợp sạc.</t>
+          <t>Dịch chuyển việc sạc sang giờ rẻ và giờ điện xanh, giúp khách hàng tiết kiệm.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Tài xế, Hệ thống (tự động)</t>
+          <t>Tài xế, Điều vận</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>• Thời gian lái liên tục và trong ngày của từng tài xế
-• Cảnh báo trước mỗi ngưỡng
-• Gợi ý điểm dừng nghỉ ưu tiên trạm sạc</t>
+          <t>• Kết hợp biểu giá, dự báo tải trạm, mức pin và dự báo tiêu thụ trên tuyến
+• Hiển thị tiền tiết kiệm và rủi ro trễ cho mỗi gợi ý</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Bắt buộc</t>
+          <t>Nên có</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -18383,53 +18743,57 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>DRV-04, MON-12, STN-06</t>
+          <t>RTE-01, STN-08, PAY-09</t>
         </is>
       </c>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-59, Bảng dữ liệu OUT-19</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="40.5" customHeight="1">
+          <t>PRD F-D6, Bảng dữ liệu OUT-9, NF-20</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>F-D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>DRV-06</t>
+          <t>RTE-06</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Báo cáo tuân thủ thời gian lái &amp; nghỉ</t>
+          <t>Báo cáo chất lượng mô hình dự báo</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Theo từng tài xế: số ca vượt 4 giờ liên tục, 10 giờ/ngày và 48 giờ/tuần.</t>
+          <t>Đo sai số dự báo: quãng đường (p50/p90), tải trạm và thời gian chờ, theo tuần.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe chứng minh tuân thủ và phát hiện tài xế làm việc quá sức.</t>
+          <t>Cho biết dự báo có đáng tin không và khi nào cần huấn luyện lại.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe</t>
+          <t>Vận hành</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>• Số lần vượt theo tài xế và kỳ báo cáo
-• Xuất báo cáo phục vụ thanh tra</t>
+          <t>• So sánh dự báo với thực tế
+• Độ chính xác theo tuần của từng mô hình</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Bắt buộc</t>
+          <t>Nên có</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -18439,7 +18803,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Chưa định giá</t>
+          <t>Chỉ nội bộ (không bán)</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -18459,49 +18823,49 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>DRV-05</t>
+          <t>RTE-01, STN-07, STN-08</t>
         </is>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu OUT-39</t>
+          <t>Bảng dữ liệu OUT-63, NF-20</t>
         </is>
       </c>
       <c r="Q10" s="3" t="n"/>
     </row>
-    <row r="11" ht="67.5" customHeight="1">
+    <row r="11" ht="54" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DRV-07</t>
+          <t>RTE-07</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Báo cáo hiệu quả sạc theo tài xế</t>
+          <t>Dữ liệu bản đồ, địa hình &amp; thời tiết</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Theo tài xế: tỷ lệ kWh sạc giờ thấp điểm hoặc giờ điện tái tạo, chi phí điện/km, tiền tiết kiệm so với sạc giờ cao điểm và xếp hạng trong đội; có khung nhìn của quản lý và của chính tài xế.</t>
+          <t>Kết nối dữ liệu bên thứ ba về bản đồ, chỉ đường, khoảng cách, giới hạn tốc độ, giao thông, cao độ và thời tiết.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Khuyến khích thói quen sạc rẻ và xanh.</t>
+          <t>Dự báo, cảnh báo và chấm điểm an toàn cần bối cảnh con đường.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe, Tài xế</t>
+          <t>Hệ thống (tự động)</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>• Báo cáo theo tuần và tháng cho từng tài xế
-• Xếp hạng trong đội xe
-• Xuất CSV/PDF</t>
+          <t>• Tuyến đường, ETA, ma trận khoảng cách, giới hạn tốc độ, giao thông
+• Cao độ dọc tuyến
+• Nhiệt độ và thời tiết theo khu vực và theo tuyến</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -18516,7 +18880,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Chưa định giá</t>
+          <t>Chỉ nội bộ (không bán)</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -18526,35 +18890,23 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Không cần</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>CHG-07, PAY-09, DRV-02</t>
-        </is>
-      </c>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n"/>
       <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>• Báo cáo có gắn với chương trình thưởng hay thi đua không, hay chỉ để tham khảo?</t>
-        </is>
-      </c>
+      <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>PRD F-A8, Bảng dữ liệu OUT-32</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>F-A8</t>
-        </is>
-      </c>
+          <t>Bảng dữ liệu IN-42, Bảng dữ liệu IN-43, Bảng dữ liệu IN-44, Điều kiện tiên quyết 4</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -18570,7 +18922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18592,17 +18944,17 @@
     <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="54" customHeight="1">
+    <row r="1" ht="27" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FLT — Quản lý đội xe</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="202.5" customHeight="1">
+          <t>DRV — Tài xế</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="175.5" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Nhóm xe trong một tổ chức, người quản lý, bản đồ đội xe, vùng địa lý và báo cáo đội xe.</t>
+          <t>Hồ sơ tài xế, phân công xe, ca làm việc, thời gian lái và báo cáo theo tài xế.</t>
         </is>
       </c>
     </row>
@@ -18700,25 +19052,25 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="40.5" customHeight="1">
+    <row r="5" ht="54" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>FLT-01</t>
+          <t>DRV-01</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Đội xe &amp; cấp bậc đội xe</t>
+          <t>Hồ sơ tài xế</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Nhóm xe của một tổ chức thành các đội xe có tên, đội này có thể nằm dưới đội khác (vùng, chi nhánh, bãi).</t>
+          <t>Lưu thông tin của tài xế trong một tổ chức: số bằng lái, hạng, ngày hết hạn và trạng thái.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Mỗi khách hàng tự mô tả cơ cấu của mình bằng dữ liệu; tổ chức lại không phải sửa hệ thống.</t>
+          <t>Chỉ tài xế có bằng lái hợp lệ mới được giao xe.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -18728,9 +19080,9 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>• Tạo, đổi tên, di chuyển và đóng đội xe
-• Đội xe lồng nhau; báo cáo cộng dồn lên cấp trên
-• Tìm theo tên hoặc mã</t>
+          <t>• Thêm, sửa, tìm kiếm và ngừng hoạt động tài xế
+• Nhắc bằng lái sắp hết hạn
+• Hồ sơ tài xế thuộc một thành viên tổ chức; tài xế đã nghỉ vẫn giữ lịch sử</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -18765,52 +19117,56 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>ACC-01</t>
+          <t>ACC-12</t>
         </is>
       </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E1, Quyết định FL-02</t>
+          <t>PRD F-E4, Bảng dữ liệu IN-37, Bảng dữ liệu OUT-34, Quyết định ID-13, Quyết định DR-03</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>F-E1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40.5" customHeight="1">
+          <t>F-E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="189" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>FLT-02</t>
+          <t>DRV-02</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Thành viên xe của đội</t>
+          <t>Nhận xe</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Thêm xe vào đội và rút xe khỏi đội, lưu lịch sử; mỗi xe chỉ thuộc tối đa một đội tại một thời điểm.</t>
+          <t>Tài xế nhận chiếc xe sắp lái bằng cách quét mã QR trên xe hoặc chọn xe trên ứng dụng; hệ thống luôn biết ai đang cầm lái và lưu toàn bộ lịch sử.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Báo cáo cho một kỳ trước dùng đúng thành phần đội xe tại thời điểm đó.</t>
+          <t>Trong vận tải chặng ngắn, tài xế và xe đổi nhau hằng ngày; mọi sự kiện của xe vẫn truy được tài xế tại thời điểm đó.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe</t>
+          <t>Tài xế, Quản lý đội xe, Điều vận, Hệ thống (tự động)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>• Thêm hoặc rút xe theo VIN; lịch sử thành viên
-• Xe này đang thuộc đội nào?</t>
+          <t>• Nhận xe bằng cách quét mã QR trên xe hoặc chọn xe ở gần trên ứng dụng, bị từ chối khi điện thoại ở xa xe; quản lý có thể nhận xe giúp tài xế trên portal
+• Tài xế đang hoạt động nào cũng có thể lái xe của bất kỳ tổ chức nào; cảnh báo khi tài xế thuộc tổ chức khác
+• Mỗi xe một người cầm lái; phiên kết thúc khi trả xe, khi tài xế khác nhận xe, khi tài xế nhận xe khác, hoặc khi xe không di chuyển quá thời gian tự kết thúc của tổ chức (mặc định 2 giờ)
+• Cảnh báo lên portal khi xe chạy mà không ai nhận xe
+• Cảnh báo dành cho tài xế gửi tới tài xế đang nhận xe và portal
+• Lịch sử theo tài xế và theo xe</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -18835,7 +19191,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Không cần</t>
+          <t>Chưa làm</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -18845,210 +19201,213 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>FLT-01, VEH-01</t>
+          <t>DRV-01, VEH-01</t>
         </is>
       </c>
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E1, Quyết định FL-01, Quyết định FL-06</t>
+          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-07, Quyết định DR-08, Quyết định NT-07, Quyết định ID-45</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>F-E1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40.5" customHeight="1">
+          <t>F-E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>FLT-03</t>
+          <t>DRV-03</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Phạm vi quản lý đội xe</t>
+          <t>Lịch làm việc của tài xế</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Giới hạn quản lý đội xe hoặc điều vận chỉ trong một số đội (và mọi đội cấp dưới); không giới hạn thì xem toàn bộ tổ chức.</t>
+          <t>Lập lịch ngày làm việc và ca của tài xế.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Khách hàng lớn phân quyền cho quản lý vùng an toàn trên cùng một tài khoản.</t>
+          <t>Điều vận biết ai đang sẵn sàng và bố trí nghỉ ngơi hợp lý.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Quản trị tổ chức</t>
+          <t>Điều vận, Quản lý đội xe, Tài xế</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>• Giao đội xe cho vai trò cấp đội xe của thành viên
-• Phạm vi được giao bao gồm mọi đội cấp dưới</t>
+          <t>• Lập ca theo tài xế và theo xe
+• Tài xế xem lịch của mình trên app</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
+          <t>Nên có</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa định giá</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>DRV-02</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>• Phạm vi lịch làm việc cần làm rõ (Hùng Võ).</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Bảng dữ liệu IN-55</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="40.5" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>DRV-04</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Định danh tài xế theo ca</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Ghi nhận ai thực sự lái xe trong từng ca, bằng khuôn mặt, thẻ hoặc đăng nhập app, kèm thời điểm bắt đầu và kết thúc ca.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Hồ sơ thời gian lái đúng luật và báo cáo theo tài xế công bằng.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Tài xế, Hệ thống (tự động)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>• Bắt đầu và kết thúc ca bằng khuôn mặt, thẻ hoặc app
+• Cảnh báo khi người lái không phải tài xế được phân công</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
           <t>Bắt buộc</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>P1.0</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Chưa định giá</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Không cần</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>FLT-01, ACC-13</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>Quyết định FL-03</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>FLT-04</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Danh sách &amp; bản đồ toàn đội xe</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Toàn bộ xe của đội trên danh sách và bản đồ realtime, kèm trạng thái vận hành (đang lái, đỗ, sạc, tắt máy), vị trí, xe offline và cảnh báo qua đêm; lọc và tìm kiếm.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Màn hình chính của quản lý đội xe: nắm toàn bộ hoạt động trong một cái nhìn.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Quản lý đội xe, Điều vận</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>• Vị trí và trạng thái mới nhất của mọi xe trong đội
-• Làm nổi bật xe offline và cảnh báo qua đêm
-• Lọc theo trạng thái và tìm theo VIN hoặc biển số</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>FLT-02, MON-02, MON-09</t>
+          <t>DRV-02, SAF-03</t>
         </is>
       </c>
       <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>• Hai tài xế một xe: dùng một app hay hai app?</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E1, Bảng dữ liệu OUT-24</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>F-E1</t>
-        </is>
-      </c>
+          <t>Bảng dữ liệu IN-58</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="n"/>
     </row>
     <row r="9" ht="40.5" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>FLT-05</t>
+          <t>DRV-05</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Vùng địa lý &amp; cảnh báo ra/vào vùng</t>
+          <t>Cảnh báo thời gian lái liên tục</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Vẽ vùng trên bản đồ và nhận cảnh báo khi xe đi vào hoặc ra khỏi vùng.</t>
+          <t>Nhắc tài xế trước khi chạm ngưỡng 4 giờ lái liên tục hoặc 10 giờ/ngày, và gợi ý điểm dừng nghỉ, ưu tiên trạm sạc trên tuyến.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Biết khi xe tới bãi, tới khách hàng hoặc vào khu vực không được phép.</t>
+          <t>Tài xế an toàn hơn và tuân thủ luật về thời gian lái; thời gian nghỉ kết hợp sạc.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe, Điều vận, Hệ thống (tự động)</t>
+          <t>Tài xế, Hệ thống (tự động)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>• Tạo, sửa và xóa vùng đa giác
-• Cảnh báo vào và ra vùng theo từng bản tin
-• Vùng thuộc tổ chức, áp dụng cho các đội được chọn</t>
+          <t>• Thời gian lái liên tục và trong ngày của từng tài xế
+• Cảnh báo trước mỗi ngưỡng
+• Gợi ý điểm dừng nghỉ ưu tiên trạm sạc</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -19073,64 +19432,58 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
           <t>Không cần</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>FLT-02, MON-01, NTF-01</t>
+          <t>DRV-04, MON-12, STN-06</t>
         </is>
       </c>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>PRD F-A5, Quyết định FL-05, deferred.md 86</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>F-A5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
+          <t>Bảng dữ liệu IN-59, Bảng dữ liệu OUT-19</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>FLT-06</t>
+          <t>DRV-06</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Dashboard KPI đội xe</t>
+          <t>Báo cáo tuân thủ thời gian lái &amp; nghỉ</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Km, kWh, kWh/km, chi phí/km, SOH, tỷ lệ sử dụng và cảnh báo, cho cả đội và từng xe, theo kỳ chọn, có xuất file.</t>
+          <t>Theo từng tài xế: số ca vượt 4 giờ liên tục, 10 giờ/ngày và 48 giờ/tuần.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Quản lý biết đội xe điện có vận hành như kế hoạch không.</t>
+          <t>Quản lý đội xe chứng minh tuân thủ và phát hiện tài xế làm việc quá sức.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe, Quản trị tổ chức</t>
+          <t>Quản lý đội xe</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>• Tổng của đội và từng xe
-• Tỷ lệ sử dụng tính từ trạng thái vận hành
-• Số cảnh báo theo kỳ
-• Lọc thời gian và xuất file</t>
+          <t>• Số lần vượt theo tài xế và kỳ báo cáo
+• Xuất báo cáo phục vụ thanh tra</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -19165,52 +19518,49 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>MON-14, MON-07, MON-09, NTF-01</t>
+          <t>DRV-05</t>
         </is>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E2, Bảng dữ liệu OUT-25, deferred.md 72</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>F-E2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1">
+          <t>Bảng dữ liệu OUT-39</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="67.5" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>FLT-07</t>
+          <t>DRV-07</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Báo cáo chi phí vận hành đội xe</t>
+          <t>Báo cáo hiệu quả sạc theo tài xế</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Chi phí điện và chi phí/km theo xe, tài xế và tuyến.</t>
+          <t>Theo tài xế: tỷ lệ kWh sạc giờ thấp điểm hoặc giờ điện tái tạo, chi phí điện/km, tiền tiết kiệm so với sạc giờ cao điểm và xếp hạng trong đội; có khung nhìn của quản lý và của chính tài xế.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Cho thấy tiền đi đâu và tuyến hay tài xế nào tốn kém hơn.</t>
+          <t>Khuyến khích thói quen sạc rẻ và xanh.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Quản lý đội xe, Kế toán</t>
+          <t>Quản lý đội xe, Tài xế</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>• Chi phí/km theo xe, tài xế và tuyến
-• Cộng dồn theo đội xe; xuất CSV</t>
+          <t>• Báo cáo theo tuần và tháng cho từng tài xế
+• Xếp hạng trong đội xe
+• Xuất CSV/PDF</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -19235,7 +19585,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Không cần</t>
+          <t>Chưa làm</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -19245,96 +19595,23 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>MON-14, MON-11, DRV-02</t>
+          <t>CHG-07, PAY-09, DRV-02</t>
         </is>
       </c>
       <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>• Báo cáo có gắn với chương trình thưởng hay thi đua không, hay chỉ để tham khảo?</t>
+        </is>
+      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu OUT-36, PRD F-A6</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="n"/>
-    </row>
-    <row r="12" ht="40.5" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>FLT-08</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Báo cáo sạc &amp; bảo hành theo đội/xe</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Phiên sạc, mức tuân thủ chính sách sạc và trạng thái bảo hành theo đội và xe, lọc được, xuất CSV/PDF.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Quản lý đội xe giữ quyền bảo hành bằng cách sửa thói quen sạc sai.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Quản lý đội xe, Bảo hành</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>• Phiên sạc theo xe và đội
-• Điểm tuân thủ và vi phạm
-• Xuất CSV/PDF</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Bắt buộc</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>P1.0</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Chưa định giá</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>Không cần</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>CHG-07, POL-04</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>PRD F-E3, Bảng dữ liệu OUT-29</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>F-E3</t>
+          <t>PRD F-A8, Bảng dữ liệu OUT-32</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>F-A8</t>
         </is>
       </c>
     </row>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -9576,7 +9576,7 @@
       </c>
       <c r="Q7" s="3" t="n"/>
     </row>
-    <row r="8" ht="40.5" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>SAF-04</t>
@@ -9647,7 +9647,7 @@
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-57, Bảng dữ liệu OUT-21, Điều kiện tiên quyết 7</t>
+          <t>Bảng dữ liệu IN-57, Bảng dữ liệu OUT-21, Điều kiện tiên quyết 7, deferred.md 89</t>
         </is>
       </c>
       <c r="Q8" s="3" t="n"/>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="Q6" s="3" t="n"/>
     </row>
-    <row r="7" ht="40.5" customHeight="1">
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>VEH-03</t>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Lưu thông số từng dòng xe (EVT-262/400/825): dung lượng pin, đường cong tiêu thụ theo tải và đường cơ sở xe diesel tương đương.</t>
+          <t>Lưu thông số từng dòng xe (EVT-262/400/825): dung lượng pin, đường cong tiêu thụ theo tải (chỉ số liệu xe điện).</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -15159,7 +15159,7 @@
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-32, Bảng dữ liệu IN-34, deferred.md 61, Quyết định VH-08</t>
+          <t>Bảng dữ liệu IN-32, Bảng dữ liệu IN-34, deferred.md 61, Quyết định VH-08, Quyết định VH-15</t>
         </is>
       </c>
       <c r="Q7" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -15465,7 +15465,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="67.5" customHeight="1">
+    <row r="5" ht="94.5" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>BAT-01</t>
@@ -15495,7 +15495,8 @@
         <is>
           <t>• Danh mục dòng pin: hóa học (LFP/CATL), dung lượng thiết kế, điện áp, cấu trúc
 • Từng pin: số serial, dòng pin, chủ sở hữu (có thể khác chủ xe), trạng thái kèm lý do
-• Mỗi xe một pin; lịch sử pin đã được lắp trên xe nào</t>
+• Mỗi xe một pin; lịch sử pin đã được lắp trên xe nào
+• Pin thuộc bên bán chuyển sang bên mua khi xe được bán</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -15534,10 +15535,14 @@
         </is>
       </c>
       <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>• BMS của xe có gửi số serial của pin qua T-Box không? Nếu có, việc thay pin không được ghi nhận có thể phát cảnh báo.</t>
+        </is>
+      </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-33, Quyết định VH-08, Quyết định VH-13, deferred.md 87, deferred.md 88</t>
+          <t>Bảng dữ liệu IN-33, Quyết định VH-08, Quyết định VH-13, Quyết định VH-16, deferred.md 87, deferred.md 88</t>
         </is>
       </c>
       <c r="Q5" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -12323,7 +12323,7 @@
       <c r="O19" s="3" t="n"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>Quyết định ID-11, Quyết định DM-18</t>
+          <t>Quyết định ID-11, Quyết định DM-24</t>
         </is>
       </c>
       <c r="Q19" s="3" t="n"/>
@@ -15763,7 +15763,7 @@
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-32, Quyết định VH-09, Quyết định VH-14</t>
+          <t>Bảng dữ liệu IN-32, Quyết định VH-09, Quyết định VH-14, Quyết định VH-18</t>
         </is>
       </c>
       <c r="Q5" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -15912,7 +15912,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="40.5" customHeight="1">
+    <row r="5" ht="67.5" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>DEV-01</t>
@@ -15941,7 +15941,8 @@
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>• Tạo, sửa, tìm kiếm và ngừng sử dụng thiết bị
-• Serial không trùng; thiết bị ngừng dùng vẫn giữ lịch sử</t>
+• Serial không trùng; thiết bị ngừng dùng vẫn giữ lịch sử
+• Mỗi thiết bị có chủ sở hữu riêng, là chủ xe hoặc G3; thiết bị thuộc bên bán đi theo xe khi bán xe</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -15979,7 +15980,7 @@
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-19, Bảng dữ liệu IN-20, Bảng dữ liệu IN-21, PRD F-G1</t>
+          <t>Bảng dữ liệu IN-19, Bảng dữ liệu IN-20, Bảng dữ liệu IN-21, PRD F-G1, Quyết định TX-07</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -15980,7 +15980,7 @@
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-19, Bảng dữ liệu IN-20, Bảng dữ liệu IN-21, PRD F-G1, Quyết định TX-07</t>
+          <t>Bảng dữ liệu IN-19, Bảng dữ liệu IN-20, Bảng dữ liệu IN-21, PRD F-G1, Quyết định TX-07, Quyết định TX-08</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -16060,7 +16060,7 @@
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-19, PRD F-G1, Quyết định TX-02, Quyết định TX-03</t>
+          <t>Bảng dữ liệu IN-19, PRD F-G1, Quyết định TX-02, Quyết định TX-08</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -16396,7 +16396,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="54" customHeight="1">
+    <row r="11" ht="81" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>DEV-07</t>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Đẩy thay đổi cấu hình (chu kỳ gửi, ngưỡng cảnh báo tại xe) tới một thiết bị hoặc cả đội xe, xác nhận đã áp dụng và cho phép khôi phục.</t>
+          <t>Đặt chu kỳ gửi cho các xe của một tổ chức và đẩy xuống thiết bị, xem thiết bị nào đã áp dụng và cho phép khôi phục.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -16424,8 +16424,8 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>• Đẩy tới một thiết bị hoặc mọi thiết bị của đội xe, có kết quả từng thiết bị
-• Xác nhận thiết bị đã áp dụng thay đổi
+          <t>• Một chu kỳ gửi cho mỗi tổ chức, đẩy xuống mọi thiết bị trên xe của tổ chức và xuống thiết bị khi được gắn lên xe, có kết quả từng thiết bị
+• Xác nhận: thiết bị báo chu kỳ đang dùng; nếu khác nghĩa là lần đẩy chưa được áp dụng
 • Khôi phục và lịch sử mọi lệnh</t>
         </is>
       </c>
@@ -16468,7 +16468,7 @@
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>PRD F-J2, deferred.md 52, deferred.md 53, deferred.md 56, deferred.md 59</t>
+          <t>PRD F-J2, deferred.md 52, deferred.md 53, deferred.md 56, deferred.md 59, Quyết định TX-09</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -16150,7 +16150,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
+    <row r="8" ht="67.5" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>DEV-04</t>
@@ -16178,7 +16178,8 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>• Cờ online và im lặng tính từ dữ liệu mới nhất
+          <t>• Lịch sử sức khỏe theo từng thiết bị (sóng, nguồn điện, bộ nhớ, SIM) để xem xu hướng
+• Cờ online và im lặng tính từ dữ liệu mới nhất
 • Trạng thái SIM/ICCID, data, nguồn, bộ nhớ và GNSS
 • Tỷ lệ thiết bị khỏe trên toàn mạng</t>
         </is>
@@ -16222,7 +16223,7 @@
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>PRD F-J1, Bảng dữ liệu IN-21, Bảng dữ liệu IN-22, Bảng dữ liệu OUT-55, deferred.md 50</t>
+          <t>PRD F-J1, Bảng dữ liệu IN-21, Bảng dữ liệu IN-22, Bảng dữ liệu OUT-55, deferred.md 50, Quyết định TX-10</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -14933,7 +14933,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="108" customHeight="1">
+    <row r="5" ht="135" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>VEH-01</t>
@@ -14963,7 +14963,7 @@
         <is>
           <t>• Tạo, sửa, tìm kiếm và ngừng sử dụng xe
 • VIN và biển số không trùng trong các xe đang dùng và đều sửa được (nhập nhầm, biển số theo chủ xe); lưu lịch sử thay đổi kèm lý do
-• Trạng thái phục vụ do con người đặt: đang phục vụ, đang bảo dưỡng, đã rời hệ thống, kèm lý do; xe nhàn rỗi hay mất tín hiệu được hiển thị từ dữ liệu, không lưu
+• Trạng thái phục vụ: đang phục vụ hoặc không phục vụ (ở xưởng, không dùng), kèm lý do; xe rời hệ thống được gỡ khỏi hệ thống kèm lý do và vẫn giữ dữ liệu; xe nhàn rỗi hay mất tín hiệu được hiển thị từ dữ liệu, không lưu
 • Lọc theo trạng thái, dòng xe, chủ sở hữu và đội xe</t>
         </is>
       </c>
@@ -15002,7 +15002,7 @@
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-32, PRD F-F2, Quyết định VH-05, Quyết định VH-07</t>
+          <t>Bảng dữ liệu IN-32, PRD F-F2, Quyết định VH-05, Quyết định VH-07, Quyết định DM-25</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -17357,7 +17357,7 @@
       </c>
       <c r="Q12" s="3" t="n"/>
     </row>
-    <row r="13" ht="40.5" customHeight="1">
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MON-09</t>
@@ -17425,10 +17425,14 @@
         </is>
       </c>
       <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>• Hợp đồng dữ liệu thiết bị chưa có tín hiệu khóa điện, cấp số, phanh hay chân ga; nhà sản xuất phải mở các tín hiệu này (điều kiện tiên quyết 1).</t>
+        </is>
+      </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-15, Bảng dữ liệu OUT-24</t>
+          <t>Bảng dữ liệu IN-15, Bảng dữ liệu OUT-24, Quyết định TM-16</t>
         </is>
       </c>
       <c r="Q13" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -7717,7 +7717,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="67.5" customHeight="1">
+    <row r="5" ht="108" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>SUP-01</t>
@@ -7748,7 +7748,8 @@
           <t>• Tạo yêu cầu với ngữ cảnh xe tự động và ảnh
 • Vòng đời mở → đã tiếp nhận → đã xử lý → đóng
 • Hạn SLA chốt khi tạo
-• Khiếu nại và báo lỗi phần mềm là các loại yêu cầu</t>
+• Khiếu nại và báo lỗi phần mềm là các loại yêu cầu
+• Yêu cầu dữ liệu là một loại yêu cầu: dữ liệu lái xe của chủ xe chỉ được cung cấp khi chủ xe đồng ý bằng văn bản hoặc có yêu cầu của cơ quan có thẩm quyền, và được ghi nhật ký</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -7794,7 +7795,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>PRD F-I1, Bảng dữ liệu IN-51, Bảng dữ liệu OUT-61</t>
+          <t>PRD F-I1, Bảng dữ liệu IN-51, Bảng dữ liệu OUT-61, Quyết định DR-11</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -19063,7 +19064,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1">
+    <row r="5" ht="81" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>DRV-01</t>
@@ -19135,7 +19136,7 @@
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E4, Bảng dữ liệu IN-37, Bảng dữ liệu OUT-34, Quyết định ID-13, Quyết định DR-03</t>
+          <t>PRD F-E4, Bảng dữ liệu IN-37, Bảng dữ liệu OUT-34, Quyết định ID-13, Quyết định DR-03, Quyết định DR-09, Quyết định DR-10</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -19144,7 +19145,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="189" customHeight="1">
+    <row r="6" ht="229.5" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>DRV-02</t>
@@ -19177,7 +19178,7 @@
 • Mỗi xe một người cầm lái; phiên kết thúc khi trả xe, khi tài xế khác nhận xe, khi tài xế nhận xe khác, hoặc khi xe không di chuyển quá thời gian tự kết thúc của tổ chức (mặc định 2 giờ)
 • Cảnh báo lên portal khi xe chạy mà không ai nhận xe
 • Cảnh báo dành cho tài xế gửi tới tài xế đang nhận xe và portal
-• Lịch sử theo tài xế và theo xe</t>
+• Lịch sử đầy đủ theo tài xế và theo xe trên portal; tài xế chỉ xem bản tóm tắt các phiên của mình trên ứng dụng (không có lộ trình hay địa điểm, không xuất dữ liệu)</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -19219,7 +19220,7 @@
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-07, Quyết định DR-08, Quyết định NT-07, Quyết định ID-45</t>
+          <t>PRD F-E4, Bảng dữ liệu IN-55, Bảng dữ liệu OUT-34, Quyết định DR-07, Quyết định DR-08, Quyết định DR-10, Quyết định DR-11, Quyết định NT-07, Quyết định ID-45</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -19388,7 +19389,7 @@
       </c>
       <c r="Q8" s="3" t="n"/>
     </row>
-    <row r="9" ht="40.5" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>DRV-05</t>
@@ -19457,7 +19458,11 @@
         </is>
       </c>
       <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>• Thời gian lái qua nhiều tổ chức: ai được xem tổng thời gian lái khi tài xế lái xe của nhiều tổ chức (câu hỏi mở 8, cố vấn pháp lý).</t>
+        </is>
+      </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
           <t>Bảng dữ liệu IN-59, Bảng dữ liệu OUT-19</t>
@@ -19465,7 +19470,7 @@
       </c>
       <c r="Q9" s="3" t="n"/>
     </row>
-    <row r="10" ht="40.5" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>DRV-06</t>
@@ -19533,7 +19538,11 @@
         </is>
       </c>
       <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>• Thời gian lái qua nhiều tổ chức: ai được xem tổng thời gian lái khi tài xế lái xe của nhiều tổ chức (câu hỏi mở 8, cố vấn pháp lý).</t>
+        </is>
+      </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
           <t>Bảng dữ liệu OUT-39</t>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -4910,7 +4910,11 @@
         </is>
       </c>
       <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>• Xe khách vãng lai (chưa đăng ký với chúng ta) không có hồ sơ xe: ứng dụng có hỏi biển số khi bắt đầu sạc bằng QR không?</t>
+        </is>
+      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
           <t>deferred.md 62, Quyết định CO-12, Bảng dữ liệu IN-27</t>
@@ -4993,7 +4997,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Quyết định CO-12, Quyết định CO-06</t>
+          <t>Quyết định CO-12, Quyết định CO-06, Quyết định CO-13, deferred.md 90</t>
         </is>
       </c>
       <c r="Q12" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -1095,7 +1095,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="27" customHeight="1">
+    <row r="12" ht="67.5" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>10</v>
       </c>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Trạm và trụ sạc, trạng thái realtime qua OCPP, sự cố, bản đồ trạm, hàng đợi, đặt chỗ và phân tải.</t>
+          <t>Trạm và trụ sạc, trạng thái realtime qua OCPP, sự cố, bản đồ trạm, hàng đợi, đặt chỗ và phân tải. Trong danh mục này "trạm" là nơi tài xế tới (bảng charging_locations) và "trụ" là một trụ sạc OCPP (bảng charging_stations), theo CS-09.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -2925,10 +2925,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="229.5" customHeight="1">
+    <row r="2" ht="526.5" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Trạm và trụ sạc, trạng thái realtime qua OCPP, sự cố, bản đồ trạm, hàng đợi, đặt chỗ và phân tải.</t>
+          <t>Trạm và trụ sạc, trạng thái realtime qua OCPP, sự cố, bản đồ trạm, hàng đợi, đặt chỗ và phân tải. Trong danh mục này "trạm" là nơi tài xế tới (bảng charging_locations) và "trụ" là một trụ sạc OCPP (bảng charging_stations), theo CS-09.</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1">
+    <row r="5" ht="67.5" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>STN-01</t>
@@ -3055,7 +3055,7 @@
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>• Tạo, sửa, tìm kiếm và ngừng hoạt động trạm
-• Đơn vị quản lý và đầu mối sự cố của từng trạm
+• Tổ chức sở hữu của từng trạm; cảnh báo trụ sạc gửi tới nhân viên vận hành của tổ chức đó; trạm mở 24/7, trạm tạm đóng được đánh dấu ngừng hoạt động kèm lý do
 • Xem mọi trạm trên bản đồ</t>
         </is>
       </c>
@@ -3094,7 +3094,7 @@
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>PRD F-C1, Bảng dữ liệu IN-25</t>
+          <t>PRD F-C1, Bảng dữ liệu IN-25, Quyết định CS-09, Quyết định CS-10, Quyết định CS-11</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -3658,7 +3658,7 @@
       <c r="O12" s="3" t="n"/>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>PRD F-C7, Bảng dữ liệu IN-28, Bảng dữ liệu OUT-53, NF-20</t>
+          <t>PRD F-C7, Bảng dữ liệu IN-28, Bảng dữ liệu OUT-53, NF-20, deferred.md 91</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu OUT-10</t>
+          <t>Bảng dữ liệu OUT-10, Quyết định CS-10</t>
         </is>
       </c>
       <c r="Q16" s="3" t="n"/>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="81" customHeight="1">
+    <row r="5" ht="121.5" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>CHG-01</t>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Tài xế quét mã QR trên trụ, hệ thống bắt đầu sạc từ xa, và app hiển thị tiến trình sạc tới khi dừng.</t>
+          <t>Tài xế quét mã QR trên màn hình trụ; ứng dụng xác thực và kiểm tra ví, tài xế bắt đầu và dừng sạc trên trụ, và ứng dụng hiển thị tiến trình.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -4391,10 +4391,11 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>• Quét mã QR của súng sạc và xác nhận
+          <t>• Quét mã QR trên màn hình trụ sạc; ứng dụng xác thực tài xế và kiểm tra ví
+• Tài xế chọn súng và bắt đầu sạc trên màn hình trụ
 • Ghi nhận ai bắt đầu sạc và tổ chức nào trả tiền
 • Tiến trình realtime: kWh, % pin, công suất, chi phí tạm tính
-• Dừng từ app hoặc tại trụ
+• Dừng trên màn hình trụ (hoặc do xe tự dừng); ứng dụng không gửi lệnh
 • Giữ phiên và tính tiền sau nếu sóng yếu</t>
         </is>
       </c>
@@ -4434,10 +4435,14 @@
         </is>
       </c>
       <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>• Nhà cung cấp cần xác nhận: nội dung mã QR, chọn súng trên màn hình sau khi xác thực từ xa, AuthorizeRemoteTxRequests (câu hỏi mở 4).</t>
+        </is>
+      </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>PRD F-H1, Quyết định CO-12</t>
+          <t>PRD F-H1, Quyết định CO-12, Quyết định CO-13, Quyết định CO-14</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -3103,7 +3103,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="40.5" customHeight="1">
+    <row r="6" ht="54" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>STN-02</t>
@@ -3174,7 +3174,7 @@
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Quyết định CS-02, Quyết định CS-03, deferred.md 80</t>
+          <t>Quyết định CS-02, Quyết định CS-03, deferred.md 80, Quyết định CS-16, Quyết định CS-17</t>
         </is>
       </c>
       <c r="Q6" s="3" t="n"/>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>PRD F-C4, Bảng dữ liệu IN-54</t>
+          <t>PRD F-C4, Bảng dữ liệu IN-54, deferred.md 92</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="67.5" customHeight="1">
+    <row r="5" ht="94.5" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>WAR-01</t>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Lưu mọi bảo hành của xe, pin và thiết bị trên xe: thời hạn, các giới hạn như quãng đường hay số chu kỳ sạc, và trạng thái, kèm lý do khi bảo hành bị hủy.</t>
+          <t>Lưu mọi bảo hành của xe, pin, thiết bị trên xe và của trụ sạc: thời hạn, các giới hạn như quãng đường, số chu kỳ sạc, điện năng đã cấp hay số phiên sạc, và trạng thái, kèm lý do khi bảo hành bị hủy.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -15731,7 +15731,8 @@
         <is>
           <t>• Bảo hành theo từng xe, pin và thiết bị, đặt riêng cho từng xe, mỗi bảo hành có thời hạn và giới hạn riêng
 • Hết hạn được tính từ ngày và bộ đếm của xe hoặc pin; hủy bảo hành kèm lý do và lịch sử
-• Bảo hành của pin đi theo pin sang xe khác</t>
+• Bảo hành của pin đi theo pin sang xe khác
+• Bảo hành trụ sạc giới hạn theo điện năng đã cấp (kWh) và số phiên sạc, nhận diện theo số serial đã đăng ký</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -15773,7 +15774,7 @@
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-32, Quyết định VH-09, Quyết định VH-14, Quyết định VH-18</t>
+          <t>Bảng dữ liệu IN-32, Quyết định VH-09, Quyết định VH-14, Quyết định VH-18, Quyết định VH-19, Quyết định CS-14</t>
         </is>
       </c>
       <c r="Q5" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -4442,7 +4442,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>PRD F-H1, Quyết định CO-12, Quyết định CO-13, Quyết định CO-14</t>
+          <t>PRD F-H1, Quyết định CO-12, Quyết định CO-13, Quyết định CO-14, Quyết định CE-10, Quyết định CE-11</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -4524,7 +4524,7 @@
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>PRD F-B2, Bảng dữ liệu IN-27, NF-11, deferred.md 27</t>
+          <t>PRD F-B2, Bảng dữ liệu IN-27, NF-11, deferred.md 27, Quyết định CE-10, Quyết định CE-12</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>deferred.md 62, Quyết định CO-12, Bảng dữ liệu IN-27</t>
+          <t>deferred.md 62, Quyết định CO-12, Bảng dữ liệu IN-27, Quyết định CE-13</t>
         </is>
       </c>
       <c r="Q11" s="3" t="n"/>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Quyết định CO-12, Quyết định CO-06, Quyết định CO-13, deferred.md 90</t>
+          <t>Quyết định CO-12, Quyết định CE-11, Quyết định CO-13, deferred.md 90</t>
         </is>
       </c>
       <c r="Q12" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -4524,7 +4524,7 @@
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>PRD F-B2, Bảng dữ liệu IN-27, NF-11, deferred.md 27, Quyết định CE-10, Quyết định CE-12</t>
+          <t>PRD F-B2, Bảng dữ liệu IN-27, NF-11, deferred.md 27, Quyết định CE-10, Quyết định CE-12, Quyết định CE-14</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -4451,7 +4451,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="67.5" customHeight="1">
+    <row r="6" ht="81" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>CHG-02</t>
@@ -4524,7 +4524,7 @@
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>PRD F-B2, Bảng dữ liệu IN-27, NF-11, deferred.md 27, Quyết định CE-10, Quyết định CE-12, Quyết định CE-14</t>
+          <t>PRD F-B2, Bảng dữ liệu IN-27, NF-11, deferred.md 27, Quyết định CE-10, Quyết định CE-12, Quyết định CE-14, Quyết định CE-15</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -3824,7 +3824,7 @@
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Quyết định CO-12, deferred.md 74</t>
+          <t>Quyết định CO-12, deferred.md 74, Quyết định CS-20</t>
         </is>
       </c>
       <c r="Q14" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -6248,7 +6248,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="40.5" customHeight="1">
+    <row r="11" ht="81" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>PAY-07</t>
@@ -6319,7 +6319,8 @@
       <c r="N11" s="3" t="n"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>• Quy tắc tiền cọc: cọc 300 nghìn, rút thì xử lý thế nào? (ghi chú bảng dữ liệu)</t>
+          <t>• Quy tắc tiền cọc: cọc 300 nghìn, rút thì xử lý thế nào? (ghi chú bảng dữ liệu)
+• Giới hạn pháp lý của số dư trả trước: chuyển, rút, hoàn tiền, cách gọi tên khi giới thiệu (câu hỏi mở 11 trong nhật ký quyết định).</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -6333,7 +6334,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="40.5" customHeight="1">
+    <row r="12" ht="67.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>PAY-08</t>
@@ -6403,7 +6404,7 @@
       <c r="N12" s="3" t="n"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>• Khi tài xế của đội xe đi sạc, ai trả tiền: tài xế hay doanh nghiệp? (quyết định mở D5)</t>
+          <t>• Thanh toán doanh nghiệp đến sau khi ra mắt: khi ra mắt mỗi người trả bằng ví của chính mình (BL-13); phương thức doanh nghiệp nào làm trước (ví tổ chức, hóa đơn tháng) vẫn cần chọn.</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -17529,7 +17529,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
+    <row r="15" ht="121.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>MON-11</t>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Chia luồng dữ liệu thành các chuyến (bắt đầu, điểm dừng, kết thúc) kèm quãng đường, năng lượng và thời gian từng chuyến; mỗi chuyến có mã để sau này gắn với đơn hàng.</t>
+          <t>Chuyến do quản lý đội xe lập kế hoạch (từ A tới B, giờ dự kiến, tài xế, xe) và được tài xế thực hiện bằng nút Bắt đầu và Kết thúc trên ứng dụng, kèm quãng đường, năng lượng và thời gian từng chuyến; mỗi chuyến có mã để sau này gắn với đơn hàng.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -17557,7 +17557,9 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>• Quy tắc xác định chuyến thống nhất với vận hành
+          <t>• Lập kế hoạch chuyến: từ A tới B, giờ đi và giờ đến dự kiến, tài xế và xe (không bắt buộc với tài xế tự chạy)
+• Tài xế bấm Bắt đầu và Kết thúc sau khi nhận xe; ghi vị trí T-Box, số km và phần trăm pin ở hai đầu
+• Nhắc khi xe chạy mà chưa bắt đầu chuyến; chuyến đang mở tự đóng khi phiên lái kết thúc
 • Km, kWh, kWh/km và chi phí theo chuyến
 • Lịch sử chuyến và chi phí trên app tài xế</t>
         </is>
@@ -17594,18 +17596,14 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>MON-09</t>
+          <t>MON-09, DRV-02</t>
         </is>
       </c>
       <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>• Thế nào là một chuyến? (bộ phận vận hành định nghĩa)</t>
-        </is>
-      </c>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-14, Bảng dữ liệu OUT-17, Bảng dữ liệu IN-40, deferred.md 46</t>
+          <t>Bảng dữ liệu IN-14, Bảng dữ liệu OUT-17, Bảng dữ liệu IN-40, deferred.md 46, Quyết định DR-12</t>
         </is>
       </c>
       <c r="Q15" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -1347,10 +1347,10 @@
         <v>8</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
@@ -1721,10 +1721,10 @@
         <v>178</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>9</v>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="40.5" customHeight="1">
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>NTF-03</t>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>P1.0</t>
+          <t>P1.1</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -7194,7 +7194,7 @@
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>PRD F-F3, Bảng dữ liệu IN-47, Quyết định BL-05</t>
+          <t>PRD F-F3, Bảng dữ liệu IN-47, Quyết định BL-05, Quyết định NT-11, deferred.md 96</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -1347,10 +1347,10 @@
         <v>8</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
@@ -1721,10 +1721,10 @@
         <v>178</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>9</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>P1.0</t>
+          <t>P1.1</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -7502,7 +7502,7 @@
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Bảng dữ liệu IN-47</t>
+          <t>Bảng dữ liệu IN-47, Quyết định NT-12</t>
         </is>
       </c>
       <c r="Q11" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -4363,7 +4363,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="121.5" customHeight="1">
+    <row r="5" ht="135" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>CHG-01</t>
@@ -4395,7 +4395,7 @@
 • Tài xế chọn súng và bắt đầu sạc trên màn hình trụ
 • Ghi nhận ai bắt đầu sạc và tổ chức nào trả tiền
 • Tiến trình realtime: kWh, % pin, công suất, chi phí tạm tính
-• Dừng trên màn hình trụ (hoặc do xe tự dừng); ứng dụng không gửi lệnh
+• Dừng trên màn hình trụ (hoặc do xe tự dừng); ứng dụng cũng có thể gửi lệnh dừng từ xa cho người đã bắt đầu sạc
 • Giữ phiên và tính tiền sau nếu sóng yếu</t>
         </is>
       </c>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -636,7 +636,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>0/22</t>
+          <t>16/22</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -690,7 +690,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -744,7 +744,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -798,7 +798,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>0/18</t>
+          <t>3/18</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1022,7 +1022,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1076,7 +1076,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>4/8</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>0/15</t>
+          <t>6/15</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1190,7 +1190,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -1300,7 +1300,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>0/13</t>
+          <t>4/13</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -1356,7 +1356,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>0/176</t>
+          <t>57/176</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -2312,7 +2312,11 @@
           <t>ACC-01</t>
         </is>
       </c>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>fleets</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -2374,7 +2378,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -2392,7 +2396,11 @@
           <t>FLT-01, VEH-01</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>fleet_vehicle_memberships</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2405,7 +2413,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="40.5" customHeight="1">
+    <row r="7" ht="94.5" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>FLT-03</t>
@@ -2454,7 +2462,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -2472,8 +2480,16 @@
           <t>FLT-01, ACC-13</t>
         </is>
       </c>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>fleet_user_assignments</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>• Giới hạn đội xe đã áp dụng cho đội xe, dữ liệu xe, danh sách xe, phiên lái, chuyến đi và người nhận cảnh báo; chưa áp dụng cho danh sách thông báo của tổ chức, ca hỗ trợ, phiên sạc, hóa đơn, pin, bảo hành và các API chi tiết theo ID (xem Known issues trong kế hoạch refactor).</t>
+        </is>
+      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Quyết định FL-03</t>
@@ -2531,7 +2547,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -2549,7 +2565,11 @@
           <t>FLT-02, MON-02, MON-09</t>
         </is>
       </c>
-      <c r="N8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>fleets, fleet_vehicle_memberships, telemetry</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2612,7 +2632,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -2630,7 +2650,11 @@
           <t>FLT-02, MON-01, NTF-01</t>
         </is>
       </c>
-      <c r="N9" s="3" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>geofences</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -3076,7 +3100,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -3090,7 +3114,11 @@
         </is>
       </c>
       <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>charging_locations, charging_stations, charging_evses, charging_connectors</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -3103,7 +3131,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="67.5" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>STN-02</t>
@@ -3152,7 +3180,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -3170,8 +3198,16 @@
           <t>STN-01</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>charging_stations, charging_evses, charging_connectors, charging_station_state</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>• Đặt trụ INACTIVE chỉ có hiệu lực ở lần bắt tay kết nối kế tiếp; trụ đang kết nối vẫn giữ kết nối đến khi nối lại (deferred.md 74).</t>
+        </is>
+      </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t>Quyết định CS-02, Quyết định CS-03, deferred.md 80, Quyết định CS-16, Quyết định CS-17</t>
@@ -3179,7 +3215,7 @@
       </c>
       <c r="Q6" s="3" t="n"/>
     </row>
-    <row r="7" ht="67.5" customHeight="1">
+    <row r="7" ht="135" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>STN-03</t>
@@ -3230,7 +3266,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -3248,7 +3284,11 @@
           <t>STN-02</t>
         </is>
       </c>
-      <c r="N7" s="3" t="n"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>charging_stations, charging_station_state, charging_ocpp_messages, charging_station_configuration_captures, charging_station_configuration_entries</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
           <t>• Còn thiếu tài liệu từ nhà cung cấp: hướng dẫn tích hợp, bảng mã lỗi, thông tin công tơ, TLS/xác thực (câu hỏi mở 4).
@@ -3316,7 +3356,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -3334,8 +3374,16 @@
           <t>STN-03</t>
         </is>
       </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>charging_connector_state, charging_connectors</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>• Trạng thái được đánh dấu cũ khi trụ ngoại tuyến nhưng vẫn trả giá trị báo cáo cuối; quy tắc hết hạn thật là deferred.md 76.</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
           <t>PRD F-C2, Bảng dữ liệu IN-26, Bảng dữ liệu OUT-48, NF-02, deferred.md 76</t>
@@ -3802,7 +3850,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -3820,7 +3868,11 @@
           <t>STN-03</t>
         </is>
       </c>
-      <c r="N14" s="3" t="n"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>charging_station_commands</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3954,7 +4006,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -3972,7 +4024,11 @@
           <t>STN-01, PAY-09</t>
         </is>
       </c>
-      <c r="N16" s="3" t="n"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>charging_locations, charging_location_access</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t>• Trụ riêng (của mỏ, không công cộng) tính tiền thế nào? Bảng dữ liệu ghi 'phương án riêng'.</t>
@@ -4416,7 +4472,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -4434,7 +4490,11 @@
           <t>STN-10, CHG-02, ACC-04</t>
         </is>
       </c>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>charging_sessions, charging_station_commands</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
           <t>• Nhà cung cấp cần xác nhận: nội dung mã QR, chọn súng trên màn hình sau khi xác thực từ xa, AuthorizeRemoteTxRequests (câu hỏi mở 4).</t>
@@ -4502,7 +4562,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -4520,7 +4580,11 @@
           <t>STN-03</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>charging_sessions, charging_session_measurements</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -4533,7 +4597,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="27" customHeight="1">
+    <row r="7" ht="40.5" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>CHG-03</t>
@@ -4582,7 +4646,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -4600,7 +4664,11 @@
           <t>CHG-02, PAY-10</t>
         </is>
       </c>
-      <c r="N7" s="3" t="n"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>charging_sessions, charging_session_bills</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -4658,7 +4726,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -4676,7 +4744,11 @@
           <t>CHG-02, CHG-07</t>
         </is>
       </c>
-      <c r="N8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>charging_sessions</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -4689,7 +4761,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="27" customHeight="1">
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>CHG-05</t>
@@ -4738,7 +4810,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -4756,8 +4828,16 @@
           <t>CHG-07</t>
         </is>
       </c>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>charging_sessions, charging_session_measurements</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>• Đã có điện năng theo phiên và theo trụ; chưa có tổng theo tổ chức trong kỳ, và chủ trụ chỉ thấy phiên do tổ chức mình trả tiền.</t>
+        </is>
+      </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
           <t>PRD F-C6, Bảng dữ liệu OUT-51, deferred.md 62</t>
@@ -4896,7 +4976,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -4914,7 +4994,11 @@
           <t>CHG-01, DRV-02</t>
         </is>
       </c>
-      <c r="N11" s="3" t="n"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>charging_sessions, driving_sessions</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t>• Xe khách vãng lai (chưa đăng ký với chúng ta) không có hồ sơ xe: ứng dụng có hỏi biển số khi bắt đầu sạc bằng QR không?</t>
@@ -6167,7 +6251,7 @@
       </c>
       <c r="Q9" s="3" t="n"/>
     </row>
-    <row r="10" ht="40.5" customHeight="1">
+    <row r="10" ht="67.5" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>PAY-06</t>
@@ -6217,7 +6301,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -6235,8 +6319,16 @@
           <t>CHG-01, CHG-03</t>
         </is>
       </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>payments, wallets, charging_session_bills</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>• Cấu trúc mã VietQR theo chuẩn NAPAS nhưng chưa được quét thử bằng app ngân hàng thật; cần kiểm chứng với tài khoản thật đầu tiên. Thông báo ngân hàng đang dùng nhà cung cấp giả.</t>
+        </is>
+      </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
           <t>PRD F-H1, Bảng dữ liệu IN-45, NF-05</t>
@@ -6298,7 +6390,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -6316,7 +6408,11 @@
           <t>PAY-06</t>
         </is>
       </c>
-      <c r="N11" s="3" t="n"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>wallets, wallet_transactions, payments</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t>• Quy tắc tiền cọc: cọc 300 nghìn, rút thì xử lý thế nào? (ghi chú bảng dữ liệu)
@@ -6468,7 +6564,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -6486,7 +6582,11 @@
           <t>STN-01, STN-13</t>
         </is>
       </c>
-      <c r="N13" s="3" t="n"/>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>tariffs, tariff_versions</t>
+        </is>
+      </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
           <t>• Ai sở hữu biểu giá (G3 Energy hay G3 Network), và chênh lệch giá cao điểm/thấp điểm bao nhiêu?</t>
@@ -6503,7 +6603,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14" ht="40.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>PAY-10</t>
@@ -6552,7 +6652,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -6570,7 +6670,11 @@
           <t>PAY-09, CHG-02</t>
         </is>
       </c>
-      <c r="N14" s="3" t="n"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>charging_session_bills, tariff_versions</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -7016,7 +7120,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -7030,7 +7134,11 @@
         </is>
       </c>
       <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>notifications, notification_recipients</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -7043,7 +7151,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="40.5" customHeight="1">
+    <row r="6" ht="54" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>NTF-02</t>
@@ -7092,7 +7200,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -7110,8 +7218,16 @@
           <t>NTF-01, ACC-16, NTF-06</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>notification_recipients, user_sessions</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>• Thông báo đẩy đi qua nhà cung cấp giả và được gửi trong giao dịch của bên tạo; nhà cung cấp thật cần outbox gửi sau khi commit (deferred.md 100).</t>
+        </is>
+      </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t>PRD F-F3, Quyết định ID-19, deferred.md 41</t>
@@ -7252,7 +7368,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -7270,8 +7386,16 @@
           <t>NTF-06</t>
         </is>
       </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>notification_recipients, notifications</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>• E-mail đi qua nhà cung cấp giả và được gửi trong giao dịch của bên tạo (deferred.md 100).</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
           <t>Quyết định NT-03</t>
@@ -7328,7 +7452,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -7346,7 +7470,11 @@
           <t>NTF-06</t>
         </is>
       </c>
-      <c r="N9" s="3" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>organization_notification_settings</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -7404,7 +7532,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -7422,7 +7550,11 @@
           <t>ACC-14, ACC-15</t>
         </is>
       </c>
-      <c r="N10" s="3" t="n"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>notifications, notification_recipients</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -11220,7 +11352,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -11234,7 +11366,11 @@
         </is>
       </c>
       <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>organizations, organization_settings</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -11296,7 +11432,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -11314,7 +11450,11 @@
           <t>ACC-01</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>organizations, users</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -11373,7 +11513,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -11387,7 +11527,11 @@
         </is>
       </c>
       <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>users, user_state, user_credentials</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -11454,7 +11598,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -11472,7 +11616,11 @@
           <t>ACC-03</t>
         </is>
       </c>
-      <c r="N8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>user_credentials, user_sessions, user_state</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -11531,7 +11679,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -11549,7 +11697,11 @@
           <t>ACC-03, NTF-03</t>
         </is>
       </c>
-      <c r="N9" s="3" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>one_time_codes</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -11609,7 +11761,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -11627,8 +11779,16 @@
           <t>ACC-05</t>
         </is>
       </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>one_time_codes, user_credentials, users</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>• Chưa có bước xác minh thêm khi đặt lại mật khẩu tài khoản lâu không hoạt động (SĐT bị cấp lại) và giới hạn tần suất theo thiết bị (deferred.md 99).</t>
+        </is>
+      </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
           <t>Quyết định ID-16, Rà soát thiết kế 2026-10-03</t>
@@ -11687,7 +11847,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -11705,7 +11865,11 @@
           <t>ACC-01, ACC-05, ACC-17, PAY-02</t>
         </is>
       </c>
-      <c r="N11" s="3" t="n"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>users, organizations, memberships, user_credentials, one_time_codes</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -11765,7 +11929,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -11783,7 +11947,11 @@
           <t>ACC-01, ACC-09, PAY-03</t>
         </is>
       </c>
-      <c r="N12" s="3" t="n"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>organizations, users, memberships, one_time_codes</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="n"/>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -11842,7 +12010,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -11860,7 +12028,11 @@
           <t>ACC-05, ACC-12, ACC-13</t>
         </is>
       </c>
-      <c r="N13" s="3" t="n"/>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>memberships, users, one_time_codes, user_role_assignments</t>
+        </is>
+      </c>
       <c r="O13" s="3" t="n"/>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -11918,7 +12090,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -11936,7 +12108,11 @@
           <t>ACC-09, DRV-01</t>
         </is>
       </c>
-      <c r="N14" s="3" t="n"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>memberships, drivers, one_time_codes, users</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -12071,7 +12247,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -12089,7 +12265,11 @@
           <t>ACC-01, ACC-03</t>
         </is>
       </c>
-      <c r="N16" s="3" t="n"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>memberships</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="n"/>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -12148,7 +12328,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -12166,7 +12346,11 @@
           <t>ACC-12</t>
         </is>
       </c>
-      <c r="N17" s="3" t="n"/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>user_role_assignments, memberships</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -12231,7 +12415,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -12249,7 +12433,11 @@
           <t>ACC-13, PAY-02</t>
         </is>
       </c>
-      <c r="N18" s="3" t="n"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>user_role_assignments, memberships</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="n"/>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -12312,7 +12500,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -12330,7 +12518,11 @@
           <t>ACC-12, FLT-03</t>
         </is>
       </c>
-      <c r="N19" s="3" t="n"/>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>memberships, organizations, fleet_user_assignments</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="n"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -12389,7 +12581,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -12407,7 +12599,11 @@
           <t>ACC-04</t>
         </is>
       </c>
-      <c r="N20" s="3" t="n"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>user_sessions</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -12468,7 +12664,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -12482,8 +12678,16 @@
         </is>
       </c>
       <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>user_consents, legal_documents</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>• Việc chấp nhận được ghi nhận, nhưng chưa có API nào từ chối sử dụng khi còn văn bản chưa chấp nhận; điểm áp dụng sẽ làm cùng bước cấp quyền (ID-44).</t>
+        </is>
+      </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
           <t>Bảng dữ liệu IN-37, NF-08, Quyết định ID-20, Quyết định ID-38, Quyết định ID-43</t>
@@ -12543,7 +12747,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -12557,7 +12761,11 @@
         </is>
       </c>
       <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>access_audit_logs</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="n"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -12701,7 +12909,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -12715,7 +12923,11 @@
         </is>
       </c>
       <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="n"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>users, user_role_assignments, access_audit_logs</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="n"/>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -14995,7 +15207,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -15009,7 +15221,11 @@
         </is>
       </c>
       <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>vehicles, vehicle_models</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -15072,7 +15288,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -15090,7 +15306,11 @@
           <t>VEH-01, ACC-01</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>vehicles, organizations</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -15148,7 +15368,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -15166,7 +15386,11 @@
           <t>VEH-01</t>
         </is>
       </c>
-      <c r="N7" s="3" t="n"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>vehicle_models</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -15224,7 +15448,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -15242,7 +15466,11 @@
           <t>VEH-01, DEV-02</t>
         </is>
       </c>
-      <c r="N8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>vehicles, telematics, telemetry</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -15527,7 +15755,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -15545,7 +15773,11 @@
           <t>VEH-01</t>
         </is>
       </c>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>batteries, battery_models</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
           <t>• BMS của xe có gửi số serial của pin qua T-Box không? Nếu có, việc thay pin không được ghi nhận có thể phát cảnh báo.</t>
@@ -15753,7 +15985,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -15771,7 +16003,11 @@
           <t>VEH-01, BAT-01</t>
         </is>
       </c>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>warranties</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -15974,7 +16210,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -15988,7 +16224,11 @@
         </is>
       </c>
       <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>telematics</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -16050,7 +16290,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -16068,7 +16308,11 @@
           <t>DEV-01, VEH-01</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>telematics, vehicles</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -16131,7 +16375,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -16145,7 +16389,11 @@
         </is>
       </c>
       <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>telematics, telemetry, telematic_status_reports</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
           <t>• Đặc tả telematics của Tri-Ring (trường, tần suất, giao thức, quyền truy cập BMS) chưa được chốt; phương án dự phòng là gateway OBD/CAN bên thứ ba.</t>
@@ -16213,7 +16461,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -16231,7 +16479,11 @@
           <t>DEV-01, MON-01</t>
         </is>
       </c>
-      <c r="N8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>telematics, telematic_status_reports, telemetry</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -16293,7 +16545,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -16311,7 +16563,11 @@
           <t>DEV-02, NTF-01</t>
         </is>
       </c>
-      <c r="N9" s="3" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>telematics, telemetry, notifications</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -16763,7 +17019,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -16781,7 +17037,11 @@
           <t>DEV-03</t>
         </is>
       </c>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>telemetry, telematics</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -16843,7 +17103,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -16861,7 +17121,11 @@
           <t>MON-01</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>telemetry</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -17581,7 +17845,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -17599,7 +17863,11 @@
           <t>MON-09, DRV-02</t>
         </is>
       </c>
-      <c r="N15" s="3" t="n"/>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>trips, driving_sessions</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -19123,7 +19391,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -19141,7 +19409,11 @@
           <t>ACC-12</t>
         </is>
       </c>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>drivers, memberships</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -19207,7 +19479,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -19225,7 +19497,11 @@
           <t>DRV-01, VEH-01</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>driving_sessions, drivers</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -19367,7 +19643,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -19385,7 +19661,11 @@
           <t>DRV-02, SAF-03</t>
         </is>
       </c>
-      <c r="N8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>driving_sessions, drivers</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
           <t>• Hai tài xế một xe: dùng một app hay hai app?</t>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -3297,7 +3297,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>PRD F-G2, Quyết định CO-01, Quyết định CO-02, Quyết định CO-05</t>
+          <t>PRD F-G2, Quyết định CO-01, Quyết định CO-02, Quyết định CO-05, Quyết định CO-16, Quyết định CO-17</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>PRD F-H1, Quyết định CO-12, Quyết định CO-13, Quyết định CO-14, Quyết định CE-10, Quyết định CE-11</t>
+          <t>PRD F-H1, Quyết định CO-12, Quyết định CO-13, Quyết định CO-14, Quyết định CE-10, Quyết định CE-11, Quyết định CE-28</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="81" customHeight="1">
+    <row r="6" ht="108" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>CHG-02</t>
@@ -4542,7 +4542,8 @@
           <t>• Vòng đời phiên từ bản tin của trụ
 • Mọi chỉ số đo (điện năng, công suất, điện áp, dòng, % pin, nhiệt độ)
 • Không sửa được sau khi kết thúc
-• Xử lý gửi lại, trùng lặp và sai thứ tự</t>
+• Xử lý gửi lại, trùng lặp và sai thứ tự
+• Nhân viên đóng phiên mà trụ không bao giờ kết thúc (trụ khởi động lại hoặc mất điện giữa phiên)</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -4588,7 +4589,7 @@
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>PRD F-B2, Bảng dữ liệu IN-27, NF-11, deferred.md 27, Quyết định CE-10, Quyết định CE-12, Quyết định CE-14, Quyết định CE-15</t>
+          <t>PRD F-B2, Bảng dữ liệu IN-27, NF-11, deferred.md 27, Quyết định CE-10, Quyết định CE-12, Quyết định CE-14, Quyết định CE-15, Quyết định CO-16, Quyết định CE-29, deferred.md 101</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -3205,7 +3205,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>• Đặt trụ INACTIVE chỉ có hiệu lực ở lần bắt tay kết nối kế tiếp; trụ đang kết nối vẫn giữ kết nối đến khi nối lại (deferred.md 74).</t>
+          <t>• Đặt trụ INACTIVE chỉ có hiệu lực ở lần bắt tay kết nối kế tiếp; trụ đang kết nối vẫn giữ kết nối đến khi nối lại (deferred.md 102).</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>PRD F-G2, Quyết định CO-01, Quyết định CO-02, Quyết định CO-05, Quyết định CO-16, Quyết định CO-17</t>
+          <t>PRD F-G2, Quyết định CO-01, Quyết định CO-02, Quyết định CO-16, Quyết định CO-17, Quyết định CO-18</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="40.5" customHeight="1">
+    <row r="14" ht="67.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>STN-10</t>
@@ -3876,7 +3876,7 @@
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Quyết định CO-12, deferred.md 74, Quyết định CS-20</t>
+          <t>Quyết định CO-12, deferred.md 74, Quyết định CS-20, Quyết định CS-24, Quyết định CO-18, deferred.md 102</t>
         </is>
       </c>
       <c r="Q14" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>57/176</t>
+          <t>60/176</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="Q9" s="3" t="n"/>
     </row>
-    <row r="10" ht="54" customHeight="1">
+    <row r="10" ht="81" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>STN-06</t>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -3541,7 +3541,11 @@
         </is>
       </c>
       <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>• Đã có ở backend: tìm trạm gần theo bán kính, lọc đang trống, công suất tối thiểu, chuẩn đầu sạc, kèm số súng trống (F-D1). Chưa có: giá hiện tại trong từng kết quả (giá đang lấy riêng theo từng trụ từ phần thanh toán).</t>
+        </is>
+      </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
           <t>PRD F-D1, Bảng dữ liệu OUT-5</t>
@@ -4167,7 +4171,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -7912,7 +7916,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -7933,7 +7937,8 @@
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>• Ai trực CSKH 24/7 (nội bộ hay thuê ngoài), và cam kết được SLA nào?</t>
+          <t>• Ai trực CSKH 24/7 (nội bộ hay thuê ngoài), và cam kết được SLA nào?
+• Đã có ở backend: ticket kèm VIN, vị trí và mã lỗi do app gửi, kênh app/Zalo/hotline, vòng đời mở → đã tiếp nhận → đã xử lý → đóng, hạn SLA phản hồi chốt khi tạo (F-I1). Chưa có: ảnh, và các loại khiếu nại, báo lỗi phần mềm, yêu cầu dữ liệu.</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -7997,7 +8002,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -17224,7 +17229,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="67.5" customHeight="1">
+    <row r="8" ht="108" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>MON-04</t>
@@ -17274,7 +17279,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -17295,7 +17300,8 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>• Ngưỡng 30/20/10% cần chốt sau khi phỏng vấn tài xế.</t>
+          <t>• Ngưỡng 30/20/10% cần chốt sau khi phỏng vấn tài xế.
+• Đã có ở backend: cảnh báo khi pin giảm qua ngưỡng 30/20/10%, kèm trạm trống gần nhất chốt tại thời điểm cảnh báo (F-A2). Chưa có: ngưỡng đang cố định trong mã (MON-17), và cảnh báo lặp lại mỗi lần pin giảm qua ngưỡng chứ chưa phải một lần mỗi chuyến.</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -17360,7 +17366,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -17379,7 +17385,11 @@
         </is>
       </c>
       <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>• Đã có ở backend: cảnh báo nhiệt độ cao (≥60 °C) và sụt áp đột ngột (F-A4). Chưa có: cảnh báo cell/module, mất cân bằng, cách điện, contactor và làm mát, và nhắc lại khi tình trạng còn kéo dài.</t>
+        </is>
+      </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
           <t>PRD F-A4, Bảng dữ liệu IN-7, Bảng dữ liệu IN-8, Bảng dữ liệu OUT-4, deferred.md 43, deferred.md 44</t>
@@ -17441,7 +17451,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -17460,7 +17470,11 @@
         </is>
       </c>
       <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>• Đã có ở backend: mã lỗi từ thiết bị tạo cảnh báo bất thường kèm mã gốc (F-A4). Chưa có: dịch mã qua bảng mã lỗi (VEH-06, chờ bảng của nhà sản xuất), tín hiệu trạng thái thiết bị và bảng tổng hợp lỗi của đội xe.</t>
+        </is>
+      </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
           <t>PRD F-A4, Bảng dữ liệu IN-9, Bảng dữ liệu IN-10, Bảng dữ liệu IN-16, Bảng dữ liệu OUT-4, Bảng dữ liệu OUT-27, deferred.md 42, deferred.md 45</t>
@@ -17472,7 +17486,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="54" customHeight="1">
+    <row r="11" ht="67.5" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>MON-07</t>
@@ -17522,7 +17536,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -17541,7 +17555,11 @@
         </is>
       </c>
       <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>• Đã có ở backend: xu hướng SOH và số chu kỳ theo ngày, cảnh báo SOH dưới ngưỡng cấu hình (F-A3). Chưa có: dung lượng khả dụng ước tính, và định nghĩa SOH, chu kỳ thống nhất với nhà sản xuất.</t>
+        </is>
+      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
           <t>PRD F-A3, Bảng dữ liệu IN-4, Bảng dữ liệu IN-5, Điều kiện tiên quyết 1</t>
@@ -17763,7 +17781,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -18040,7 +18058,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="67.5" customHeight="1">
+    <row r="18" ht="81" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>MON-14</t>
@@ -18090,7 +18108,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -18109,7 +18127,11 @@
         </is>
       </c>
       <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>• Đã có ở backend: quãng đường, năng lượng và các chỉ số theo xe, chia theo ngày, tuần, tháng, xuất CSV (F-A6). Chưa có: chi phí đang tính theo một giá cố định mỗi kWh trong cấu hình, chưa theo biểu giá áp dụng (PAY-09).</t>
+        </is>
+      </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
           <t>PRD F-A6, Bảng dữ liệu OUT-17, deferred.md 60, deferred.md 64</t>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -1076,7 +1076,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>60/176</t>
+          <t>61/176</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="94.5" customHeight="1">
+    <row r="7" ht="108" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>FLT-03</t>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>• Giới hạn đội xe đã áp dụng cho đội xe, dữ liệu xe, danh sách xe, phiên lái, chuyến đi và người nhận cảnh báo; chưa áp dụng cho danh sách thông báo của tổ chức, ca hỗ trợ, phiên sạc, hóa đơn, pin, bảo hành và các API chi tiết theo ID (xem Known issues trong kế hoạch refactor).</t>
+          <t>• Dữ liệu không gắn xe (D5, FL-15, đang giả định): thông báo và ca hỗ trợ không gắn xe vẫn hiện với quản lý bị giới hạn đội; phiên sạc và hóa đơn không gắn xe (trừ của chính người đó), pin trong kho, thiết bị chưa lắp, bảo hành của chúng, bảo hành trụ sạc và chuyến đi không có xe bị ẩn. Chờ chủ dự án xác nhận.</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Quyết định FL-03</t>
+          <t>Quyết định FL-03, Quyết định FL-13, Quyết định FL-14, Quyết định FL-15, Quyết định FL-16</t>
         </is>
       </c>
       <c r="Q7" s="3" t="n"/>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -2413,7 +2413,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="108" customHeight="1">
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>FLT-03</t>
@@ -2485,11 +2485,7 @@
           <t>fleet_user_assignments</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>• Dữ liệu không gắn xe (D5, FL-15, đang giả định): thông báo và ca hỗ trợ không gắn xe vẫn hiện với quản lý bị giới hạn đội; phiên sạc và hóa đơn không gắn xe (trừ của chính người đó), pin trong kho, thiết bị chưa lắp, bảo hành của chúng, bảo hành trụ sạc và chuyến đi không có xe bị ẩn. Chờ chủ dự án xác nhận.</t>
-        </is>
-      </c>
+      <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Quyết định FL-03, Quyết định FL-13, Quyết định FL-14, Quyết định FL-15, Quyết định FL-16</t>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -7094,7 +7094,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Tài xế, Quản lý đội xe, Vận hành, CSKH</t>
+          <t>Tài xế, Quản lý đội xe, Điều vận, Vận hành, CSKH</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>4</v>
@@ -636,7 +636,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>16/22</t>
+          <t>17/23</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>0/19</t>
+          <t>0/20</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -1718,10 +1718,10 @@
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>17</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>61/176</t>
+          <t>62/177</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>0/138</t>
+          <t>0/139</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13086,6 +13086,82 @@
         </is>
       </c>
       <c r="Q26" s="3" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ACC-23</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Cài đặt tổ chức</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Cho quản trị viên của tổ chức chọn cách hệ thống hoạt động cho tổ chức mình: phiên lái xe không hoạt động tự kết thúc sau bao lâu, xe gửi dữ liệu bao lâu một lần.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Mỗi khách hàng tự chỉnh quy tắc theo cách vận hành xe của mình, không cần nhờ chúng tôi.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Quản trị tổ chức, Đồng quản trị (nội bộ), Quản trị trưởng (nội bộ)</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>• Thời gian tự kết thúc phiên lái xe và chu kỳ gửi dữ liệu, trong giới hạn cho phép
+• Mỗi thay đổi cần lý do và được lưu trong lịch sử thay đổi</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>P1.0</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Có trong mọi gói</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Không cần</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>organization_settings</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Quyết định ID-45</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/product/features/features.xlsx
+++ b/docs/product/features/features.xlsx
@@ -2553,7 +2553,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="M5" s="3" t="n"/>
